--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-09T16:50:32Z (source: live)</t>
+          <t>Registry updated 2026-10-09T22:41:29Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-09T22:41:29Z (source: live)</t>
+          <t>Registry updated 2026-10-10T05:57:03Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-10T05:57:03Z (source: live)</t>
+          <t>Registry updated 2026-10-10T12:36:53Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-10T12:36:53Z (source: live)</t>
+          <t>Registry updated 2026-10-10T21:47:32Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-10T21:47:32Z (source: live)</t>
+          <t>Registry updated 2026-10-11T05:51:57Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-11T05:51:57Z (source: live)</t>
+          <t>Registry updated 2026-10-11T12:55:38Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-11T12:55:38Z (source: live)</t>
+          <t>Registry updated 2026-10-11T22:01:04Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-11T22:01:04Z (source: live)</t>
+          <t>Registry updated 2026-10-12T06:03:35Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-12T06:03:35Z (source: live)</t>
+          <t>Registry updated 2026-10-12T15:32:51Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-12T15:32:51Z (source: live)</t>
+          <t>Registry updated 2026-10-13T00:44:46Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16802,7 +16802,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-13T00:44:46Z (source: live)</t>
+          <t>Registry updated 2026-10-13T14:16:40Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R197"/>
+  <dimension ref="A1:R196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>gemini-nano-banana-2.1</t>
+          <t>gemini-4-argon</t>
         </is>
       </c>
       <c r="C76" s="35" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="G76" s="20" t="inlineStr">
         <is>
-          <t>gemini-nano-banana-2.1</t>
+          <t>gemini-4-argon</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="Q76" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R76" s="18" t="n">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-preview</t>
+          <t>gemini-nano-banana-2.1</t>
         </is>
       </c>
       <c r="C77" s="35" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-preview</t>
+          <t>gemini-nano-banana-2.1</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R77" s="2" t="n">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-streaming-preview</t>
+          <t>gemini-robotics-er-2-preview</t>
         </is>
       </c>
       <c r="C78" s="35" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="G78" s="20" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-streaming-preview</t>
+          <t>gemini-robotics-er-2-preview</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>codestral-22b-instruct-v0.1</t>
+          <t>gemini-robotics-er-2-streaming-preview</t>
         </is>
       </c>
       <c r="C79" s="35" t="inlineStr">
@@ -7079,28 +7079,30 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>22B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>mistralai/codestral-22b-instruct-v0.1</t>
-        </is>
-      </c>
-      <c r="H79" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="n"/>
+          <t>gemini-robotics-er-2-streaming-preview</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>1048576</v>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K79" s="23" t="inlineStr">
@@ -7118,13 +7120,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N79" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -7133,7 +7135,7 @@
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R79" s="2" t="n">
@@ -7146,7 +7148,7 @@
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite</t>
+          <t>codestral-22b-instruct-v0.1</t>
         </is>
       </c>
       <c r="C80" s="35" t="inlineStr">
@@ -7159,30 +7161,28 @@
       </c>
       <c r="E80" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>22B</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G80" s="20" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I80" s="22" t="n">
-        <v>1048576</v>
-      </c>
+          <t>mistralai/codestral-22b-instruct-v0.1</t>
+        </is>
+      </c>
+      <c r="H80" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="n"/>
       <c r="J80" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K80" s="23" t="inlineStr">
@@ -7195,18 +7195,18 @@
           <t>Yes~</t>
         </is>
       </c>
-      <c r="M80" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N80" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M80" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N80" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O80" s="18" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="P80" s="18" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="Q80" s="20" t="inlineStr">
         <is>
-          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+          <t>coding, extraction, agent</t>
         </is>
       </c>
       <c r="R80" s="18" t="n">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>starcoder2-15b</t>
+          <t>gemini-2.5-flash-lite</t>
         </is>
       </c>
       <c r="C81" s="35" t="inlineStr">
@@ -7241,28 +7241,30 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>15B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>bigcode/starcoder2-15b</t>
-        </is>
-      </c>
-      <c r="H81" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="n"/>
+          <t>gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>1048576</v>
+      </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K81" s="23" t="inlineStr">
@@ -7275,9 +7277,9 @@
           <t>Yes~</t>
         </is>
       </c>
-      <c r="M81" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M81" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="N81" s="9" t="inlineStr">
@@ -7286,7 +7288,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
@@ -7295,7 +7297,7 @@
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R81" s="2" t="n">
@@ -7308,7 +7310,7 @@
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>ministral-14b-2512</t>
+          <t>starcoder2-15b</t>
         </is>
       </c>
       <c r="C82" s="35" t="inlineStr">
@@ -7321,40 +7323,38 @@
       </c>
       <c r="E82" s="18" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>15B</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G82" s="20" t="inlineStr">
         <is>
-          <t>ministral-14b-2512</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I82" s="22" t="n">
-        <v>262144</v>
-      </c>
+          <t>bigcode/starcoder2-15b</t>
+        </is>
+      </c>
+      <c r="H82" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="n"/>
       <c r="J82" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K82" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K82" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L82" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M82" s="24" t="inlineStr">
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="O82" s="18" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P82" s="18" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="Q82" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R82" s="18" t="n">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>ministral-14b-latest</t>
+          <t>ministral-14b-2512</t>
         </is>
       </c>
       <c r="C83" s="35" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>ministral-14b-latest</t>
+          <t>ministral-14b-2512</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="B84" s="19" t="inlineStr">
         <is>
-          <t>mistral-small-2603</t>
+          <t>ministral-14b-latest</t>
         </is>
       </c>
       <c r="C84" s="35" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E84" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="G84" s="20" t="inlineStr">
         <is>
-          <t>mistral-small-2603</t>
+          <t>ministral-14b-latest</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="O84" s="18" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="P84" s="18" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>mistral-small-latest</t>
+          <t>mistral-small-2603</t>
         </is>
       </c>
       <c r="C85" s="35" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>mistral-small-latest</t>
+          <t>mistral-small-2603</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>mistral-small-latest</t>
         </is>
       </c>
       <c r="C86" s="35" t="inlineStr">
@@ -7649,38 +7649,40 @@
       </c>
       <c r="E86" s="18" t="inlineStr">
         <is>
-          <t>12B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G86" s="20" t="inlineStr">
         <is>
-          <t>google/gemma-3-12b-it</t>
-        </is>
-      </c>
-      <c r="H86" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I86" s="22" t="n"/>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I86" s="22" t="n">
+        <v>262144</v>
+      </c>
       <c r="J86" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K86" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L86" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M86" s="24" t="inlineStr">
@@ -7694,7 +7696,7 @@
         </is>
       </c>
       <c r="O86" s="18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P86" s="18" t="inlineStr">
         <is>
@@ -7703,7 +7705,7 @@
       </c>
       <c r="Q86" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, fast</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R86" s="18" t="n">
@@ -7716,7 +7718,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>mistral-nemo-12b-instruct</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="C87" s="35" t="inlineStr">
@@ -7739,7 +7741,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>nv-mistralai/mistral-nemo-12b-instruct</t>
+          <t>google/gemma-3-12b-it</t>
         </is>
       </c>
       <c r="H87" s="21" t="inlineStr">
@@ -7750,7 +7752,7 @@
       <c r="I87" s="7" t="n"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K87" s="23" t="inlineStr">
@@ -7783,7 +7785,7 @@
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>vision, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R87" s="2" t="n">
@@ -7796,7 +7798,7 @@
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite</t>
+          <t>mistral-nemo-12b-instruct</t>
         </is>
       </c>
       <c r="C88" s="35" t="inlineStr">
@@ -7809,30 +7811,28 @@
       </c>
       <c r="E88" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>12B</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G88" s="20" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I88" s="22" t="n">
-        <v>1048576</v>
-      </c>
+          <t>nv-mistralai/mistral-nemo-12b-instruct</t>
+        </is>
+      </c>
+      <c r="H88" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I88" s="22" t="n"/>
       <c r="J88" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K88" s="23" t="inlineStr">
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="O88" s="18" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="P88" s="18" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="Q88" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R88" s="18" t="n">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite-preview</t>
+          <t>gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="C89" s="35" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite-preview</t>
+          <t>gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite</t>
+          <t>gemini-3.1-flash-lite-preview</t>
         </is>
       </c>
       <c r="C90" s="35" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="G90" s="20" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite</t>
+          <t>gemini-3.1-flash-lite-preview</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>gemini-flash-lite-latest</t>
+          <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C91" s="35" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>gemini-flash-lite-latest</t>
+          <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -8124,30 +8124,30 @@
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>ministral-8b-2512</t>
-        </is>
-      </c>
-      <c r="C92" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
+          <t>gemini-flash-lite-latest</t>
+        </is>
+      </c>
+      <c r="C92" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="D92" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" s="18" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G92" s="20" t="inlineStr">
         <is>
-          <t>ministral-8b-2512</t>
+          <t>gemini-flash-lite-latest</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
@@ -8156,21 +8156,21 @@
         </is>
       </c>
       <c r="I92" s="22" t="n">
-        <v>262144</v>
+        <v>1048576</v>
       </c>
       <c r="J92" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K92" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L92" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M92" s="24" t="inlineStr">
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="O92" s="18" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="P92" s="18" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>ministral-8b-latest</t>
+          <t>ministral-8b-2512</t>
         </is>
       </c>
       <c r="C93" s="37" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>ministral-8b-latest</t>
+          <t>ministral-8b-2512</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B94" s="19" t="inlineStr">
         <is>
-          <t>llama3.1-8b</t>
+          <t>ministral-8b-latest</t>
         </is>
       </c>
       <c r="C94" s="37" t="inlineStr">
@@ -8306,35 +8306,35 @@
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>cerebras</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G94" s="20" t="inlineStr">
         <is>
-          <t>llama3.1-8b</t>
-        </is>
-      </c>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>ministral-8b-latest</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I94" s="22" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="J94" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K94" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L94" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M94" s="24" t="inlineStr">
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="O94" s="18" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P94" s="18" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="Q94" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R94" s="18" t="n">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>cosmos-reason2-8b</t>
+          <t>llama3.1-8b</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
@@ -8388,20 +8388,22 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>cerebras</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>nvidia/cosmos-reason2-8b</t>
-        </is>
-      </c>
-      <c r="H95" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I95" s="7" t="n"/>
+          <t>llama3.1-8b</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="n">
+        <v>131072</v>
+      </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
           <t>Text</t>
@@ -8428,7 +8430,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -8437,7 +8439,7 @@
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R95" s="2" t="n">
@@ -8450,7 +8452,7 @@
       </c>
       <c r="B96" s="19" t="inlineStr">
         <is>
-          <t>granite-3.0-8b-instruct</t>
+          <t>cosmos-reason2-8b</t>
         </is>
       </c>
       <c r="C96" s="37" t="inlineStr">
@@ -8473,7 +8475,7 @@
       </c>
       <c r="G96" s="20" t="inlineStr">
         <is>
-          <t>ibm/granite-3.0-8b-instruct</t>
+          <t>nvidia/cosmos-reason2-8b</t>
         </is>
       </c>
       <c r="H96" s="21" t="inlineStr">
@@ -8530,7 +8532,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>granite-8b-code-instruct</t>
+          <t>granite-3.0-8b-instruct</t>
         </is>
       </c>
       <c r="C97" s="37" t="inlineStr">
@@ -8553,7 +8555,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>ibm/granite-8b-code-instruct</t>
+          <t>ibm/granite-3.0-8b-instruct</t>
         </is>
       </c>
       <c r="H97" s="21" t="inlineStr">
@@ -8582,9 +8584,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N97" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N97" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O97" s="2" t="n">
@@ -8597,7 +8599,7 @@
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R97" s="2" t="n">
@@ -8610,7 +8612,7 @@
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>mistral-nemo-minitron-8b-8k-instruct</t>
+          <t>granite-8b-code-instruct</t>
         </is>
       </c>
       <c r="C98" s="37" t="inlineStr">
@@ -8633,7 +8635,7 @@
       </c>
       <c r="G98" s="20" t="inlineStr">
         <is>
-          <t>nvidia/mistral-nemo-minitron-8b-8k-instruct</t>
+          <t>ibm/granite-8b-code-instruct</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
@@ -8662,9 +8664,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N98" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N98" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O98" s="18" t="n">
@@ -8677,7 +8679,7 @@
       </c>
       <c r="Q98" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R98" s="18" t="n">
@@ -8690,7 +8692,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>allam-2-7b</t>
+          <t>mistral-nemo-minitron-8b-8k-instruct</t>
         </is>
       </c>
       <c r="C99" s="37" t="inlineStr">
@@ -8703,27 +8705,25 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>groq</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>allam-2-7b</t>
-        </is>
-      </c>
-      <c r="H99" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="n">
-        <v>4096</v>
-      </c>
+          <t>nvidia/mistral-nemo-minitron-8b-8k-instruct</t>
+        </is>
+      </c>
+      <c r="H99" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="n"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
           <t>Text</t>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>codegemma-1.1-7b</t>
+          <t>allam-2-7b</t>
         </is>
       </c>
       <c r="C100" s="37" t="inlineStr">
@@ -8790,20 +8790,22 @@
       </c>
       <c r="F100" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>groq</t>
         </is>
       </c>
       <c r="G100" s="20" t="inlineStr">
         <is>
-          <t>google/codegemma-1.1-7b</t>
-        </is>
-      </c>
-      <c r="H100" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I100" s="22" t="n"/>
+          <t>allam-2-7b</t>
+        </is>
+      </c>
+      <c r="H100" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
+        </is>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>4096</v>
+      </c>
       <c r="J100" s="18" t="inlineStr">
         <is>
           <t>Text</t>
@@ -8830,7 +8832,7 @@
         </is>
       </c>
       <c r="O100" s="18" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="P100" s="18" t="inlineStr">
         <is>
@@ -8852,7 +8854,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>codegemma-7b</t>
+          <t>codegemma-1.1-7b</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
@@ -8875,7 +8877,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>google/codegemma-7b</t>
+          <t>google/codegemma-1.1-7b</t>
         </is>
       </c>
       <c r="H101" s="21" t="inlineStr">
@@ -8932,7 +8934,7 @@
       </c>
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>mistral-7b-instruct-v0.3</t>
+          <t>codegemma-7b</t>
         </is>
       </c>
       <c r="C102" s="37" t="inlineStr">
@@ -8955,7 +8957,7 @@
       </c>
       <c r="G102" s="20" t="inlineStr">
         <is>
-          <t>mistralai/mistral-7b-instruct-v0.3</t>
+          <t>google/codegemma-7b</t>
         </is>
       </c>
       <c r="H102" s="21" t="inlineStr">
@@ -9012,7 +9014,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>sea-lion-7b-instruct</t>
+          <t>mistral-7b-instruct-v0.3</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
@@ -9035,7 +9037,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>aisingapore/sea-lion-7b-instruct</t>
+          <t>mistralai/mistral-7b-instruct-v0.3</t>
         </is>
       </c>
       <c r="H103" s="21" t="inlineStr">
@@ -9092,7 +9094,7 @@
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>zamba2-7b-instruct</t>
+          <t>sea-lion-7b-instruct</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
@@ -9115,7 +9117,7 @@
       </c>
       <c r="G104" s="20" t="inlineStr">
         <is>
-          <t>zyphra/zamba2-7b-instruct</t>
+          <t>aisingapore/sea-lion-7b-instruct</t>
         </is>
       </c>
       <c r="H104" s="21" t="inlineStr">
@@ -9172,7 +9174,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>deepseek-coder-6.7b-instruct</t>
+          <t>zamba2-7b-instruct</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
@@ -9185,7 +9187,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>6.7B</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -9195,7 +9197,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-coder-6.7b-instruct</t>
+          <t>zyphra/zamba2-7b-instruct</t>
         </is>
       </c>
       <c r="H105" s="21" t="inlineStr">
@@ -9209,9 +9211,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K105" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K105" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L105" s="23" t="inlineStr">
@@ -9224,9 +9226,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N105" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N105" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O105" s="2" t="n">
@@ -9239,7 +9241,7 @@
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>coding, fast</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R105" s="2" t="n">
@@ -9252,7 +9254,7 @@
       </c>
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>deepseek-coder-6.7b-instruct</t>
         </is>
       </c>
       <c r="C106" s="37" t="inlineStr">
@@ -9265,7 +9267,7 @@
       </c>
       <c r="E106" s="18" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>6.7B</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -9275,7 +9277,7 @@
       </c>
       <c r="G106" s="20" t="inlineStr">
         <is>
-          <t>google/gemma-3-4b-it</t>
+          <t>deepseek-ai/deepseek-coder-6.7b-instruct</t>
         </is>
       </c>
       <c r="H106" s="21" t="inlineStr">
@@ -9286,7 +9288,7 @@
       <c r="I106" s="22" t="n"/>
       <c r="J106" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K106" s="24" t="inlineStr">
@@ -9304,13 +9306,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N106" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N106" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O106" s="18" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P106" s="18" t="inlineStr">
         <is>
@@ -9319,7 +9321,7 @@
       </c>
       <c r="Q106" s="20" t="inlineStr">
         <is>
-          <t>vision, fast</t>
+          <t>coding, fast</t>
         </is>
       </c>
       <c r="R106" s="18" t="n">
@@ -9332,7 +9334,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>riva-translate-4b-instruct</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C107" s="37" t="inlineStr">
@@ -9355,7 +9357,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>nvidia/riva-translate-4b-instruct</t>
+          <t>google/gemma-3-4b-it</t>
         </is>
       </c>
       <c r="H107" s="21" t="inlineStr">
@@ -9366,7 +9368,7 @@
       <c r="I107" s="7" t="n"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr">
@@ -9399,7 +9401,7 @@
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>vision, fast</t>
         </is>
       </c>
       <c r="R107" s="2" t="n">
@@ -9412,7 +9414,7 @@
       </c>
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>riva-translate-4b-instruct-v2</t>
+          <t>riva-translate-4b-instruct</t>
         </is>
       </c>
       <c r="C108" s="37" t="inlineStr">
@@ -9435,7 +9437,7 @@
       </c>
       <c r="G108" s="20" t="inlineStr">
         <is>
-          <t>nvidia/riva-translate-4b-instruct-v2</t>
+          <t>nvidia/riva-translate-4b-instruct</t>
         </is>
       </c>
       <c r="H108" s="21" t="inlineStr">
@@ -9492,53 +9494,51 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>ministral-3b-2512</t>
-        </is>
-      </c>
-      <c r="C109" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>riva-translate-4b-instruct-v2</t>
+        </is>
+      </c>
+      <c r="C109" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>ministral-3b-2512</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I109" s="7" t="n">
-        <v>131072</v>
-      </c>
+          <t>nvidia/riva-translate-4b-instruct-v2</t>
+        </is>
+      </c>
+      <c r="H109" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I109" s="7" t="n"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K109" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L109" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L109" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M109" s="9" t="inlineStr">
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>vision, long_doc, fast</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R109" s="2" t="n">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>ministral-3b-latest</t>
+          <t>ministral-3b-2512</t>
         </is>
       </c>
       <c r="C110" s="39" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="G110" s="20" t="inlineStr">
         <is>
-          <t>ministral-3b-latest</t>
+          <t>ministral-3b-2512</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>granite-3.0-3b-a800m-instruct</t>
+          <t>ministral-3b-latest</t>
         </is>
       </c>
       <c r="C111" s="39" t="inlineStr">
@@ -9674,33 +9674,35 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>ibm/granite-3.0-3b-a800m-instruct</t>
-        </is>
-      </c>
-      <c r="H111" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I111" s="7" t="n"/>
+          <t>ministral-3b-latest</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="n">
+        <v>131072</v>
+      </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K111" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L111" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K111" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L111" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M111" s="9" t="inlineStr">
@@ -9714,7 +9716,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
@@ -9723,7 +9725,7 @@
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>vision, long_doc, fast</t>
         </is>
       </c>
       <c r="R111" s="2" t="n">
@@ -9736,7 +9738,7 @@
       </c>
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>inkling</t>
+          <t>granite-3.0-3b-a800m-instruct</t>
         </is>
       </c>
       <c r="C112" s="39" t="inlineStr">
@@ -9749,45 +9751,43 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G112" s="20" t="inlineStr">
         <is>
-          <t>thinkingmachines/inkling:free</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>1048576</v>
-      </c>
+          <t>ibm/granite-3.0-3b-a800m-instruct</t>
+        </is>
+      </c>
+      <c r="H112" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I112" s="22" t="n"/>
       <c r="J112" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K112" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L112" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M112" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K112" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L112" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M112" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N112" s="24" t="inlineStr">
@@ -9796,16 +9796,16 @@
         </is>
       </c>
       <c r="O112" s="18" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="P112" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q112" s="20" t="inlineStr">
         <is>
-          <t>reasoning, vision, agent, long_doc</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R112" s="18" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>inkling-small</t>
+          <t>inkling</t>
         </is>
       </c>
       <c r="C113" s="39" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>thinkingmachines/inkling-small:free</t>
+          <t>thinkingmachines/inkling:free</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>reasoning, vision, agent, long_doc, fast</t>
+          <t>reasoning, vision, agent, long_doc</t>
         </is>
       </c>
       <c r="R113" s="2" t="n">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B114" s="19" t="inlineStr">
         <is>
-          <t>nemotron-3.5-lightning</t>
+          <t>inkling-small</t>
         </is>
       </c>
       <c r="C114" s="39" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G114" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-3.5-lightning:free</t>
+          <t>thinkingmachines/inkling-small:free</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -9932,11 +9932,11 @@
         </is>
       </c>
       <c r="I114" s="22" t="n">
-        <v>1000000</v>
+        <v>1048576</v>
       </c>
       <c r="J114" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K114" s="8" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="Q114" s="20" t="inlineStr">
         <is>
-          <t>reasoning, agent, long_doc</t>
+          <t>reasoning, vision, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R114" s="18" t="n">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>magistral-medium-latest</t>
+          <t>nemotron-3.5-lightning</t>
         </is>
       </c>
       <c r="C115" s="39" t="inlineStr">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>magistral-medium-latest</t>
+          <t>nvidia/nemotron-3.5-lightning:free</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
@@ -10014,11 +10014,11 @@
         </is>
       </c>
       <c r="I115" s="7" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K115" s="8" t="inlineStr">
@@ -10026,32 +10026,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L115" s="8" t="inlineStr">
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M115" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M115" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N115" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q115" s="5" t="inlineStr">
         <is>
-          <t>reasoning, vision, extraction, agent, long_doc</t>
+          <t>reasoning, agent, long_doc</t>
         </is>
       </c>
       <c r="R115" s="2" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="B116" s="19" t="inlineStr">
         <is>
-          <t>magistral-small-latest</t>
+          <t>magistral-medium-latest</t>
         </is>
       </c>
       <c r="C116" s="39" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="G116" s="20" t="inlineStr">
         <is>
-          <t>magistral-small-latest</t>
+          <t>magistral-medium-latest</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="Q116" s="20" t="inlineStr">
         <is>
-          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+          <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R116" s="18" t="n">
@@ -10146,240 +10146,242 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
+          <t>magistral-small-latest</t>
+        </is>
+      </c>
+      <c r="C117" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>magistral-small-latest</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="n">
+        <v>262144</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K117" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M117" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="n">
+        <v>104</v>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
+        <is>
           <t>nemotron-3.5-content-safety</t>
         </is>
       </c>
-      <c r="C117" s="39" t="inlineStr">
+      <c r="C118" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="D118" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F118" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G118" s="20" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-content-safety:free</t>
         </is>
       </c>
-      <c r="H117" s="8" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I117" s="7" t="n">
+      <c r="I118" s="22" t="n">
         <v>128000</v>
       </c>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="J118" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K117" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L117" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M117" s="8" t="inlineStr">
+      <c r="K118" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L118" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M118" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N117" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O117" s="2" t="n">
+      <c r="N118" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O118" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P117" s="2" t="inlineStr">
+      <c r="P118" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q117" s="5" t="inlineStr">
+      <c r="Q118" s="20" t="inlineStr">
         <is>
           <t>reasoning, vision, long_doc</t>
         </is>
       </c>
-      <c r="R117" s="2" t="n">
+      <c r="R118" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="10" t="n">
-        <v>103</v>
-      </c>
-      <c r="B118" s="11" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="25" t="n">
+        <v>104</v>
+      </c>
+      <c r="B119" s="26" t="inlineStr">
         <is>
           <t>nemotron-3.5-content-safety</t>
         </is>
       </c>
-      <c r="C118" s="40" t="inlineStr">
+      <c r="C119" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="10" t="inlineStr">
+      <c r="D119" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F118" s="13" t="inlineStr">
+      <c r="F119" s="27" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G118" s="13" t="inlineStr">
+      <c r="G119" s="27" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-content-safety</t>
         </is>
       </c>
-      <c r="H118" s="14" t="inlineStr">
+      <c r="H119" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I118" s="15" t="n"/>
-      <c r="J118" s="10" t="inlineStr">
+      <c r="I119" s="28" t="n"/>
+      <c r="J119" s="25" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K118" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L118" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M118" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N118" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O118" s="10" t="n">
+      <c r="K119" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L119" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N119" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O119" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="P118" s="10" t="inlineStr">
+      <c r="P119" s="25" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q118" s="13" t="inlineStr">
+      <c r="Q119" s="27" t="inlineStr">
         <is>
           <t>reasoning, extraction, agent</t>
         </is>
       </c>
-      <c r="R118" s="10" t="n">
+      <c r="R119" s="25" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="18" t="n">
-        <v>104</v>
-      </c>
-      <c r="B119" s="19" t="inlineStr">
-        <is>
-          <t>nemotron-parse</t>
-        </is>
-      </c>
-      <c r="C119" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D119" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F119" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G119" s="20" t="inlineStr">
-        <is>
-          <t>nvidia/nemotron-parse</t>
-        </is>
-      </c>
-      <c r="H119" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I119" s="22" t="n"/>
-      <c r="J119" s="18" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K119" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L119" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M119" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N119" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O119" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="P119" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q119" s="20" t="inlineStr">
-        <is>
-          <t>reasoning, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R119" s="18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -10388,7 +10390,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>nemotron-parse-2.0</t>
+          <t>nemotron-parse</t>
         </is>
       </c>
       <c r="C120" s="39" t="inlineStr">
@@ -10411,7 +10413,7 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse-2.0</t>
+          <t>nvidia/nemotron-parse</t>
         </is>
       </c>
       <c r="H120" s="21" t="inlineStr">
@@ -10468,7 +10470,7 @@
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>lfm-2.5-2.6b</t>
+          <t>nemotron-parse-2.0</t>
         </is>
       </c>
       <c r="C121" s="39" t="inlineStr">
@@ -10481,45 +10483,43 @@
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>2.6B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G121" s="20" t="inlineStr">
         <is>
-          <t>liquid/lfm-2.5-2.6b:free</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I121" s="22" t="n">
-        <v>65536</v>
-      </c>
+          <t>nvidia/nemotron-parse-2.0</t>
+        </is>
+      </c>
+      <c r="H121" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I121" s="22" t="n"/>
       <c r="J121" s="18" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K121" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L121" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M121" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K121" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L121" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M121" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="N121" s="24" t="inlineStr">
@@ -10528,16 +10528,16 @@
         </is>
       </c>
       <c r="O121" s="18" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="P121" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
-          <t>long_doc, fast</t>
+          <t>reasoning, extraction, agent</t>
         </is>
       </c>
       <c r="R121" s="18" t="n">
@@ -10550,404 +10550,404 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
+          <t>lfm-2.5-2.6b</t>
+        </is>
+      </c>
+      <c r="C122" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>2.6B</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>liquid/lfm-2.5-2.6b:free</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K122" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M122" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N122" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q122" s="5" t="inlineStr">
+        <is>
+          <t>long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="n">
+        <v>108</v>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C122" s="39" t="inlineStr">
+      <c r="C123" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="D123" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F123" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G123" s="20" t="inlineStr">
         <is>
           <t>google/lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H122" s="6" t="inlineStr">
+      <c r="H123" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I122" s="7" t="n">
+      <c r="I123" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J123" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K122" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L122" s="8" t="inlineStr">
+      <c r="K123" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M122" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N122" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O122" s="2" t="n">
+      <c r="M123" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N123" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O123" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P122" s="2" t="inlineStr">
+      <c r="P123" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q122" s="5" t="inlineStr">
+      <c r="Q123" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R122" s="2" t="n">
+      <c r="R123" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="10" t="n">
-        <v>107</v>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="25" t="n">
+        <v>108</v>
+      </c>
+      <c r="B124" s="26" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C123" s="40" t="inlineStr">
+      <c r="C124" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="10" t="inlineStr">
+      <c r="D124" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F123" s="13" t="inlineStr">
+      <c r="F124" s="27" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G123" s="13" t="inlineStr">
+      <c r="G124" s="27" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H123" s="14" t="inlineStr">
+      <c r="H124" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I123" s="15" t="n"/>
-      <c r="J123" s="10" t="inlineStr">
+      <c r="I124" s="28" t="n"/>
+      <c r="J124" s="25" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K123" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L123" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M123" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N123" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O123" s="10" t="n">
+      <c r="K124" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L124" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M124" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O124" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="P123" s="10" t="inlineStr">
+      <c r="P124" s="25" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q123" s="13" t="inlineStr">
+      <c r="Q124" s="27" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R123" s="10" t="n">
+      <c r="R124" s="25" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="18" t="n">
-        <v>108</v>
-      </c>
-      <c r="B124" s="19" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C124" s="39" t="inlineStr">
+      <c r="C125" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D124" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="18" t="inlineStr">
+      <c r="D125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F124" s="20" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G124" s="20" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>google/lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H125" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I124" s="22" t="n">
+      <c r="I125" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J124" s="18" t="inlineStr">
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K124" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
+      <c r="K125" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M124" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N124" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O124" s="18" t="n">
+      <c r="M125" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="P124" s="18" t="inlineStr">
+      <c r="P125" s="2" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q124" s="20" t="inlineStr">
+      <c r="Q125" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R124" s="18" t="n">
+      <c r="R125" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="25" t="n">
-        <v>108</v>
-      </c>
-      <c r="B125" s="26" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C125" s="40" t="inlineStr">
+      <c r="C126" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D125" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="25" t="inlineStr">
+      <c r="D126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F125" s="27" t="inlineStr">
+      <c r="F126" s="13" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G125" s="27" t="inlineStr">
+      <c r="G126" s="13" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H125" s="14" t="inlineStr">
+      <c r="H126" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I125" s="28" t="n"/>
-      <c r="J125" s="25" t="inlineStr">
+      <c r="I126" s="15" t="n"/>
+      <c r="J126" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K125" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L125" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M125" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N125" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O125" s="25" t="n">
+      <c r="K126" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L126" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M126" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O126" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="P125" s="25" t="inlineStr">
+      <c r="P126" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q125" s="27" t="inlineStr">
+      <c r="Q126" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R125" s="25" t="n">
+      <c r="R126" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C126" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>fastrouter/auto</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I126" s="7" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K126" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L126" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M126" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N126" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O126" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="P126" s="2" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q126" s="5" t="inlineStr">
-        <is>
-          <t>vision, long_doc</t>
-        </is>
-      </c>
-      <c r="R126" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B127" s="19" t="inlineStr">
         <is>
-          <t>dots-3-note-preview</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C127" s="39" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="F127" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G127" s="20" t="inlineStr">
         <is>
-          <t>dots-studio/dots-3-note-preview:free</t>
+          <t>fastrouter/auto</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
@@ -10988,21 +10988,21 @@
         </is>
       </c>
       <c r="I127" s="22" t="n">
-        <v>512000</v>
+        <v>1000000</v>
       </c>
       <c r="J127" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K127" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L127" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K127" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L127" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M127" s="24" t="inlineStr">
@@ -11016,7 +11016,7 @@
         </is>
       </c>
       <c r="O127" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P127" s="18" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="Q127" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R127" s="18" t="n">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-6</t>
+          <t>dots-3-note-preview</t>
         </is>
       </c>
       <c r="C128" s="39" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-6</t>
+          <t>dots-studio/dots-3-note-preview:free</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="I128" s="7" t="n">
-        <v>400000</v>
+        <v>512000</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K128" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M128" s="9" t="inlineStr">
@@ -11098,7 +11098,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="Q128" s="5" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R128" s="2" t="n">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>apodex-1.1-mini</t>
+          <t>wan-v2-6</t>
         </is>
       </c>
       <c r="C129" s="39" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>apodex/apodex-1.1-mini:free</t>
+          <t>wanx/wan-v2-6</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -11152,21 +11152,21 @@
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>262144</v>
+        <v>400000</v>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K129" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L129" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K129" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L129" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M129" s="24" t="inlineStr">
@@ -11180,7 +11180,7 @@
         </is>
       </c>
       <c r="O129" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P129" s="18" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Q129" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, long_doc, fast</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ling-3.1-flash</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="C135" s="39" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>inclusionai/ling-3.1-flash</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K135" s="8" t="inlineStr">
@@ -11654,9 +11654,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L135" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L135" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M135" s="9" t="inlineStr">
@@ -11670,16 +11670,16 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
-          <t>agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R135" s="2" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="B136" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-fast</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C136" s="39" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="G136" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-fast</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="Q136" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R136" s="18" t="n">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C137" s="39" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11888,11 +11888,11 @@
         </is>
       </c>
       <c r="I138" s="22" t="n">
-        <v>262144</v>
+        <v>256000</v>
       </c>
       <c r="J138" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K138" s="8" t="inlineStr">
@@ -11910,9 +11910,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N138" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N138" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O138" s="18" t="n">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="Q138" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R138" s="18" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12038,12 +12038,12 @@
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>cohere/north-mini-code:free</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12064,32 +12064,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L140" s="8" t="inlineStr">
+      <c r="L140" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M140" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N140" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M140" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N140" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O140" s="18" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P140" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q140" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R140" s="18" t="n">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12125,20 +12125,20 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
-        </is>
-      </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
+          <t>openrouter/free</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I141" s="7" t="n">
-        <v>256000</v>
+        <v>200000</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K141" s="8" t="inlineStr">
@@ -12146,9 +12146,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L141" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M141" s="9" t="inlineStr">
@@ -12156,9 +12156,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N141" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N141" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O141" s="2" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="Q141" s="5" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R141" s="2" t="n">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
+          <t>openai/gpt-live-1</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
@@ -12216,21 +12216,21 @@
         </is>
       </c>
       <c r="I142" s="22" t="n">
-        <v>200000</v>
+        <v>128000</v>
       </c>
       <c r="J142" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K142" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L142" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M142" s="24" t="inlineStr">
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="O142" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P142" s="18" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12284,35 +12284,35 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>voxtral-small-2507</t>
+        </is>
+      </c>
+      <c r="H143" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>128000</v>
+        <v>32768</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K143" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M143" s="9" t="inlineStr">
@@ -12326,16 +12326,16 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="H144" s="34" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12448,35 +12448,35 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
-        </is>
-      </c>
-      <c r="H145" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>alibaba/happyhorse-1.1</t>
+        </is>
+      </c>
+      <c r="H145" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>32768</v>
+        <v>4096</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -12490,16 +12490,16 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R145" s="2" t="n">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H146" s="38" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="J146" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K146" s="24" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="Q146" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R146" s="18" t="n">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H147" s="38" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12720,9 +12720,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L148" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M148" s="24" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="Q148" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R148" s="18" t="n">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12802,9 +12802,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L149" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L149" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M149" s="9" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R149" s="2" t="n">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="J152" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K152" s="24" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="Q152" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R152" s="18" t="n">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>wanx/wan-v3-0</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13186,35 +13186,33 @@
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
-        </is>
-      </c>
-      <c r="H154" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
-        </is>
-      </c>
-      <c r="I154" s="22" t="n">
-        <v>4096</v>
-      </c>
+          <t>nvidia/ai-synthetic-video-detector</t>
+        </is>
+      </c>
+      <c r="H154" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I154" s="22" t="n"/>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K154" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L154" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K154" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L154" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M154" s="24" t="inlineStr">
@@ -13228,16 +13226,16 @@
         </is>
       </c>
       <c r="O154" s="18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P154" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q154" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R154" s="18" t="n">
@@ -13250,7 +13248,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13268,12 +13266,12 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H155" s="21" t="inlineStr">
@@ -13308,7 +13306,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
@@ -13330,7 +13328,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13353,7 +13351,7 @@
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H156" s="21" t="inlineStr">
@@ -13410,7 +13408,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13433,7 +13431,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13490,7 +13488,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13508,12 +13506,12 @@
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13548,7 +13546,7 @@
         </is>
       </c>
       <c r="O158" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P158" s="18" t="inlineStr">
         <is>
@@ -13570,7 +13568,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13588,12 +13586,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13628,7 +13626,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
@@ -13650,7 +13648,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13673,7 +13671,7 @@
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13730,7 +13728,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13753,7 +13751,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13810,7 +13808,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13828,12 +13826,12 @@
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13862,13 +13860,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N162" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N162" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O162" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P162" s="18" t="inlineStr">
         <is>
@@ -13877,7 +13875,7 @@
       </c>
       <c r="Q162" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R162" s="18" t="n">
@@ -13890,7 +13888,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13913,7 +13911,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13942,9 +13940,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N163" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N163" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O163" s="2" t="n">
@@ -13957,7 +13955,7 @@
       </c>
       <c r="Q163" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R163" s="2" t="n">
@@ -13970,7 +13968,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13983,7 +13981,7 @@
       </c>
       <c r="E164" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
@@ -13993,7 +13991,7 @@
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14007,9 +14005,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K164" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K164" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L164" s="23" t="inlineStr">
@@ -14028,7 +14026,7 @@
         </is>
       </c>
       <c r="O164" s="18" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
@@ -14037,7 +14035,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14050,7 +14048,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14063,7 +14061,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -14073,7 +14071,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14087,9 +14085,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K165" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K165" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L165" s="23" t="inlineStr">
@@ -14108,7 +14106,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
@@ -14117,7 +14115,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14130,7 +14128,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14153,7 +14151,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14197,7 +14195,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14210,7 +14208,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14233,7 +14231,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14277,7 +14275,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14290,7 +14288,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14313,7 +14311,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14370,7 +14368,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>kimi-k3</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14393,7 +14391,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>moonshotai/kimi-k3</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14450,7 +14448,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>kimi-k3</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14468,12 +14466,12 @@
       </c>
       <c r="F170" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k3</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14508,7 +14506,7 @@
         </is>
       </c>
       <c r="O170" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P170" s="18" t="inlineStr">
         <is>
@@ -14530,7 +14528,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14553,7 +14551,7 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14610,7 +14608,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14633,7 +14631,7 @@
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14677,7 +14675,7 @@
       </c>
       <c r="Q172" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R172" s="18" t="n">
@@ -14690,7 +14688,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14708,12 +14706,12 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14748,7 +14746,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
@@ -14757,7 +14755,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R173" s="2" t="n">
@@ -14770,7 +14768,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14793,7 +14791,7 @@
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14850,7 +14848,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14868,12 +14866,12 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14887,14 +14885,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K175" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L175" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K175" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L175" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M175" s="9" t="inlineStr">
@@ -14908,16 +14906,16 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q175" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R175" s="2" t="n">
@@ -14930,7 +14928,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14943,17 +14941,17 @@
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14972,9 +14970,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L176" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L176" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M176" s="24" t="inlineStr">
@@ -14988,16 +14986,16 @@
         </is>
       </c>
       <c r="O176" s="18" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="P176" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q176" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R176" s="18" t="n">
@@ -15010,7 +15008,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>yi-large</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15023,7 +15021,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
@@ -15033,7 +15031,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>01-ai/yi-large</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15047,9 +15045,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K177" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K177" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L177" s="23" t="inlineStr">
@@ -15068,7 +15066,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
@@ -15077,1496 +15075,1416 @@
       </c>
       <c r="Q177" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R177" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="18" t="n">
-        <v>160</v>
-      </c>
-      <c r="B178" s="19" t="inlineStr">
-        <is>
-          <t>yi-large</t>
-        </is>
-      </c>
-      <c r="C178" s="39" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="41" t="inlineStr">
+        <is>
+          <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>Tier (1-5)</t>
+        </is>
+      </c>
+      <c r="E180" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>Gateway model id</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>Context class</t>
+        </is>
+      </c>
+      <c r="I180" s="1" t="inlineStr">
+        <is>
+          <t>Context (tokens)</t>
+        </is>
+      </c>
+      <c r="J180" s="1" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="K180" s="1" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="L180" s="1" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="M180" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="N180" s="1" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="O180" s="1" t="inlineStr">
+        <is>
+          <t>Speed (0-100)</t>
+        </is>
+      </c>
+      <c r="P180" s="1" t="inlineStr">
+        <is>
+          <t>Free type</t>
+        </is>
+      </c>
+      <c r="Q180" s="1" t="inlineStr">
+        <is>
+          <t>Best for</t>
+        </is>
+      </c>
+      <c r="R180" s="1" t="inlineStr">
+        <is>
+          <t>Gateways in group</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K181" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L181" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M181" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N181" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q181" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B182" s="19" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D182" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E182" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F182" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G182" s="20" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I182" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J182" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K182" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L182" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M182" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N182" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O182" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P182" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q182" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R182" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B183" s="26" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D183" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E183" s="25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F183" s="27" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G183" s="27" t="inlineStr">
+        <is>
+          <t>google/gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H183" s="30" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I183" s="28" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J183" s="25" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K183" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L183" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M183" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N183" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O183" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="P183" s="25" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q183" s="27" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R183" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>90B</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>meta/llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="H184" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I184" s="7" t="n"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M184" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N184" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q184" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B185" s="19" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="C185" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D185" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E185" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F185" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G185" s="20" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I185" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J185" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N185" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P185" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q185" s="20" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R185" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B186" s="26" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="C186" s="32" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D186" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E186" s="25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F186" s="27" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G186" s="27" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="H186" s="42" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
+        </is>
+      </c>
+      <c r="I186" s="28" t="n">
+        <v>32768</v>
+      </c>
+      <c r="J186" s="25" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K186" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L186" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M186" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N186" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="P186" s="25" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q186" s="27" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, fast</t>
+        </is>
+      </c>
+      <c r="R186" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image</t>
+        </is>
+      </c>
+      <c r="C187" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I187" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M187" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q187" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="C188" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D188" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F188" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G188" s="20" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I188" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J188" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M188" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N188" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P188" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q188" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R188" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B189" s="26" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="C189" s="32" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D189" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E189" s="25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F189" s="27" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G189" s="27" t="inlineStr">
+        <is>
+          <t>google/gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="H189" s="30" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I189" s="28" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J189" s="25" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K189" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L189" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M189" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N189" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="P189" s="25" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q189" s="27" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R189" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>neva-22b</t>
+        </is>
+      </c>
+      <c r="C190" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>22B</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>nvidia/neva-22b</t>
+        </is>
+      </c>
+      <c r="H190" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I190" s="7" t="n"/>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M190" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N190" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q190" s="5" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B191" s="19" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="C191" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="D191" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E191" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F191" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G191" s="20" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I191" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J191" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M191" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P191" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q191" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R191" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>llama-3.2-11b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="C192" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>11B</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>meta/llama-3.2-11b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="H192" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="n"/>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M192" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q192" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, fast</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>fuyu-8b</t>
+        </is>
+      </c>
+      <c r="C193" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="D193" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E193" s="18" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="F193" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G193" s="20" t="inlineStr">
+        <is>
+          <t>adept/fuyu-8b</t>
+        </is>
+      </c>
+      <c r="H193" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I193" s="22" t="n"/>
+      <c r="J193" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="P193" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q193" s="20" t="inlineStr">
+        <is>
+          <t>extraction, agent, fast</t>
+        </is>
+      </c>
+      <c r="R193" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>kosmos-2</t>
+        </is>
+      </c>
+      <c r="C194" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D178" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="18" t="inlineStr">
+      <c r="D194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F178" s="20" t="inlineStr">
+      <c r="F194" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G178" s="20" t="inlineStr">
-        <is>
-          <t>01-ai/yi-large</t>
-        </is>
-      </c>
-      <c r="H178" s="21" t="inlineStr">
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>microsoft/kosmos-2</t>
+        </is>
+      </c>
+      <c r="H194" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I178" s="22" t="n"/>
-      <c r="J178" s="18" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K178" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L178" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M178" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N178" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O178" s="18" t="n">
+      <c r="I194" s="7" t="n"/>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P178" s="18" t="inlineStr">
+      <c r="P194" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q178" s="20" t="inlineStr">
+      <c r="Q194" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R178" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="41" t="inlineStr">
-        <is>
-          <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="30" customHeight="1">
-      <c r="A181" s="1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B181" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C181" s="1" t="inlineStr">
-        <is>
-          <t>Intelligence</t>
-        </is>
-      </c>
-      <c r="D181" s="1" t="inlineStr">
-        <is>
-          <t>Tier (1-5)</t>
-        </is>
-      </c>
-      <c r="E181" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F181" s="1" t="inlineStr">
-        <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="G181" s="1" t="inlineStr">
-        <is>
-          <t>Gateway model id</t>
-        </is>
-      </c>
-      <c r="H181" s="1" t="inlineStr">
-        <is>
-          <t>Context class</t>
-        </is>
-      </c>
-      <c r="I181" s="1" t="inlineStr">
-        <is>
-          <t>Context (tokens)</t>
-        </is>
-      </c>
-      <c r="J181" s="1" t="inlineStr">
-        <is>
-          <t>Modality</t>
-        </is>
-      </c>
-      <c r="K181" s="1" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="L181" s="1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="M181" s="1" t="inlineStr">
-        <is>
-          <t>Reasoning</t>
-        </is>
-      </c>
-      <c r="N181" s="1" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
-      </c>
-      <c r="O181" s="1" t="inlineStr">
-        <is>
-          <t>Speed (0-100)</t>
-        </is>
-      </c>
-      <c r="P181" s="1" t="inlineStr">
-        <is>
-          <t>Free type</t>
-        </is>
-      </c>
-      <c r="Q181" s="1" t="inlineStr">
-        <is>
-          <t>Best for</t>
-        </is>
-      </c>
-      <c r="R181" s="1" t="inlineStr">
-        <is>
-          <t>Gateways in group</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="R194" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="C195" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D195" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image</t>
-        </is>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I182" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="F195" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G195" s="20" t="inlineStr">
+        <is>
+          <t>microsoft/phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="H195" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I195" s="22" t="n"/>
+      <c r="J195" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K182" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L182" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M182" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N182" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O182" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P182" s="2" t="inlineStr">
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P195" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q182" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R182" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B183" s="19" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D183" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E183" s="18" t="inlineStr">
+      <c r="Q195" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R195" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>vila</t>
+        </is>
+      </c>
+      <c r="C196" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F183" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G183" s="20" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I183" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J183" s="18" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>nvidia/vila</t>
+        </is>
+      </c>
+      <c r="H196" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M183" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N183" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O183" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P183" s="18" t="inlineStr">
+      <c r="K196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q183" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R183" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B184" s="26" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="C184" s="12" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D184" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E184" s="25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F184" s="27" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G184" s="27" t="inlineStr">
-        <is>
-          <t>google/gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="H184" s="30" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I184" s="28" t="n">
-        <v>65536</v>
-      </c>
-      <c r="J184" s="25" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K184" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L184" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M184" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N184" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="25" t="n">
-        <v>39</v>
-      </c>
-      <c r="P184" s="25" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q184" s="27" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R184" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>90B</t>
-        </is>
-      </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr">
-        <is>
-          <t>meta/llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H185" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I185" s="7" t="n"/>
-      <c r="J185" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="P185" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q185" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R185" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B186" s="19" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="C186" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D186" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E186" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F186" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G186" s="20" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I186" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J186" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N186" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P186" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q186" s="20" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R186" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B187" s="26" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="C187" s="32" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D187" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E187" s="25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F187" s="27" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G187" s="27" t="inlineStr">
-        <is>
-          <t>google/gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="H187" s="42" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
-        </is>
-      </c>
-      <c r="I187" s="28" t="n">
-        <v>32768</v>
-      </c>
-      <c r="J187" s="25" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K187" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L187" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M187" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N187" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="25" t="n">
-        <v>39</v>
-      </c>
-      <c r="P187" s="25" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q187" s="27" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, fast</t>
-        </is>
-      </c>
-      <c r="R187" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="C188" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="H188" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I188" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M188" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N188" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P188" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q188" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R188" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B189" s="19" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="C189" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D189" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E189" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F189" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G189" s="20" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I189" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J189" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M189" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N189" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P189" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q189" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R189" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B190" s="26" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="C190" s="32" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D190" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E190" s="25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F190" s="27" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G190" s="27" t="inlineStr">
-        <is>
-          <t>google/gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="H190" s="30" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I190" s="28" t="n">
-        <v>65536</v>
-      </c>
-      <c r="J190" s="25" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K190" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L190" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M190" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N190" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="25" t="n">
-        <v>39</v>
-      </c>
-      <c r="P190" s="25" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q190" s="27" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R190" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>neva-22b</t>
-        </is>
-      </c>
-      <c r="C191" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>22B</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/neva-22b</t>
-        </is>
-      </c>
-      <c r="H191" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I191" s="7" t="n"/>
-      <c r="J191" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M191" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="P191" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q191" s="5" t="inlineStr">
+      <c r="Q196" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R191" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B192" s="19" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="C192" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D192" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E192" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F192" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G192" s="20" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I192" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J192" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M192" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P192" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q192" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R192" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C193" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>11B</t>
-        </is>
-      </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G193" s="5" t="inlineStr">
-        <is>
-          <t>meta/llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H193" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I193" s="7" t="n"/>
-      <c r="J193" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M193" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="P193" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q193" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, fast</t>
-        </is>
-      </c>
-      <c r="R193" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B194" s="19" t="inlineStr">
-        <is>
-          <t>fuyu-8b</t>
-        </is>
-      </c>
-      <c r="C194" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="D194" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E194" s="18" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="F194" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G194" s="20" t="inlineStr">
-        <is>
-          <t>adept/fuyu-8b</t>
-        </is>
-      </c>
-      <c r="H194" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I194" s="22" t="n"/>
-      <c r="J194" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="18" t="n">
-        <v>45</v>
-      </c>
-      <c r="P194" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q194" s="20" t="inlineStr">
-        <is>
-          <t>extraction, agent, fast</t>
-        </is>
-      </c>
-      <c r="R194" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>kosmos-2</t>
-        </is>
-      </c>
-      <c r="C195" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>microsoft/kosmos-2</t>
-        </is>
-      </c>
-      <c r="H195" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I195" s="7" t="n"/>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="P195" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q195" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R195" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B196" s="19" t="inlineStr">
-        <is>
-          <t>phi-3-vision-128k-instruct</t>
-        </is>
-      </c>
-      <c r="C196" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D196" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E196" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F196" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G196" s="20" t="inlineStr">
-        <is>
-          <t>microsoft/phi-3-vision-128k-instruct</t>
-        </is>
-      </c>
-      <c r="H196" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I196" s="22" t="n"/>
-      <c r="J196" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="P196" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q196" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R196" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>vila</t>
-        </is>
-      </c>
-      <c r="C197" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/vila</t>
-        </is>
-      </c>
-      <c r="H197" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I197" s="7" t="n"/>
-      <c r="J197" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="P197" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q197" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R197" s="2" t="n">
+      <c r="R196" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R178"/>
+  <autoFilter ref="A1:R177"/>
   <mergeCells count="1">
-    <mergeCell ref="A180:R180"/>
+    <mergeCell ref="A179:R179"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O178">
+  <conditionalFormatting sqref="O2:O177">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16802,7 +16720,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-13T14:16:40Z (source: live)</t>
+          <t>Registry updated 2026-10-13T22:48:34Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16720,7 +16720,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-13T22:48:34Z (source: live)</t>
+          <t>Registry updated 2026-10-14T04:58:05Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16720,7 +16720,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-14T04:58:05Z (source: live)</t>
+          <t>Registry updated 2026-10-14T11:57:52Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16720,7 +16720,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-14T11:57:52Z (source: live)</t>
+          <t>Registry updated 2026-10-14T17:15:16Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16720,7 +16720,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-14T17:15:16Z (source: live)</t>
+          <t>Registry updated 2026-10-14T21:44:04Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16720,7 +16720,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-14T21:44:04Z (source: live)</t>
+          <t>Registry updated 2026-10-15T04:45:02Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -14368,7 +14368,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>kimi-k3</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k3</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14426,7 +14426,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="Q171" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R171" s="2" t="n">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14626,12 +14626,12 @@
       </c>
       <c r="F172" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="O172" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P172" s="18" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="Q172" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R172" s="18" t="n">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14786,12 +14786,12 @@
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14805,14 +14805,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K174" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L174" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K174" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L174" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M174" s="24" t="inlineStr">
@@ -14826,16 +14826,16 @@
         </is>
       </c>
       <c r="O174" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P174" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q174" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R174" s="18" t="n">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14861,17 +14861,17 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14890,9 +14890,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L175" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L175" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M175" s="9" t="inlineStr">
@@ -14906,16 +14906,16 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q175" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R175" s="2" t="n">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14965,9 +14965,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K176" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K176" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L176" s="23" t="inlineStr">
@@ -14986,7 +14986,7 @@
         </is>
       </c>
       <c r="O176" s="18" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P176" s="18" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="Q176" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R176" s="18" t="n">
@@ -16720,7 +16720,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-15T04:45:02Z (source: live)</t>
+          <t>Registry updated 2026-10-15T11:34:46Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R196"/>
+  <dimension ref="A1:R198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>gemini-3-pro-image</t>
+          <t>nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -15200,27 +15200,25 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>120B</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>gemini-3-pro-image</t>
-        </is>
-      </c>
-      <c r="H181" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I181" s="7" t="n">
-        <v>1048576</v>
-      </c>
+          <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
+        </is>
+      </c>
+      <c r="H181" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="n"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
@@ -15236,9 +15234,9 @@
           <t>Yes~</t>
         </is>
       </c>
-      <c r="M181" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M181" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="N181" s="9" t="inlineStr">
@@ -15247,7 +15245,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
@@ -15256,7 +15254,7 @@
       </c>
       <c r="Q181" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>reasoning, vision, extraction, agent</t>
         </is>
       </c>
       <c r="R181" s="2" t="n">
@@ -15269,7 +15267,7 @@
       </c>
       <c r="B182" s="19" t="inlineStr">
         <is>
-          <t>gemini-3-pro-image-preview</t>
+          <t>gemini-3-pro-image</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -15292,7 +15290,7 @@
       </c>
       <c r="G182" s="20" t="inlineStr">
         <is>
-          <t>gemini-3-pro-image-preview</t>
+          <t>gemini-3-pro-image</t>
         </is>
       </c>
       <c r="H182" s="6" t="inlineStr">
@@ -15342,169 +15340,171 @@
         </is>
       </c>
       <c r="R182" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I183" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M183" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N183" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q183" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="25" t="n">
+    <row r="184">
+      <c r="A184" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C184" s="12" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E184" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F184" s="13" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G184" s="13" t="inlineStr">
+        <is>
+          <t>google/gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H184" s="30" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I184" s="15" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J184" s="10" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K184" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L184" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M184" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N184" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="P184" s="10" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q184" s="13" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R184" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="B183" s="26" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="C183" s="12" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D183" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E183" s="25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F183" s="27" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G183" s="27" t="inlineStr">
-        <is>
-          <t>google/gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="H183" s="30" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I183" s="28" t="n">
-        <v>65536</v>
-      </c>
-      <c r="J183" s="25" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K183" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L183" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M183" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N183" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O183" s="25" t="n">
-        <v>39</v>
-      </c>
-      <c r="P183" s="25" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q183" s="27" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R183" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>90B</t>
-        </is>
-      </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr">
-        <is>
-          <t>meta/llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H184" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I184" s="7" t="n"/>
-      <c r="J184" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M184" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N184" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="P184" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q184" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R184" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -15513,244 +15513,242 @@
       </c>
       <c r="B185" s="19" t="inlineStr">
         <is>
+          <t>llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D185" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E185" s="18" t="inlineStr">
+        <is>
+          <t>90B</t>
+        </is>
+      </c>
+      <c r="F185" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G185" s="20" t="inlineStr">
+        <is>
+          <t>meta/llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="H185" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I185" s="22" t="n"/>
+      <c r="J185" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N185" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P185" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q185" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R185" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C185" s="31" t="inlineStr">
+      <c r="C186" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D185" s="18" t="n">
+      <c r="D186" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E185" s="18" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F185" s="20" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G185" s="20" t="inlineStr">
+      <c r="G186" s="5" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I185" s="22" t="n">
+      <c r="I186" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J185" s="18" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="18" t="n">
+      <c r="K186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N186" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P185" s="18" t="inlineStr">
+      <c r="P186" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q185" s="20" t="inlineStr">
+      <c r="Q186" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R185" s="18" t="n">
+      <c r="R186" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="25" t="n">
+    <row r="187">
+      <c r="A187" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="C187" s="32" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B186" s="26" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="C186" s="32" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D186" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E186" s="25" t="inlineStr">
+      <c r="E187" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F186" s="27" t="inlineStr">
+      <c r="F187" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G186" s="27" t="inlineStr">
+      <c r="G187" s="13" t="inlineStr">
         <is>
           <t>google/gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H186" s="42" t="inlineStr">
+      <c r="H187" s="42" t="inlineStr">
         <is>
           <t>Medium (8K-32K)</t>
         </is>
       </c>
-      <c r="I186" s="28" t="n">
+      <c r="I187" s="15" t="n">
         <v>32768</v>
       </c>
-      <c r="J186" s="25" t="inlineStr">
+      <c r="J187" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K186" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L186" s="30" t="inlineStr">
+      <c r="K187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L187" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M186" s="30" t="inlineStr">
+      <c r="M187" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N186" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="25" t="n">
+      <c r="N187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P186" s="25" t="inlineStr">
+      <c r="P187" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q186" s="27" t="inlineStr">
+      <c r="Q187" s="13" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, fast</t>
         </is>
       </c>
-      <c r="R186" s="25" t="n">
+      <c r="R187" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="C187" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="H187" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I187" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M187" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N187" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P187" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q187" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R187" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -15759,7 +15757,7 @@
       </c>
       <c r="B188" s="19" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-image-preview</t>
+          <t>gemini-3.1-flash-image</t>
         </is>
       </c>
       <c r="C188" s="31" t="inlineStr">
@@ -15782,7 +15780,7 @@
       </c>
       <c r="G188" s="20" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-image-preview</t>
+          <t>gemini-3.1-flash-image</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
@@ -15832,169 +15830,171 @@
         </is>
       </c>
       <c r="R188" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="C189" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I189" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M189" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N189" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q189" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B189" s="26" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C189" s="32" t="inlineStr">
+      <c r="C190" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D189" s="25" t="n">
+      <c r="D190" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E189" s="25" t="inlineStr">
+      <c r="E190" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F189" s="27" t="inlineStr">
+      <c r="F190" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G189" s="27" t="inlineStr">
+      <c r="G190" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H189" s="30" t="inlineStr">
+      <c r="H190" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I189" s="28" t="n">
+      <c r="I190" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J189" s="25" t="inlineStr">
+      <c r="J190" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K189" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L189" s="30" t="inlineStr">
+      <c r="K190" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L190" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M189" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N189" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="25" t="n">
+      <c r="M190" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N190" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P189" s="25" t="inlineStr">
+      <c r="P190" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q189" s="27" t="inlineStr">
+      <c r="Q190" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R189" s="25" t="n">
+      <c r="R190" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>neva-22b</t>
-        </is>
-      </c>
-      <c r="C190" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>22B</t>
-        </is>
-      </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/neva-22b</t>
-        </is>
-      </c>
-      <c r="H190" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I190" s="7" t="n"/>
-      <c r="J190" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M190" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N190" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="P190" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q190" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R190" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="B191" s="19" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite-image</t>
+          <t>neva-22b</t>
         </is>
       </c>
       <c r="C191" s="35" t="inlineStr">
@@ -16016,27 +16016,25 @@
       </c>
       <c r="E191" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>22B</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G191" s="20" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="H191" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I191" s="22" t="n">
-        <v>1048576</v>
-      </c>
+          <t>nvidia/neva-22b</t>
+        </is>
+      </c>
+      <c r="H191" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I191" s="22" t="n"/>
       <c r="J191" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
@@ -16063,7 +16061,7 @@
         </is>
       </c>
       <c r="O191" s="18" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="P191" s="18" t="inlineStr">
         <is>
@@ -16072,7 +16070,7 @@
       </c>
       <c r="Q191" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R191" s="18" t="n">
@@ -16085,38 +16083,40 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C192" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="C192" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>11B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>meta/llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H192" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I192" s="7" t="n"/>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="n">
+        <v>1048576</v>
+      </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
@@ -16143,7 +16143,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="Q192" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, fast</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R192" s="2" t="n">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="B193" s="19" t="inlineStr">
         <is>
-          <t>fuyu-8b</t>
+          <t>llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
       <c r="C193" s="37" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="E193" s="18" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>11B</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="G193" s="20" t="inlineStr">
         <is>
-          <t>adept/fuyu-8b</t>
+          <t>meta/llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
       <c r="H193" s="21" t="inlineStr">
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="O193" s="18" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P193" s="18" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="Q193" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>vision, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R193" s="18" t="n">
@@ -16245,20 +16245,20 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>kosmos-2</t>
-        </is>
-      </c>
-      <c r="C194" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>fuyu-8b</t>
+        </is>
+      </c>
+      <c r="C194" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>microsoft/kosmos-2</t>
+          <t>adept/fuyu-8b</t>
         </is>
       </c>
       <c r="H194" s="21" t="inlineStr">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="Q194" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R194" s="2" t="n">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="B195" s="19" t="inlineStr">
         <is>
-          <t>phi-3-vision-128k-instruct</t>
+          <t>nemotron-3.5-super-vl</t>
         </is>
       </c>
       <c r="C195" s="39" t="inlineStr">
@@ -16343,38 +16343,40 @@
       </c>
       <c r="F195" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G195" s="20" t="inlineStr">
         <is>
-          <t>microsoft/phi-3-vision-128k-instruct</t>
-        </is>
-      </c>
-      <c r="H195" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I195" s="22" t="n"/>
+          <t>nvidia/nemotron-3.5-super-vl:free</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I195" s="22" t="n">
+        <v>1000000</v>
+      </c>
       <c r="J195" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K195" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L195" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M195" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N195" s="24" t="inlineStr">
@@ -16383,16 +16385,16 @@
         </is>
       </c>
       <c r="O195" s="18" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P195" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q195" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent</t>
+          <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R195" s="18" t="n">
@@ -16405,7 +16407,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>vila</t>
+          <t>kosmos-2</t>
         </is>
       </c>
       <c r="C196" s="39" t="inlineStr">
@@ -16428,7 +16430,7 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>nvidia/vila</t>
+          <t>microsoft/kosmos-2</t>
         </is>
       </c>
       <c r="H196" s="21" t="inlineStr">
@@ -16476,6 +16478,166 @@
         </is>
       </c>
       <c r="R196" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="C197" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D197" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F197" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G197" s="20" t="inlineStr">
+        <is>
+          <t>microsoft/phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="H197" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I197" s="22" t="n"/>
+      <c r="J197" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M197" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N197" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P197" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q197" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R197" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>vila</t>
+        </is>
+      </c>
+      <c r="C198" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>nvidia/vila</t>
+        </is>
+      </c>
+      <c r="H198" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I198" s="7" t="n"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q198" s="5" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16720,7 +16882,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-15T11:34:46Z (source: live)</t>
+          <t>Registry updated 2026-10-15T17:04:47Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16882,7 +16882,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-15T17:04:47Z (source: live)</t>
+          <t>Registry updated 2026-10-15T21:26:29Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16882,7 +16882,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-15T21:26:29Z (source: live)</t>
+          <t>Registry updated 2026-10-16T04:36:20Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16882,7 +16882,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-16T04:36:20Z (source: live)</t>
+          <t>Registry updated 2026-10-16T11:29:13Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16882,7 +16882,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-16T11:29:13Z (source: live)</t>
+          <t>Registry updated 2026-10-16T16:42:45Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R198"/>
+  <dimension ref="A1:R199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>muse-glimmer-30b</t>
+          <t>xing4.0-29b-a4b</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
@@ -5775,38 +5775,40 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>30B</t>
+          <t>29B</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>meta/muse-glimmer-30b</t>
-        </is>
-      </c>
-      <c r="H63" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="n"/>
+          <t>xingchen-agi/xing4.0-29b-a4b:free</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>262144</v>
+      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K63" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L63" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M63" s="9" t="inlineStr">
@@ -5820,16 +5822,16 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R63" s="2" t="n">
@@ -5842,7 +5844,7 @@
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>muse-glimmer-30b</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
@@ -5855,555 +5857,553 @@
       </c>
       <c r="E64" s="18" t="inlineStr">
         <is>
+          <t>30B</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>meta/muse-glimmer-30b</t>
+        </is>
+      </c>
+      <c r="H64" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="n"/>
+      <c r="J64" s="18" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K64" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L64" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M64" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N64" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O64" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="P64" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q64" s="20" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R64" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="C65" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>20B</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>groq</t>
         </is>
       </c>
-      <c r="G64" s="20" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I64" s="22" t="n">
+      <c r="I65" s="7" t="n">
         <v>131072</v>
       </c>
-      <c r="J64" s="18" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K64" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L64" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M64" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N64" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O64" s="18" t="n">
+      <c r="K65" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L65" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M65" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N65" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="P64" s="18" t="inlineStr">
+      <c r="P65" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q64" s="20" t="inlineStr">
+      <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>reasoning, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R64" s="18" t="n">
+      <c r="R65" s="2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="25" t="n">
-        <v>54</v>
-      </c>
-      <c r="B65" s="26" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>gpt-oss-20b</t>
         </is>
       </c>
-      <c r="C65" s="36" t="inlineStr">
+      <c r="C66" s="36" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D65" s="25" t="n">
+      <c r="D66" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>20B</t>
         </is>
       </c>
-      <c r="F65" s="27" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G65" s="27" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b:free</t>
         </is>
       </c>
-      <c r="H65" s="30" t="inlineStr">
+      <c r="H66" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I65" s="28" t="n">
+      <c r="I66" s="15" t="n">
         <v>131072</v>
       </c>
-      <c r="J65" s="25" t="inlineStr">
+      <c r="J66" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K65" s="30" t="inlineStr">
+      <c r="K66" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L65" s="30" t="inlineStr">
+      <c r="L66" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M65" s="30" t="inlineStr">
+      <c r="M66" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N65" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O65" s="25" t="n">
+      <c r="N66" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O66" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P65" s="25" t="inlineStr">
+      <c r="P66" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q65" s="27" t="inlineStr">
+      <c r="Q66" s="13" t="inlineStr">
         <is>
           <t>reasoning, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R65" s="25" t="n">
+      <c r="R66" s="10" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="25" t="n">
-        <v>54</v>
-      </c>
-      <c r="B66" s="26" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>gpt-oss-20b</t>
         </is>
       </c>
-      <c r="C66" s="36" t="inlineStr">
+      <c r="C67" s="36" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D66" s="25" t="n">
+      <c r="D67" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E66" s="25" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>20B</t>
         </is>
       </c>
-      <c r="F66" s="27" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G66" s="27" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="H66" s="14" t="inlineStr">
+      <c r="H67" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I66" s="28" t="n"/>
-      <c r="J66" s="25" t="inlineStr">
+      <c r="I67" s="15" t="n"/>
+      <c r="J67" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K66" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L66" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M66" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N66" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O66" s="25" t="n">
+      <c r="K67" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L67" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N67" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O67" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="P66" s="25" t="inlineStr">
+      <c r="P67" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q66" s="27" t="inlineStr">
+      <c r="Q67" s="13" t="inlineStr">
         <is>
           <t>reasoning, extraction, agent</t>
         </is>
       </c>
-      <c r="R66" s="25" t="n">
+      <c r="R67" s="10" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>gemma-4-26b-a4b-it</t>
         </is>
       </c>
-      <c r="C67" s="35" t="inlineStr">
+      <c r="C68" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D68" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="18" t="inlineStr">
         <is>
           <t>26B</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F68" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G68" s="20" t="inlineStr">
         <is>
           <t>google/gemma-4-26b-a4b-it:free</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I67" s="7" t="n">
+      <c r="I68" s="22" t="n">
         <v>262144</v>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J68" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K67" s="8" t="inlineStr">
+      <c r="K68" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L67" s="8" t="inlineStr">
+      <c r="L68" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M67" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N67" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="n">
+      <c r="M68" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N68" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O68" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="P67" s="2" t="inlineStr">
+      <c r="P68" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q67" s="5" t="inlineStr">
+      <c r="Q68" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R67" s="2" t="n">
+      <c r="R68" s="18" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>gemma-4-26b-a4b-it</t>
         </is>
       </c>
-      <c r="C68" s="36" t="inlineStr">
+      <c r="C69" s="36" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n">
+      <c r="D69" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E69" s="25" t="inlineStr">
         <is>
           <t>26B</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F69" s="27" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G69" s="27" t="inlineStr">
         <is>
           <t>google/gemma-4-26b-a4b-it</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I68" s="15" t="n">
+      <c r="I69" s="28" t="n">
         <v>131072</v>
       </c>
-      <c r="J68" s="10" t="inlineStr">
+      <c r="J69" s="25" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L68" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M68" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N68" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O68" s="10" t="n">
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O69" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="P68" s="10" t="inlineStr">
+      <c r="P69" s="25" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q68" s="13" t="inlineStr">
+      <c r="Q69" s="27" t="inlineStr">
         <is>
           <t>vision, agent, long_doc</t>
         </is>
       </c>
-      <c r="R68" s="10" t="n">
+      <c r="R69" s="25" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>gemma-4-26b-a4b-it</t>
         </is>
       </c>
-      <c r="C69" s="36" t="inlineStr">
+      <c r="C70" s="36" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n">
+      <c r="D70" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="E70" s="25" t="inlineStr">
         <is>
           <t>26B</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
+      <c r="F70" s="27" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="G70" s="27" t="inlineStr">
         <is>
           <t>gemma-4-26b-a4b-it</t>
         </is>
       </c>
-      <c r="H69" s="14" t="inlineStr">
+      <c r="H70" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I69" s="15" t="n"/>
-      <c r="J69" s="10" t="inlineStr">
+      <c r="I70" s="28" t="n"/>
+      <c r="J70" s="25" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K69" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L69" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M69" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N69" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O69" s="10" t="n">
+      <c r="K70" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L70" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M70" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N70" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O70" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="P69" s="10" t="inlineStr">
+      <c r="P70" s="25" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q69" s="13" t="inlineStr">
+      <c r="Q70" s="27" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R69" s="10" t="n">
+      <c r="R70" s="25" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>gemma4-26b</t>
-        </is>
-      </c>
-      <c r="C70" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D70" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E70" s="18" t="inlineStr">
-        <is>
-          <t>26B</t>
-        </is>
-      </c>
-      <c r="F70" s="20" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G70" s="20" t="inlineStr">
-        <is>
-          <t>google/gemma4-26b:free</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I70" s="22" t="n">
-        <v>262144</v>
-      </c>
-      <c r="J70" s="18" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K70" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M70" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N70" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O70" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="P70" s="18" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q70" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc</t>
-        </is>
-      </c>
-      <c r="R70" s="18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>codestral-2508</t>
+          <t>gemma4-26b</t>
         </is>
       </c>
       <c r="C71" s="35" t="inlineStr">
@@ -6425,17 +6425,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>26B</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>codestral-2508</t>
+          <t>google/gemma4-26b:free</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -6444,11 +6444,11 @@
         </is>
       </c>
       <c r="I71" s="7" t="n">
-        <v>256000</v>
+        <v>262144</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K71" s="8" t="inlineStr">
@@ -6466,22 +6466,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N71" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R71" s="2" t="n">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>codestral-latest</t>
+          <t>codestral-2508</t>
         </is>
       </c>
       <c r="C72" s="35" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G72" s="20" t="inlineStr">
         <is>
-          <t>codestral-latest</t>
+          <t>codestral-2508</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>diffusiongemma-26b-a4b-it</t>
+          <t>codestral-latest</t>
         </is>
       </c>
       <c r="C73" s="35" t="inlineStr">
@@ -6589,38 +6589,40 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>26B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>google/diffusiongemma-26b-a4b-it</t>
-        </is>
-      </c>
-      <c r="H73" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="n"/>
+          <t>codestral-latest</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>256000</v>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K73" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L73" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K73" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M73" s="9" t="inlineStr">
@@ -6628,13 +6630,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N73" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6643,7 +6645,7 @@
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R73" s="2" t="n">
@@ -6656,7 +6658,7 @@
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>gemini-3.5-live-translate-preview</t>
+          <t>diffusiongemma-26b-a4b-it</t>
         </is>
       </c>
       <c r="C74" s="35" t="inlineStr">
@@ -6669,30 +6671,28 @@
       </c>
       <c r="E74" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>26B</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G74" s="20" t="inlineStr">
         <is>
-          <t>gemini-3.5-live-translate-preview</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I74" s="22" t="n">
-        <v>1048576</v>
-      </c>
+          <t>google/diffusiongemma-26b-a4b-it</t>
+        </is>
+      </c>
+      <c r="H74" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I74" s="22" t="n"/>
       <c r="J74" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K74" s="23" t="inlineStr">
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="O74" s="18" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="P74" s="18" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="Q74" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R74" s="18" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.8-live</t>
+          <t>gemini-3.5-live-translate-preview</t>
         </is>
       </c>
       <c r="C75" s="35" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.8-live</t>
+          <t>gemini-3.5-live-translate-preview</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>gemini-4-argon</t>
+          <t>gemini-3.8-live</t>
         </is>
       </c>
       <c r="C76" s="35" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="G76" s="20" t="inlineStr">
         <is>
-          <t>gemini-4-argon</t>
+          <t>gemini-3.8-live</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>gemini-nano-banana-2.1</t>
+          <t>gemini-4-argon</t>
         </is>
       </c>
       <c r="C77" s="35" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>gemini-nano-banana-2.1</t>
+          <t>gemini-4-argon</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R77" s="2" t="n">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-preview</t>
+          <t>gemini-nano-banana-2.1</t>
         </is>
       </c>
       <c r="C78" s="35" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="G78" s="20" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-preview</t>
+          <t>gemini-nano-banana-2.1</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="Q78" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R78" s="18" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-streaming-preview</t>
+          <t>gemini-robotics-er-2-preview</t>
         </is>
       </c>
       <c r="C79" s="35" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>gemini-robotics-er-2-streaming-preview</t>
+          <t>gemini-robotics-er-2-preview</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>codestral-22b-instruct-v0.1</t>
+          <t>gemini-robotics-er-2-streaming-preview</t>
         </is>
       </c>
       <c r="C80" s="35" t="inlineStr">
@@ -7161,28 +7161,30 @@
       </c>
       <c r="E80" s="18" t="inlineStr">
         <is>
-          <t>22B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G80" s="20" t="inlineStr">
         <is>
-          <t>mistralai/codestral-22b-instruct-v0.1</t>
-        </is>
-      </c>
-      <c r="H80" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I80" s="22" t="n"/>
+          <t>gemini-robotics-er-2-streaming-preview</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="n">
+        <v>1048576</v>
+      </c>
       <c r="J80" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K80" s="23" t="inlineStr">
@@ -7200,13 +7202,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N80" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N80" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O80" s="18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="P80" s="18" t="inlineStr">
         <is>
@@ -7215,7 +7217,7 @@
       </c>
       <c r="Q80" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R80" s="18" t="n">
@@ -7228,7 +7230,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite</t>
+          <t>codestral-22b-instruct-v0.1</t>
         </is>
       </c>
       <c r="C81" s="35" t="inlineStr">
@@ -7241,30 +7243,28 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>22B</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="n">
-        <v>1048576</v>
-      </c>
+          <t>mistralai/codestral-22b-instruct-v0.1</t>
+        </is>
+      </c>
+      <c r="H81" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="n"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K81" s="23" t="inlineStr">
@@ -7277,18 +7277,18 @@
           <t>Yes~</t>
         </is>
       </c>
-      <c r="M81" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N81" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M81" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N81" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+          <t>coding, extraction, agent</t>
         </is>
       </c>
       <c r="R81" s="2" t="n">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>starcoder2-15b</t>
+          <t>gemini-2.5-flash-lite</t>
         </is>
       </c>
       <c r="C82" s="35" t="inlineStr">
@@ -7323,28 +7323,30 @@
       </c>
       <c r="E82" s="18" t="inlineStr">
         <is>
-          <t>15B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G82" s="20" t="inlineStr">
         <is>
-          <t>bigcode/starcoder2-15b</t>
-        </is>
-      </c>
-      <c r="H82" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I82" s="22" t="n"/>
+          <t>gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="n">
+        <v>1048576</v>
+      </c>
       <c r="J82" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K82" s="23" t="inlineStr">
@@ -7357,9 +7359,9 @@
           <t>Yes~</t>
         </is>
       </c>
-      <c r="M82" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M82" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="N82" s="24" t="inlineStr">
@@ -7368,7 +7370,7 @@
         </is>
       </c>
       <c r="O82" s="18" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="P82" s="18" t="inlineStr">
         <is>
@@ -7377,7 +7379,7 @@
       </c>
       <c r="Q82" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R82" s="18" t="n">
@@ -7390,7 +7392,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>ministral-14b-2512</t>
+          <t>starcoder2-15b</t>
         </is>
       </c>
       <c r="C83" s="35" t="inlineStr">
@@ -7403,40 +7405,38 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>15B</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>ministral-14b-2512</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="n">
-        <v>262144</v>
-      </c>
+          <t>bigcode/starcoder2-15b</t>
+        </is>
+      </c>
+      <c r="H83" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="n"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K83" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L83" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K83" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L83" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M83" s="9" t="inlineStr">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R83" s="2" t="n">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="B84" s="19" t="inlineStr">
         <is>
-          <t>ministral-14b-latest</t>
+          <t>ministral-14b-2512</t>
         </is>
       </c>
       <c r="C84" s="35" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="G84" s="20" t="inlineStr">
         <is>
-          <t>ministral-14b-latest</t>
+          <t>ministral-14b-2512</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>mistral-small-2603</t>
+          <t>ministral-14b-latest</t>
         </is>
       </c>
       <c r="C85" s="35" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>mistral-small-2603</t>
+          <t>ministral-14b-latest</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>mistral-small-latest</t>
+          <t>mistral-small-2603</t>
         </is>
       </c>
       <c r="C86" s="35" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G86" s="20" t="inlineStr">
         <is>
-          <t>mistral-small-latest</t>
+          <t>mistral-small-2603</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>mistral-small-latest</t>
         </is>
       </c>
       <c r="C87" s="35" t="inlineStr">
@@ -7731,38 +7731,40 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>12B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>google/gemma-3-12b-it</t>
-        </is>
-      </c>
-      <c r="H87" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="n"/>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>262144</v>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K87" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L87" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M87" s="9" t="inlineStr">
@@ -7776,7 +7778,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
@@ -7785,7 +7787,7 @@
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, fast</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R87" s="2" t="n">
@@ -7798,7 +7800,7 @@
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>mistral-nemo-12b-instruct</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="C88" s="35" t="inlineStr">
@@ -7821,7 +7823,7 @@
       </c>
       <c r="G88" s="20" t="inlineStr">
         <is>
-          <t>nv-mistralai/mistral-nemo-12b-instruct</t>
+          <t>google/gemma-3-12b-it</t>
         </is>
       </c>
       <c r="H88" s="21" t="inlineStr">
@@ -7832,7 +7834,7 @@
       <c r="I88" s="22" t="n"/>
       <c r="J88" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K88" s="23" t="inlineStr">
@@ -7865,7 +7867,7 @@
       </c>
       <c r="Q88" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>vision, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R88" s="18" t="n">
@@ -7878,7 +7880,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite</t>
+          <t>mistral-nemo-12b-instruct</t>
         </is>
       </c>
       <c r="C89" s="35" t="inlineStr">
@@ -7891,30 +7893,28 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>12B</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="n">
-        <v>1048576</v>
-      </c>
+          <t>nv-mistralai/mistral-nemo-12b-instruct</t>
+        </is>
+      </c>
+      <c r="H89" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="n"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K89" s="23" t="inlineStr">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R89" s="2" t="n">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite-preview</t>
+          <t>gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="C90" s="35" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="G90" s="20" t="inlineStr">
         <is>
-          <t>gemini-3.1-flash-lite-preview</t>
+          <t>gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite</t>
+          <t>gemini-3.1-flash-lite-preview</t>
         </is>
       </c>
       <c r="C91" s="35" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash-lite</t>
+          <t>gemini-3.1-flash-lite-preview</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>gemini-flash-lite-latest</t>
+          <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C92" s="35" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="G92" s="20" t="inlineStr">
         <is>
-          <t>gemini-flash-lite-latest</t>
+          <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
@@ -8206,30 +8206,30 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>ministral-8b-2512</t>
-        </is>
-      </c>
-      <c r="C93" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
+          <t>gemini-flash-lite-latest</t>
+        </is>
+      </c>
+      <c r="C93" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>ministral-8b-2512</t>
+          <t>gemini-flash-lite-latest</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -8238,21 +8238,21 @@
         </is>
       </c>
       <c r="I93" s="7" t="n">
-        <v>262144</v>
+        <v>1048576</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K93" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K93" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L93" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M93" s="9" t="inlineStr">
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B94" s="19" t="inlineStr">
         <is>
-          <t>ministral-8b-latest</t>
+          <t>ministral-8b-2512</t>
         </is>
       </c>
       <c r="C94" s="37" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G94" s="20" t="inlineStr">
         <is>
-          <t>ministral-8b-latest</t>
+          <t>ministral-8b-2512</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>llama3.1-8b</t>
+          <t>ministral-8b-latest</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
@@ -8388,35 +8388,35 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>cerebras</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>llama3.1-8b</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>ministral-8b-latest</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I95" s="7" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K95" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L95" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R95" s="2" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="B96" s="19" t="inlineStr">
         <is>
-          <t>cosmos-reason2-8b</t>
+          <t>llama3.1-8b</t>
         </is>
       </c>
       <c r="C96" s="37" t="inlineStr">
@@ -8470,20 +8470,22 @@
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>cerebras</t>
         </is>
       </c>
       <c r="G96" s="20" t="inlineStr">
         <is>
-          <t>nvidia/cosmos-reason2-8b</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I96" s="22" t="n"/>
+          <t>llama3.1-8b</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>131072</v>
+      </c>
       <c r="J96" s="18" t="inlineStr">
         <is>
           <t>Text</t>
@@ -8510,7 +8512,7 @@
         </is>
       </c>
       <c r="O96" s="18" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="P96" s="18" t="inlineStr">
         <is>
@@ -8519,7 +8521,7 @@
       </c>
       <c r="Q96" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R96" s="18" t="n">
@@ -8532,7 +8534,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>granite-3.0-8b-instruct</t>
+          <t>cosmos-reason2-8b</t>
         </is>
       </c>
       <c r="C97" s="37" t="inlineStr">
@@ -8555,7 +8557,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>ibm/granite-3.0-8b-instruct</t>
+          <t>nvidia/cosmos-reason2-8b</t>
         </is>
       </c>
       <c r="H97" s="21" t="inlineStr">
@@ -8612,7 +8614,7 @@
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>granite-8b-code-instruct</t>
+          <t>granite-3.0-8b-instruct</t>
         </is>
       </c>
       <c r="C98" s="37" t="inlineStr">
@@ -8635,7 +8637,7 @@
       </c>
       <c r="G98" s="20" t="inlineStr">
         <is>
-          <t>ibm/granite-8b-code-instruct</t>
+          <t>ibm/granite-3.0-8b-instruct</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
@@ -8664,9 +8666,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N98" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N98" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O98" s="18" t="n">
@@ -8679,7 +8681,7 @@
       </c>
       <c r="Q98" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R98" s="18" t="n">
@@ -8692,7 +8694,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>mistral-nemo-minitron-8b-8k-instruct</t>
+          <t>granite-8b-code-instruct</t>
         </is>
       </c>
       <c r="C99" s="37" t="inlineStr">
@@ -8715,7 +8717,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>nvidia/mistral-nemo-minitron-8b-8k-instruct</t>
+          <t>ibm/granite-8b-code-instruct</t>
         </is>
       </c>
       <c r="H99" s="21" t="inlineStr">
@@ -8744,9 +8746,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N99" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N99" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O99" s="2" t="n">
@@ -8759,7 +8761,7 @@
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R99" s="2" t="n">
@@ -8772,7 +8774,7 @@
       </c>
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>allam-2-7b</t>
+          <t>mistral-nemo-minitron-8b-8k-instruct</t>
         </is>
       </c>
       <c r="C100" s="37" t="inlineStr">
@@ -8785,27 +8787,25 @@
       </c>
       <c r="E100" s="18" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
         <is>
-          <t>groq</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G100" s="20" t="inlineStr">
         <is>
-          <t>allam-2-7b</t>
-        </is>
-      </c>
-      <c r="H100" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
-        </is>
-      </c>
-      <c r="I100" s="22" t="n">
-        <v>4096</v>
-      </c>
+          <t>nvidia/mistral-nemo-minitron-8b-8k-instruct</t>
+        </is>
+      </c>
+      <c r="H100" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I100" s="22" t="n"/>
       <c r="J100" s="18" t="inlineStr">
         <is>
           <t>Text</t>
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="O100" s="18" t="n">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="P100" s="18" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>codegemma-1.1-7b</t>
+          <t>allam-2-7b</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
@@ -8872,20 +8872,22 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>groq</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>google/codegemma-1.1-7b</t>
-        </is>
-      </c>
-      <c r="H101" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="n"/>
+          <t>allam-2-7b</t>
+        </is>
+      </c>
+      <c r="H101" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>4096</v>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>Text</t>
@@ -8912,7 +8914,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
@@ -8934,7 +8936,7 @@
       </c>
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>codegemma-7b</t>
+          <t>codegemma-1.1-7b</t>
         </is>
       </c>
       <c r="C102" s="37" t="inlineStr">
@@ -8957,7 +8959,7 @@
       </c>
       <c r="G102" s="20" t="inlineStr">
         <is>
-          <t>google/codegemma-7b</t>
+          <t>google/codegemma-1.1-7b</t>
         </is>
       </c>
       <c r="H102" s="21" t="inlineStr">
@@ -9014,7 +9016,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>mistral-7b-instruct-v0.3</t>
+          <t>codegemma-7b</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
@@ -9037,7 +9039,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>mistralai/mistral-7b-instruct-v0.3</t>
+          <t>google/codegemma-7b</t>
         </is>
       </c>
       <c r="H103" s="21" t="inlineStr">
@@ -9094,7 +9096,7 @@
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>sea-lion-7b-instruct</t>
+          <t>mistral-7b-instruct-v0.3</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
@@ -9117,7 +9119,7 @@
       </c>
       <c r="G104" s="20" t="inlineStr">
         <is>
-          <t>aisingapore/sea-lion-7b-instruct</t>
+          <t>mistralai/mistral-7b-instruct-v0.3</t>
         </is>
       </c>
       <c r="H104" s="21" t="inlineStr">
@@ -9174,7 +9176,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>zamba2-7b-instruct</t>
+          <t>sea-lion-7b-instruct</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
@@ -9197,7 +9199,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>zyphra/zamba2-7b-instruct</t>
+          <t>aisingapore/sea-lion-7b-instruct</t>
         </is>
       </c>
       <c r="H105" s="21" t="inlineStr">
@@ -9254,7 +9256,7 @@
       </c>
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>deepseek-coder-6.7b-instruct</t>
+          <t>zamba2-7b-instruct</t>
         </is>
       </c>
       <c r="C106" s="37" t="inlineStr">
@@ -9267,7 +9269,7 @@
       </c>
       <c r="E106" s="18" t="inlineStr">
         <is>
-          <t>6.7B</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -9277,7 +9279,7 @@
       </c>
       <c r="G106" s="20" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-coder-6.7b-instruct</t>
+          <t>zyphra/zamba2-7b-instruct</t>
         </is>
       </c>
       <c r="H106" s="21" t="inlineStr">
@@ -9291,9 +9293,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K106" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K106" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L106" s="23" t="inlineStr">
@@ -9306,9 +9308,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N106" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N106" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O106" s="18" t="n">
@@ -9321,7 +9323,7 @@
       </c>
       <c r="Q106" s="20" t="inlineStr">
         <is>
-          <t>coding, fast</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R106" s="18" t="n">
@@ -9334,7 +9336,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>deepseek-coder-6.7b-instruct</t>
         </is>
       </c>
       <c r="C107" s="37" t="inlineStr">
@@ -9347,7 +9349,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>4B</t>
+          <t>6.7B</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -9357,7 +9359,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>google/gemma-3-4b-it</t>
+          <t>deepseek-ai/deepseek-coder-6.7b-instruct</t>
         </is>
       </c>
       <c r="H107" s="21" t="inlineStr">
@@ -9368,7 +9370,7 @@
       <c r="I107" s="7" t="n"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr">
@@ -9386,13 +9388,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N107" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N107" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
@@ -9401,7 +9403,7 @@
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>vision, fast</t>
+          <t>coding, fast</t>
         </is>
       </c>
       <c r="R107" s="2" t="n">
@@ -9414,7 +9416,7 @@
       </c>
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>riva-translate-4b-instruct</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C108" s="37" t="inlineStr">
@@ -9437,7 +9439,7 @@
       </c>
       <c r="G108" s="20" t="inlineStr">
         <is>
-          <t>nvidia/riva-translate-4b-instruct</t>
+          <t>google/gemma-3-4b-it</t>
         </is>
       </c>
       <c r="H108" s="21" t="inlineStr">
@@ -9448,7 +9450,7 @@
       <c r="I108" s="22" t="n"/>
       <c r="J108" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K108" s="24" t="inlineStr">
@@ -9481,7 +9483,7 @@
       </c>
       <c r="Q108" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>vision, fast</t>
         </is>
       </c>
       <c r="R108" s="18" t="n">
@@ -9494,7 +9496,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>riva-translate-4b-instruct-v2</t>
+          <t>riva-translate-4b-instruct</t>
         </is>
       </c>
       <c r="C109" s="37" t="inlineStr">
@@ -9517,7 +9519,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>nvidia/riva-translate-4b-instruct-v2</t>
+          <t>nvidia/riva-translate-4b-instruct</t>
         </is>
       </c>
       <c r="H109" s="21" t="inlineStr">
@@ -9574,53 +9576,51 @@
       </c>
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>ministral-3b-2512</t>
-        </is>
-      </c>
-      <c r="C110" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
+          <t>riva-translate-4b-instruct-v2</t>
+        </is>
+      </c>
+      <c r="C110" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
         </is>
       </c>
       <c r="D110" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="18" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G110" s="20" t="inlineStr">
         <is>
-          <t>ministral-3b-2512</t>
-        </is>
-      </c>
-      <c r="H110" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I110" s="22" t="n">
-        <v>131072</v>
-      </c>
+          <t>nvidia/riva-translate-4b-instruct-v2</t>
+        </is>
+      </c>
+      <c r="H110" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I110" s="22" t="n"/>
       <c r="J110" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K110" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L110" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K110" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L110" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M110" s="24" t="inlineStr">
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="O110" s="18" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="P110" s="18" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="Q110" s="20" t="inlineStr">
         <is>
-          <t>vision, long_doc, fast</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R110" s="18" t="n">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>ministral-3b-latest</t>
+          <t>ministral-3b-2512</t>
         </is>
       </c>
       <c r="C111" s="39" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>ministral-3b-latest</t>
+          <t>ministral-3b-2512</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>granite-3.0-3b-a800m-instruct</t>
+          <t>ministral-3b-latest</t>
         </is>
       </c>
       <c r="C112" s="39" t="inlineStr">
@@ -9756,33 +9756,35 @@
       </c>
       <c r="F112" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G112" s="20" t="inlineStr">
         <is>
-          <t>ibm/granite-3.0-3b-a800m-instruct</t>
-        </is>
-      </c>
-      <c r="H112" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I112" s="22" t="n"/>
+          <t>ministral-3b-latest</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>131072</v>
+      </c>
       <c r="J112" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K112" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L112" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K112" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M112" s="24" t="inlineStr">
@@ -9796,7 +9798,7 @@
         </is>
       </c>
       <c r="O112" s="18" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="P112" s="18" t="inlineStr">
         <is>
@@ -9805,7 +9807,7 @@
       </c>
       <c r="Q112" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>vision, long_doc, fast</t>
         </is>
       </c>
       <c r="R112" s="18" t="n">
@@ -9818,7 +9820,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>inkling</t>
+          <t>granite-3.0-3b-a800m-instruct</t>
         </is>
       </c>
       <c r="C113" s="39" t="inlineStr">
@@ -9831,45 +9833,43 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>thinkingmachines/inkling:free</t>
-        </is>
-      </c>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I113" s="7" t="n">
-        <v>1048576</v>
-      </c>
+          <t>ibm/granite-3.0-3b-a800m-instruct</t>
+        </is>
+      </c>
+      <c r="H113" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I113" s="7" t="n"/>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K113" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L113" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M113" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K113" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L113" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M113" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N113" s="9" t="inlineStr">
@@ -9878,16 +9878,16 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>reasoning, vision, agent, long_doc</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R113" s="2" t="n">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B114" s="19" t="inlineStr">
         <is>
-          <t>inkling-small</t>
+          <t>inkling</t>
         </is>
       </c>
       <c r="C114" s="39" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="G114" s="20" t="inlineStr">
         <is>
-          <t>thinkingmachines/inkling-small:free</t>
+          <t>thinkingmachines/inkling:free</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="Q114" s="20" t="inlineStr">
         <is>
-          <t>reasoning, vision, agent, long_doc, fast</t>
+          <t>reasoning, vision, agent, long_doc</t>
         </is>
       </c>
       <c r="R114" s="18" t="n">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>nemotron-3.5-lightning</t>
+          <t>inkling-small</t>
         </is>
       </c>
       <c r="C115" s="39" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-3.5-lightning:free</t>
+          <t>thinkingmachines/inkling-small:free</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
@@ -10014,11 +10014,11 @@
         </is>
       </c>
       <c r="I115" s="7" t="n">
-        <v>1000000</v>
+        <v>1048576</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K115" s="8" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Q115" s="5" t="inlineStr">
         <is>
-          <t>reasoning, agent, long_doc</t>
+          <t>reasoning, vision, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R115" s="2" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="B116" s="19" t="inlineStr">
         <is>
-          <t>magistral-medium-latest</t>
+          <t>nemotron-3.5-lightning</t>
         </is>
       </c>
       <c r="C116" s="39" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="F116" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G116" s="20" t="inlineStr">
         <is>
-          <t>magistral-medium-latest</t>
+          <t>nvidia/nemotron-3.5-lightning:free</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -10096,11 +10096,11 @@
         </is>
       </c>
       <c r="I116" s="22" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="J116" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K116" s="8" t="inlineStr">
@@ -10108,32 +10108,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L116" s="8" t="inlineStr">
+      <c r="L116" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M116" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M116" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N116" s="24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="O116" s="18" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P116" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q116" s="20" t="inlineStr">
         <is>
-          <t>reasoning, vision, extraction, agent, long_doc</t>
+          <t>reasoning, agent, long_doc</t>
         </is>
       </c>
       <c r="R116" s="18" t="n">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>magistral-small-latest</t>
+          <t>magistral-medium-latest</t>
         </is>
       </c>
       <c r="C117" s="39" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>magistral-small-latest</t>
+          <t>magistral-medium-latest</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
-          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+          <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R117" s="2" t="n">
@@ -10228,240 +10228,242 @@
       </c>
       <c r="B118" s="19" t="inlineStr">
         <is>
+          <t>magistral-small-latest</t>
+        </is>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F118" s="20" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="G118" s="20" t="inlineStr">
+        <is>
+          <t>magistral-small-latest</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I118" s="22" t="n">
+        <v>262144</v>
+      </c>
+      <c r="J118" s="18" t="inlineStr">
+        <is>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K118" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N118" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O118" s="18" t="n">
+        <v>44</v>
+      </c>
+      <c r="P118" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q118" s="20" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R118" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
           <t>nemotron-3.5-content-safety</t>
         </is>
       </c>
-      <c r="C118" s="39" t="inlineStr">
+      <c r="C119" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D118" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="18" t="inlineStr">
+      <c r="D119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F118" s="20" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G118" s="20" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-content-safety:free</t>
         </is>
       </c>
-      <c r="H118" s="8" t="inlineStr">
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I118" s="22" t="n">
+      <c r="I119" s="7" t="n">
         <v>128000</v>
       </c>
-      <c r="J118" s="18" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K118" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L118" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M118" s="8" t="inlineStr">
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N118" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O118" s="18" t="n">
+      <c r="N119" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="P118" s="18" t="inlineStr">
+      <c r="P119" s="2" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q118" s="20" t="inlineStr">
+      <c r="Q119" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, long_doc</t>
         </is>
       </c>
-      <c r="R118" s="18" t="n">
+      <c r="R119" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="25" t="n">
-        <v>104</v>
-      </c>
-      <c r="B119" s="26" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>nemotron-3.5-content-safety</t>
         </is>
       </c>
-      <c r="C119" s="40" t="inlineStr">
+      <c r="C120" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D119" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="25" t="inlineStr">
+      <c r="D120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F119" s="27" t="inlineStr">
+      <c r="F120" s="13" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G119" s="27" t="inlineStr">
+      <c r="G120" s="13" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-content-safety</t>
         </is>
       </c>
-      <c r="H119" s="14" t="inlineStr">
+      <c r="H120" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I119" s="28" t="n"/>
-      <c r="J119" s="25" t="inlineStr">
+      <c r="I120" s="15" t="n"/>
+      <c r="J120" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K119" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L119" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M119" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N119" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O119" s="25" t="n">
+      <c r="K120" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L120" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M120" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N120" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O120" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="P119" s="25" t="inlineStr">
+      <c r="P120" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q119" s="27" t="inlineStr">
+      <c r="Q120" s="13" t="inlineStr">
         <is>
           <t>reasoning, extraction, agent</t>
         </is>
       </c>
-      <c r="R119" s="25" t="n">
+      <c r="R120" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>nemotron-parse</t>
-        </is>
-      </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/nemotron-parse</t>
-        </is>
-      </c>
-      <c r="H120" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I120" s="7" t="n"/>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K120" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L120" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M120" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N120" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O120" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="P120" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q120" s="5" t="inlineStr">
-        <is>
-          <t>reasoning, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R120" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -10470,7 +10472,7 @@
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>nemotron-parse-2.0</t>
+          <t>nemotron-parse</t>
         </is>
       </c>
       <c r="C121" s="39" t="inlineStr">
@@ -10493,7 +10495,7 @@
       </c>
       <c r="G121" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse-2.0</t>
+          <t>nvidia/nemotron-parse</t>
         </is>
       </c>
       <c r="H121" s="21" t="inlineStr">
@@ -10550,7 +10552,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>lfm-2.5-2.6b</t>
+          <t>nemotron-parse-2.0</t>
         </is>
       </c>
       <c r="C122" s="39" t="inlineStr">
@@ -10563,45 +10565,43 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>2.6B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>liquid/lfm-2.5-2.6b:free</t>
-        </is>
-      </c>
-      <c r="H122" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I122" s="7" t="n">
-        <v>65536</v>
-      </c>
+          <t>nvidia/nemotron-parse-2.0</t>
+        </is>
+      </c>
+      <c r="H122" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="n"/>
       <c r="J122" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K122" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L122" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M122" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K122" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L122" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M122" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="N122" s="9" t="inlineStr">
@@ -10610,16 +10610,16 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q122" s="5" t="inlineStr">
         <is>
-          <t>long_doc, fast</t>
+          <t>reasoning, extraction, agent</t>
         </is>
       </c>
       <c r="R122" s="2" t="n">
@@ -10632,404 +10632,404 @@
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
+          <t>lfm-2.5-2.6b</t>
+        </is>
+      </c>
+      <c r="C123" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D123" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="18" t="inlineStr">
+        <is>
+          <t>2.6B</t>
+        </is>
+      </c>
+      <c r="F123" s="20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G123" s="20" t="inlineStr">
+        <is>
+          <t>liquid/lfm-2.5-2.6b:free</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I123" s="22" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J123" s="18" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K123" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M123" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N123" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O123" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="P123" s="18" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q123" s="20" t="inlineStr">
+        <is>
+          <t>long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R123" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C123" s="39" t="inlineStr">
+      <c r="C124" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D123" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="18" t="inlineStr">
+      <c r="D124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F123" s="20" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G123" s="20" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>google/lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="H124" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I123" s="22" t="n">
+      <c r="I124" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J123" s="18" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K123" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
+      <c r="K124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M123" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N123" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O123" s="18" t="n">
+      <c r="M124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="P123" s="18" t="inlineStr">
+      <c r="P124" s="2" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q123" s="20" t="inlineStr">
+      <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R123" s="18" t="n">
+      <c r="R124" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="25" t="n">
-        <v>108</v>
-      </c>
-      <c r="B124" s="26" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C124" s="40" t="inlineStr">
+      <c r="C125" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D124" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="25" t="inlineStr">
+      <c r="D125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F124" s="27" t="inlineStr">
+      <c r="F125" s="13" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G124" s="27" t="inlineStr">
+      <c r="G125" s="13" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H124" s="14" t="inlineStr">
+      <c r="H125" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I124" s="28" t="n"/>
-      <c r="J124" s="25" t="inlineStr">
+      <c r="I125" s="15" t="n"/>
+      <c r="J125" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K124" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L124" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M124" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N124" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O124" s="25" t="n">
+      <c r="K125" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L125" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M125" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O125" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="P124" s="25" t="inlineStr">
+      <c r="P125" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q124" s="27" t="inlineStr">
+      <c r="Q125" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R124" s="25" t="n">
+      <c r="R125" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C125" s="39" t="inlineStr">
+      <c r="C126" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="D126" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
+      <c r="F126" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G126" s="20" t="inlineStr">
         <is>
           <t>google/lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="H126" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I125" s="7" t="n">
+      <c r="I126" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="J126" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K125" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L125" s="8" t="inlineStr">
+      <c r="K126" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M125" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N125" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O125" s="2" t="n">
+      <c r="M126" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O126" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P125" s="2" t="inlineStr">
+      <c r="P126" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q125" s="5" t="inlineStr">
+      <c r="Q126" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R125" s="2" t="n">
+      <c r="R126" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="10" t="n">
-        <v>109</v>
-      </c>
-      <c r="B126" s="11" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="B127" s="26" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C126" s="40" t="inlineStr">
+      <c r="C127" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D126" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="10" t="inlineStr">
+      <c r="D127" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F126" s="13" t="inlineStr">
+      <c r="F127" s="27" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G126" s="13" t="inlineStr">
+      <c r="G127" s="27" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H126" s="14" t="inlineStr">
+      <c r="H127" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I126" s="15" t="n"/>
-      <c r="J126" s="10" t="inlineStr">
+      <c r="I127" s="28" t="n"/>
+      <c r="J127" s="25" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K126" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L126" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M126" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N126" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O126" s="10" t="n">
+      <c r="K127" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L127" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M127" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N127" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O127" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="P126" s="10" t="inlineStr">
+      <c r="P127" s="25" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q126" s="13" t="inlineStr">
+      <c r="Q127" s="27" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R126" s="10" t="n">
+      <c r="R127" s="25" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="18" t="n">
-        <v>110</v>
-      </c>
-      <c r="B127" s="19" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C127" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D127" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F127" s="20" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G127" s="20" t="inlineStr">
-        <is>
-          <t>fastrouter/auto</t>
-        </is>
-      </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="J127" s="18" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K127" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L127" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M127" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N127" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O127" s="18" t="n">
-        <v>39</v>
-      </c>
-      <c r="P127" s="18" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q127" s="20" t="inlineStr">
-        <is>
-          <t>vision, long_doc</t>
-        </is>
-      </c>
-      <c r="R127" s="18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>dots-3-note-preview</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C128" s="39" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>dots-studio/dots-3-note-preview:free</t>
+          <t>fastrouter/auto</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -11070,21 +11070,21 @@
         </is>
       </c>
       <c r="I128" s="7" t="n">
-        <v>512000</v>
+        <v>1000000</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K128" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L128" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M128" s="9" t="inlineStr">
@@ -11098,7 +11098,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="Q128" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R128" s="2" t="n">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>wan-v2-6</t>
+          <t>dots-3-note-preview</t>
         </is>
       </c>
       <c r="C129" s="39" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-6</t>
+          <t>dots-studio/dots-3-note-preview:free</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -11152,21 +11152,21 @@
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>400000</v>
+        <v>512000</v>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K129" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L129" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K129" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M129" s="24" t="inlineStr">
@@ -11180,7 +11180,7 @@
         </is>
       </c>
       <c r="O129" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P129" s="18" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Q129" s="20" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>wan-v2-6</t>
         </is>
       </c>
       <c r="C130" s="39" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>wanx/wan-v2-6</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>262144</v>
+        <v>400000</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K130" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M130" s="9" t="inlineStr">
@@ -11262,16 +11262,16 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R130" s="2" t="n">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="C131" s="39" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>laguna-s-2.1</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="C132" s="39" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>poolside/laguna-s-2.1:free</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
@@ -11410,9 +11410,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L132" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M132" s="9" t="inlineStr">
@@ -11426,16 +11426,16 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>laguna-xs-2.1</t>
+          <t>laguna-s-2.1</t>
         </is>
       </c>
       <c r="C133" s="39" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>poolside/laguna-xs-2.1:free</t>
+          <t>poolside/laguna-s-2.1:free</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -11521,169 +11521,169 @@
         </is>
       </c>
       <c r="R133" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="C134" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>poolside/laguna-xs-2.1:free</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="n">
+        <v>262144</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K134" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L134" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M134" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N134" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q134" s="5" t="inlineStr">
+        <is>
+          <t>agent, long_doc</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="25" t="n">
-        <v>116</v>
-      </c>
-      <c r="B134" s="26" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
         <is>
           <t>laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="C134" s="40" t="inlineStr">
+      <c r="C135" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D134" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="25" t="inlineStr">
+      <c r="D135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F134" s="27" t="inlineStr">
+      <c r="F135" s="13" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G134" s="27" t="inlineStr">
+      <c r="G135" s="13" t="inlineStr">
         <is>
           <t>poolside/laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="H134" s="14" t="inlineStr">
+      <c r="H135" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I134" s="28" t="n"/>
-      <c r="J134" s="25" t="inlineStr">
+      <c r="I135" s="15" t="n"/>
+      <c r="J135" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K134" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L134" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M134" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N134" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O134" s="25" t="n">
+      <c r="K135" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L135" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M135" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N135" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O135" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="P134" s="25" t="inlineStr">
+      <c r="P135" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q134" s="27" t="inlineStr">
+      <c r="Q135" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R134" s="25" t="n">
+      <c r="R135" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="C135" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>mistral</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I135" s="7" t="n">
-        <v>262144</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K135" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L135" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M135" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N135" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O135" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="P135" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q135" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R135" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="B136" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="C136" s="39" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="G136" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="Q136" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R136" s="18" t="n">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C137" s="39" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11888,11 +11888,11 @@
         </is>
       </c>
       <c r="I138" s="22" t="n">
-        <v>256000</v>
+        <v>262144</v>
       </c>
       <c r="J138" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K138" s="8" t="inlineStr">
@@ -11910,9 +11910,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N138" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N138" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O138" s="18" t="n">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="Q138" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R138" s="18" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12038,12 +12038,12 @@
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12064,9 +12064,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L140" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L140" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M140" s="24" t="inlineStr">
@@ -12080,16 +12080,16 @@
         </is>
       </c>
       <c r="O140" s="18" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P140" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q140" s="20" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R140" s="18" t="n">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12125,20 +12125,20 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
-        </is>
-      </c>
-      <c r="H141" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>cohere/north-mini-code:free</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I141" s="7" t="n">
-        <v>200000</v>
+        <v>256000</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K141" s="8" t="inlineStr">
@@ -12146,19 +12146,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L141" s="8" t="inlineStr">
+      <c r="L141" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M141" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N141" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="M141" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N141" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="O141" s="2" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="Q141" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R141" s="2" t="n">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
+          <t>openrouter/free</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
@@ -12216,21 +12216,21 @@
         </is>
       </c>
       <c r="I142" s="22" t="n">
-        <v>128000</v>
+        <v>200000</v>
       </c>
       <c r="J142" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K142" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M142" s="24" t="inlineStr">
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="O142" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P142" s="18" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12284,35 +12284,35 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
-        </is>
-      </c>
-      <c r="H143" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>openai/gpt-live-1</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K143" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L143" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M143" s="9" t="inlineStr">
@@ -12326,16 +12326,16 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="H144" s="34" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12448,35 +12448,35 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
-        </is>
-      </c>
-      <c r="H145" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
+          <t>voxtral-small-latest</t>
+        </is>
+      </c>
+      <c r="H145" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>4096</v>
+        <v>32768</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K145" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L145" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K145" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -12490,16 +12490,16 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R145" s="2" t="n">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>alibaba/happyhorse-1.1</t>
         </is>
       </c>
       <c r="H146" s="38" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="J146" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K146" s="24" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="Q146" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R146" s="18" t="n">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H147" s="38" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12720,9 +12720,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L148" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L148" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M148" s="24" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="Q148" s="20" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R148" s="18" t="n">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12802,9 +12802,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L149" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M149" s="9" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R149" s="2" t="n">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="J152" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K152" s="24" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="Q152" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R152" s="18" t="n">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13186,33 +13186,35 @@
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
-        </is>
-      </c>
-      <c r="H154" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I154" s="22" t="n"/>
+          <t>wanx/wan-v3-0</t>
+        </is>
+      </c>
+      <c r="H154" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
+        </is>
+      </c>
+      <c r="I154" s="22" t="n">
+        <v>4096</v>
+      </c>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K154" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L154" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K154" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L154" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M154" s="24" t="inlineStr">
@@ -13226,16 +13228,16 @@
         </is>
       </c>
       <c r="O154" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P154" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q154" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R154" s="18" t="n">
@@ -13248,7 +13250,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13266,12 +13268,12 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>nvidia/ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="H155" s="21" t="inlineStr">
@@ -13306,7 +13308,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
@@ -13328,7 +13330,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13351,7 +13353,7 @@
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H156" s="21" t="inlineStr">
@@ -13408,7 +13410,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13431,7 +13433,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13488,7 +13490,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13506,12 +13508,12 @@
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13546,7 +13548,7 @@
         </is>
       </c>
       <c r="O158" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P158" s="18" t="inlineStr">
         <is>
@@ -13568,7 +13570,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13586,12 +13588,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13626,7 +13628,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
@@ -13648,7 +13650,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13671,7 +13673,7 @@
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13728,7 +13730,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13751,7 +13753,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13808,7 +13810,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13826,12 +13828,12 @@
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13860,13 +13862,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N162" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N162" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O162" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P162" s="18" t="inlineStr">
         <is>
@@ -13875,7 +13877,7 @@
       </c>
       <c r="Q162" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R162" s="18" t="n">
@@ -13888,7 +13890,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13911,7 +13913,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13940,9 +13942,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N163" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N163" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O163" s="2" t="n">
@@ -13955,7 +13957,7 @@
       </c>
       <c r="Q163" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R163" s="2" t="n">
@@ -13968,7 +13970,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13981,7 +13983,7 @@
       </c>
       <c r="E164" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
@@ -13991,7 +13993,7 @@
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14005,9 +14007,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K164" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K164" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L164" s="23" t="inlineStr">
@@ -14026,7 +14028,7 @@
         </is>
       </c>
       <c r="O164" s="18" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
@@ -14035,7 +14037,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14048,7 +14050,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14061,7 +14063,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -14071,7 +14073,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14085,9 +14087,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K165" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K165" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L165" s="23" t="inlineStr">
@@ -14106,7 +14108,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
@@ -14115,7 +14117,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14128,7 +14130,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14151,7 +14153,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14195,7 +14197,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14208,7 +14210,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14231,7 +14233,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14275,7 +14277,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14288,7 +14290,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14311,7 +14313,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14368,7 +14370,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14386,12 +14388,12 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14426,7 +14428,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
@@ -14448,7 +14450,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14471,7 +14473,7 @@
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14528,7 +14530,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14551,7 +14553,7 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14595,7 +14597,7 @@
       </c>
       <c r="Q171" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R171" s="2" t="n">
@@ -14608,7 +14610,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14626,12 +14628,12 @@
       </c>
       <c r="F172" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14666,7 +14668,7 @@
         </is>
       </c>
       <c r="O172" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P172" s="18" t="inlineStr">
         <is>
@@ -14675,7 +14677,7 @@
       </c>
       <c r="Q172" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R172" s="18" t="n">
@@ -14688,7 +14690,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14711,7 +14713,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14768,7 +14770,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14786,12 +14788,12 @@
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14805,14 +14807,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K174" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L174" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K174" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L174" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M174" s="24" t="inlineStr">
@@ -14826,16 +14828,16 @@
         </is>
       </c>
       <c r="O174" s="18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P174" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q174" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R174" s="18" t="n">
@@ -14848,7 +14850,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14861,17 +14863,17 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14890,9 +14892,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L175" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="L175" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M175" s="9" t="inlineStr">
@@ -14906,16 +14908,16 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q175" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R175" s="2" t="n">
@@ -14928,7 +14930,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>step-5-preview</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14941,7 +14943,7 @@
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -14951,7 +14953,7 @@
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>stepfun-ai/step-5-preview</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14965,9 +14967,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K176" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K176" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L176" s="23" t="inlineStr">
@@ -14986,7 +14988,7 @@
         </is>
       </c>
       <c r="O176" s="18" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P176" s="18" t="inlineStr">
         <is>
@@ -14995,7 +14997,7 @@
       </c>
       <c r="Q176" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R176" s="18" t="n">
@@ -15008,7 +15010,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>yi-large</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15031,7 +15033,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>01-ai/yi-large</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15082,1571 +15084,1651 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="41" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="B178" s="19" t="inlineStr">
+        <is>
+          <t>yi-large</t>
+        </is>
+      </c>
+      <c r="C178" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D178" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G178" s="20" t="inlineStr">
+        <is>
+          <t>01-ai/yi-large</t>
+        </is>
+      </c>
+      <c r="H178" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I178" s="22" t="n"/>
+      <c r="J178" s="18" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K178" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L178" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M178" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N178" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O178" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P178" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q178" s="20" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R178" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="41" t="inlineStr">
         <is>
           <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="30" customHeight="1">
-      <c r="A180" s="1" t="inlineStr">
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B180" s="1" t="inlineStr">
+      <c r="B181" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C181" s="1" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="D180" s="1" t="inlineStr">
+      <c r="D181" s="1" t="inlineStr">
         <is>
           <t>Tier (1-5)</t>
         </is>
       </c>
-      <c r="E180" s="1" t="inlineStr">
+      <c r="E181" s="1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="F180" s="1" t="inlineStr">
+      <c r="F181" s="1" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="G180" s="1" t="inlineStr">
+      <c r="G181" s="1" t="inlineStr">
         <is>
           <t>Gateway model id</t>
         </is>
       </c>
-      <c r="H180" s="1" t="inlineStr">
+      <c r="H181" s="1" t="inlineStr">
         <is>
           <t>Context class</t>
         </is>
       </c>
-      <c r="I180" s="1" t="inlineStr">
+      <c r="I181" s="1" t="inlineStr">
         <is>
           <t>Context (tokens)</t>
         </is>
       </c>
-      <c r="J180" s="1" t="inlineStr">
+      <c r="J181" s="1" t="inlineStr">
         <is>
           <t>Modality</t>
         </is>
       </c>
-      <c r="K180" s="1" t="inlineStr">
+      <c r="K181" s="1" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="L180" s="1" t="inlineStr">
+      <c r="L181" s="1" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="M180" s="1" t="inlineStr">
+      <c r="M181" s="1" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="N180" s="1" t="inlineStr">
+      <c r="N181" s="1" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="O180" s="1" t="inlineStr">
+      <c r="O181" s="1" t="inlineStr">
         <is>
           <t>Speed (0-100)</t>
         </is>
       </c>
-      <c r="P180" s="1" t="inlineStr">
+      <c r="P181" s="1" t="inlineStr">
         <is>
           <t>Free type</t>
         </is>
       </c>
-      <c r="Q180" s="1" t="inlineStr">
+      <c r="Q181" s="1" t="inlineStr">
         <is>
           <t>Best for</t>
         </is>
       </c>
-      <c r="R180" s="1" t="inlineStr">
+      <c r="R181" s="1" t="inlineStr">
         <is>
           <t>Gateways in group</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C182" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D181" s="2" t="n">
+      <c r="D182" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>120B</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G181" s="5" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="H181" s="21" t="inlineStr">
+      <c r="H182" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I181" s="7" t="n"/>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="I182" s="7" t="n"/>
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K181" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L181" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M181" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N181" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O181" s="2" t="n">
+      <c r="K182" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L182" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M182" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N182" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="P181" s="2" t="inlineStr">
+      <c r="P182" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q181" s="5" t="inlineStr">
+      <c r="Q182" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R181" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="18" t="n">
+      <c r="R182" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B182" s="19" t="inlineStr">
+      <c r="B183" s="19" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C183" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D182" s="18" t="n">
+      <c r="D183" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E182" s="18" t="inlineStr">
+      <c r="E183" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F182" s="20" t="inlineStr">
+      <c r="F183" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G182" s="20" t="inlineStr">
+      <c r="G183" s="20" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="H182" s="6" t="inlineStr">
+      <c r="H183" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I182" s="22" t="n">
+      <c r="I183" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J182" s="18" t="inlineStr">
+      <c r="J183" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K182" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L182" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M182" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N182" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O182" s="18" t="n">
+      <c r="K183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M183" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N183" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O183" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P182" s="18" t="inlineStr">
+      <c r="P183" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q182" s="20" t="inlineStr">
+      <c r="Q183" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R182" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="R183" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
+      <c r="D184" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G183" s="5" t="inlineStr">
+      <c r="G184" s="5" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H183" s="6" t="inlineStr">
+      <c r="H184" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I183" s="7" t="n">
+      <c r="I184" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M183" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N183" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O183" s="2" t="n">
+      <c r="K184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M184" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N184" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P183" s="2" t="inlineStr">
+      <c r="P184" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q183" s="5" t="inlineStr">
+      <c r="Q184" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R183" s="2" t="n">
+      <c r="R184" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="10" t="n">
+    <row r="185">
+      <c r="A185" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B184" s="11" t="inlineStr">
+      <c r="B185" s="11" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C184" s="12" t="inlineStr">
+      <c r="C185" s="12" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D184" s="10" t="n">
+      <c r="D185" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E184" s="10" t="inlineStr">
+      <c r="E185" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F184" s="13" t="inlineStr">
+      <c r="F185" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G184" s="13" t="inlineStr">
+      <c r="G185" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H184" s="30" t="inlineStr">
+      <c r="H185" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I184" s="15" t="n">
+      <c r="I185" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J184" s="10" t="inlineStr">
+      <c r="J185" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K184" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L184" s="30" t="inlineStr">
+      <c r="K185" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L185" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M184" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N184" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="10" t="n">
+      <c r="M185" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N185" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P184" s="10" t="inlineStr">
+      <c r="P185" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q184" s="13" t="inlineStr">
+      <c r="Q185" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R184" s="10" t="n">
+      <c r="R185" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="18" t="n">
+    <row r="186">
+      <c r="A186" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B185" s="19" t="inlineStr">
+      <c r="B186" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D185" s="18" t="n">
+      <c r="D186" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E185" s="18" t="inlineStr">
+      <c r="E186" s="18" t="inlineStr">
         <is>
           <t>90B</t>
         </is>
       </c>
-      <c r="F185" s="20" t="inlineStr">
+      <c r="F186" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G185" s="20" t="inlineStr">
+      <c r="G186" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="H185" s="21" t="inlineStr">
+      <c r="H186" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I185" s="22" t="n"/>
-      <c r="J185" s="18" t="inlineStr">
+      <c r="I186" s="22" t="n"/>
+      <c r="J186" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="18" t="n">
+      <c r="K186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M186" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N186" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="P185" s="18" t="inlineStr">
+      <c r="P186" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q185" s="20" t="inlineStr">
+      <c r="Q186" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R185" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="R186" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C186" s="31" t="inlineStr">
+      <c r="C187" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n">
+      <c r="D187" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G186" s="5" t="inlineStr">
+      <c r="G187" s="5" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I186" s="7" t="n">
+      <c r="I187" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N186" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="2" t="n">
+      <c r="K187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N187" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P186" s="2" t="inlineStr">
+      <c r="P187" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q186" s="5" t="inlineStr">
+      <c r="Q187" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R186" s="2" t="n">
+      <c r="R187" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="10" t="n">
+    <row r="188">
+      <c r="A188" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B187" s="11" t="inlineStr">
+      <c r="B188" s="11" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C187" s="32" t="inlineStr">
+      <c r="C188" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D187" s="10" t="n">
+      <c r="D188" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E187" s="10" t="inlineStr">
+      <c r="E188" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F187" s="13" t="inlineStr">
+      <c r="F188" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G187" s="13" t="inlineStr">
+      <c r="G188" s="13" t="inlineStr">
         <is>
           <t>google/gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H187" s="42" t="inlineStr">
+      <c r="H188" s="42" t="inlineStr">
         <is>
           <t>Medium (8K-32K)</t>
         </is>
       </c>
-      <c r="I187" s="15" t="n">
+      <c r="I188" s="15" t="n">
         <v>32768</v>
       </c>
-      <c r="J187" s="10" t="inlineStr">
+      <c r="J188" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L187" s="30" t="inlineStr">
+      <c r="K188" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L188" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M187" s="30" t="inlineStr">
+      <c r="M188" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="10" t="n">
+      <c r="N188" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P187" s="10" t="inlineStr">
+      <c r="P188" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q187" s="13" t="inlineStr">
+      <c r="Q188" s="13" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, fast</t>
         </is>
       </c>
-      <c r="R187" s="10" t="n">
+      <c r="R188" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="18" t="n">
+    <row r="189">
+      <c r="A189" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B188" s="19" t="inlineStr">
+      <c r="B189" s="19" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="C188" s="31" t="inlineStr">
+      <c r="C189" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D188" s="18" t="n">
+      <c r="D189" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E188" s="18" t="inlineStr">
+      <c r="E189" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F188" s="20" t="inlineStr">
+      <c r="F189" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G188" s="20" t="inlineStr">
+      <c r="G189" s="20" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I188" s="22" t="n">
+      <c r="I189" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J188" s="18" t="inlineStr">
+      <c r="J189" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="18" t="n">
+      <c r="K189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M189" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N189" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P188" s="18" t="inlineStr">
+      <c r="P189" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q188" s="20" t="inlineStr">
+      <c r="Q189" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R188" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="R189" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C189" s="31" t="inlineStr">
+      <c r="C190" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D189" s="2" t="n">
+      <c r="D190" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G189" s="5" t="inlineStr">
+      <c r="G190" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I189" s="7" t="n">
+      <c r="I190" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M189" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N189" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="2" t="n">
+      <c r="K190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M190" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N190" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P189" s="2" t="inlineStr">
+      <c r="P190" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q189" s="5" t="inlineStr">
+      <c r="Q190" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R189" s="2" t="n">
+      <c r="R190" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="10" t="n">
+    <row r="191">
+      <c r="A191" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B190" s="11" t="inlineStr">
+      <c r="B191" s="11" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C190" s="32" t="inlineStr">
+      <c r="C191" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D190" s="10" t="n">
+      <c r="D191" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E190" s="10" t="inlineStr">
+      <c r="E191" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F190" s="13" t="inlineStr">
+      <c r="F191" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G190" s="13" t="inlineStr">
+      <c r="G191" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H190" s="30" t="inlineStr">
+      <c r="H191" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I190" s="15" t="n">
+      <c r="I191" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J190" s="10" t="inlineStr">
+      <c r="J191" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L190" s="30" t="inlineStr">
+      <c r="K191" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L191" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="10" t="n">
+      <c r="M191" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P190" s="10" t="inlineStr">
+      <c r="P191" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q190" s="13" t="inlineStr">
+      <c r="Q191" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R190" s="10" t="n">
+      <c r="R191" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="18" t="n">
+    <row r="192">
+      <c r="A192" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B191" s="19" t="inlineStr">
+      <c r="B192" s="19" t="inlineStr">
         <is>
           <t>neva-22b</t>
         </is>
       </c>
-      <c r="C191" s="35" t="inlineStr">
+      <c r="C192" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D191" s="18" t="n">
+      <c r="D192" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E191" s="18" t="inlineStr">
+      <c r="E192" s="18" t="inlineStr">
         <is>
           <t>22B</t>
         </is>
       </c>
-      <c r="F191" s="20" t="inlineStr">
+      <c r="F192" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G191" s="20" t="inlineStr">
+      <c r="G192" s="20" t="inlineStr">
         <is>
           <t>nvidia/neva-22b</t>
         </is>
       </c>
-      <c r="H191" s="21" t="inlineStr">
+      <c r="H192" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I191" s="22" t="n"/>
-      <c r="J191" s="18" t="inlineStr">
+      <c r="I192" s="22" t="n"/>
+      <c r="J192" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="18" t="n">
+      <c r="K192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M192" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="P191" s="18" t="inlineStr">
+      <c r="P192" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q191" s="20" t="inlineStr">
+      <c r="Q192" s="20" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R191" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="R192" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="C192" s="35" t="inlineStr">
+      <c r="C193" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D192" s="2" t="n">
+      <c r="D193" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F192" s="5" t="inlineStr">
+      <c r="F193" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G192" s="5" t="inlineStr">
+      <c r="G193" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="H192" s="6" t="inlineStr">
+      <c r="H193" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I192" s="7" t="n">
+      <c r="I193" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="2" t="n">
+      <c r="K193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M193" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P192" s="2" t="inlineStr">
+      <c r="P193" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q192" s="5" t="inlineStr">
+      <c r="Q193" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R192" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="18" t="n">
+      <c r="R193" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B193" s="19" t="inlineStr">
+      <c r="B194" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="C193" s="37" t="inlineStr">
+      <c r="C194" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D193" s="18" t="n">
+      <c r="D194" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E193" s="18" t="inlineStr">
+      <c r="E194" s="18" t="inlineStr">
         <is>
           <t>11B</t>
         </is>
       </c>
-      <c r="F193" s="20" t="inlineStr">
+      <c r="F194" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G193" s="20" t="inlineStr">
+      <c r="G194" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="H193" s="21" t="inlineStr">
+      <c r="H194" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I193" s="22" t="n"/>
-      <c r="J193" s="18" t="inlineStr">
+      <c r="I194" s="22" t="n"/>
+      <c r="J194" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M193" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="18" t="n">
+      <c r="K194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M194" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="P193" s="18" t="inlineStr">
+      <c r="P194" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q193" s="20" t="inlineStr">
+      <c r="Q194" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R193" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="R194" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>fuyu-8b</t>
         </is>
       </c>
-      <c r="C194" s="37" t="inlineStr">
+      <c r="C195" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D194" s="2" t="n">
+      <c r="D195" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>8B</t>
         </is>
       </c>
-      <c r="F194" s="5" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G194" s="5" t="inlineStr">
+      <c r="G195" s="5" t="inlineStr">
         <is>
           <t>adept/fuyu-8b</t>
         </is>
       </c>
-      <c r="H194" s="21" t="inlineStr">
+      <c r="H195" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I194" s="7" t="n"/>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="I195" s="7" t="n"/>
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="2" t="n">
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P194" s="2" t="inlineStr">
+      <c r="P195" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q194" s="5" t="inlineStr">
+      <c r="Q195" s="5" t="inlineStr">
         <is>
           <t>extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R194" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="18" t="n">
+      <c r="R195" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B195" s="19" t="inlineStr">
+      <c r="B196" s="19" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl</t>
         </is>
       </c>
-      <c r="C195" s="39" t="inlineStr">
+      <c r="C196" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D195" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" s="18" t="inlineStr">
+      <c r="D196" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F195" s="20" t="inlineStr">
+      <c r="F196" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G195" s="20" t="inlineStr">
+      <c r="G196" s="20" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl:free</t>
         </is>
       </c>
-      <c r="H195" s="6" t="inlineStr">
+      <c r="H196" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I195" s="22" t="n">
+      <c r="I196" s="22" t="n">
         <v>1000000</v>
       </c>
-      <c r="J195" s="18" t="inlineStr">
+      <c r="J196" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K195" s="8" t="inlineStr">
+      <c r="K196" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L195" s="8" t="inlineStr">
+      <c r="L196" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M195" s="8" t="inlineStr">
+      <c r="M196" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N195" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="18" t="n">
+      <c r="N196" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P195" s="18" t="inlineStr">
+      <c r="P196" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q195" s="20" t="inlineStr">
+      <c r="Q196" s="20" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R195" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="R196" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>kosmos-2</t>
         </is>
       </c>
-      <c r="C196" s="39" t="inlineStr">
+      <c r="C197" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D196" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="D197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
+      <c r="F197" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G196" s="5" t="inlineStr">
+      <c r="G197" s="5" t="inlineStr">
         <is>
           <t>microsoft/kosmos-2</t>
         </is>
       </c>
-      <c r="H196" s="21" t="inlineStr">
+      <c r="H197" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I196" s="7" t="n"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="7" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M196" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N196" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="2" t="n">
+      <c r="K197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M197" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N197" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P196" s="2" t="inlineStr">
+      <c r="P197" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q196" s="5" t="inlineStr">
+      <c r="Q197" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R196" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="18" t="n">
+      <c r="R197" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B197" s="19" t="inlineStr">
+      <c r="B198" s="19" t="inlineStr">
         <is>
           <t>phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="C197" s="39" t="inlineStr">
+      <c r="C198" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D197" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" s="18" t="inlineStr">
+      <c r="D198" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F197" s="20" t="inlineStr">
+      <c r="F198" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G197" s="20" t="inlineStr">
+      <c r="G198" s="20" t="inlineStr">
         <is>
           <t>microsoft/phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="H197" s="21" t="inlineStr">
+      <c r="H198" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I197" s="22" t="n"/>
-      <c r="J197" s="18" t="inlineStr">
+      <c r="I198" s="22" t="n"/>
+      <c r="J198" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M197" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N197" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="18" t="n">
+      <c r="K198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M198" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N198" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="P197" s="18" t="inlineStr">
+      <c r="P198" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q197" s="20" t="inlineStr">
+      <c r="Q198" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R197" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="R198" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>vila</t>
         </is>
       </c>
-      <c r="C198" s="39" t="inlineStr">
+      <c r="C199" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="D199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F198" s="5" t="inlineStr">
+      <c r="F199" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G198" s="5" t="inlineStr">
+      <c r="G199" s="5" t="inlineStr">
         <is>
           <t>nvidia/vila</t>
         </is>
       </c>
-      <c r="H198" s="21" t="inlineStr">
+      <c r="H199" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I198" s="7" t="n"/>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="I199" s="7" t="n"/>
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M198" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N198" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O198" s="2" t="n">
+      <c r="K199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M199" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N199" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P198" s="2" t="inlineStr">
+      <c r="P199" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q198" s="5" t="inlineStr">
+      <c r="Q199" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R198" s="2" t="n">
+      <c r="R199" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R177"/>
+  <autoFilter ref="A1:R178"/>
   <mergeCells count="1">
-    <mergeCell ref="A179:R179"/>
+    <mergeCell ref="A180:R180"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O177">
+  <conditionalFormatting sqref="O2:O178">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16882,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-16T16:42:45Z (source: live)</t>
+          <t>Registry updated 2026-10-16T21:13:32Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-16T21:13:32Z (source: live)</t>
+          <t>Registry updated 2026-10-17T04:32:22Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-17T04:32:22Z (source: live)</t>
+          <t>Registry updated 2026-10-17T10:49:13Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-17T10:49:13Z (source: live)</t>
+          <t>Registry updated 2026-10-17T15:38:41Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-17T15:38:41Z (source: live)</t>
+          <t>Registry updated 2026-10-17T20:39:40Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-17T20:39:40Z (source: live)</t>
+          <t>Registry updated 2026-10-18T04:38:50Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-18T04:38:50Z (source: live)</t>
+          <t>Registry updated 2026-10-18T11:12:18Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-18T11:12:18Z (source: live)</t>
+          <t>Registry updated 2026-10-18T15:54:26Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-18T15:54:26Z (source: live)</t>
+          <t>Registry updated 2026-10-18T20:48:16Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -16964,7 +16964,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-18T20:48:16Z (source: live)</t>
+          <t>Registry updated 2026-10-19T04:46:02Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R199"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>dots-3-note-preview</t>
+          <t>minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="C129" s="39" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>dots-studio/dots-3-note-preview:free</t>
+          <t>minimax/minimax-m3.1-flash:free</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>512000</v>
+        <v>1000000</v>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Q129" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-6</t>
+          <t>dots-3-note-preview</t>
         </is>
       </c>
       <c r="C130" s="39" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-6</t>
+          <t>dots-studio/dots-3-note-preview:free</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>400000</v>
+        <v>512000</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K130" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M130" s="9" t="inlineStr">
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R130" s="2" t="n">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>wan-v2-6</t>
         </is>
       </c>
       <c r="C131" s="39" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>wanx/wan-v2-6</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -11316,21 +11316,21 @@
         </is>
       </c>
       <c r="I131" s="22" t="n">
-        <v>262144</v>
+        <v>400000</v>
       </c>
       <c r="J131" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K131" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L131" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K131" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L131" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M131" s="24" t="inlineStr">
@@ -11344,16 +11344,16 @@
         </is>
       </c>
       <c r="O131" s="18" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P131" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q131" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R131" s="18" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="C132" s="39" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>laguna-s-2.1</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="C133" s="39" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="F133" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>poolside/laguna-s-2.1:free</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="J133" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K133" s="8" t="inlineStr">
@@ -11492,9 +11492,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L133" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L133" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M133" s="24" t="inlineStr">
@@ -11508,16 +11508,16 @@
         </is>
       </c>
       <c r="O133" s="18" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P133" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q133" s="20" t="inlineStr">
         <is>
-          <t>agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R133" s="18" t="n">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>laguna-xs-2.1</t>
+          <t>laguna-s-2.1</t>
         </is>
       </c>
       <c r="C134" s="39" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>poolside/laguna-xs-2.1:free</t>
+          <t>poolside/laguna-s-2.1:free</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -11603,169 +11603,169 @@
         </is>
       </c>
       <c r="R134" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="n">
+        <v>118</v>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
+        <is>
+          <t>laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="C135" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D135" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F135" s="20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G135" s="20" t="inlineStr">
+        <is>
+          <t>poolside/laguna-xs-2.1:free</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I135" s="22" t="n">
+        <v>262144</v>
+      </c>
+      <c r="J135" s="18" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K135" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L135" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M135" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N135" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O135" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="P135" s="18" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q135" s="20" t="inlineStr">
+        <is>
+          <t>agent, long_doc</t>
+        </is>
+      </c>
+      <c r="R135" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="10" t="n">
-        <v>117</v>
-      </c>
-      <c r="B135" s="11" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="25" t="n">
+        <v>118</v>
+      </c>
+      <c r="B136" s="26" t="inlineStr">
         <is>
           <t>laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="C135" s="40" t="inlineStr">
+      <c r="C136" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="10" t="inlineStr">
+      <c r="D136" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F135" s="13" t="inlineStr">
+      <c r="F136" s="27" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G135" s="13" t="inlineStr">
+      <c r="G136" s="27" t="inlineStr">
         <is>
           <t>poolside/laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="H135" s="14" t="inlineStr">
+      <c r="H136" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I135" s="15" t="n"/>
-      <c r="J135" s="10" t="inlineStr">
+      <c r="I136" s="28" t="n"/>
+      <c r="J136" s="25" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K135" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L135" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M135" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N135" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O135" s="10" t="n">
+      <c r="K136" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L136" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M136" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="P135" s="10" t="inlineStr">
+      <c r="P136" s="25" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q135" s="13" t="inlineStr">
+      <c r="Q136" s="27" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R135" s="10" t="n">
+      <c r="R136" s="25" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="18" t="n">
-        <v>118</v>
-      </c>
-      <c r="B136" s="19" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="C136" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D136" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F136" s="20" t="inlineStr">
-        <is>
-          <t>mistral</t>
-        </is>
-      </c>
-      <c r="G136" s="20" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I136" s="22" t="n">
-        <v>262144</v>
-      </c>
-      <c r="J136" s="18" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K136" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L136" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M136" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N136" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O136" s="18" t="n">
-        <v>44</v>
-      </c>
-      <c r="P136" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q136" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R136" s="18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="C137" s="39" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R137" s="2" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -11970,11 +11970,11 @@
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>256000</v>
+        <v>262144</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K139" s="8" t="inlineStr">
@@ -11992,9 +11992,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N139" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N139" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O139" s="2" t="n">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="Q139" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R139" s="2" t="n">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -12146,9 +12146,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L141" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M141" s="9" t="inlineStr">
@@ -12162,16 +12162,16 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q141" s="5" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R141" s="2" t="n">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12207,20 +12207,20 @@
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
-        </is>
-      </c>
-      <c r="H142" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>cohere/north-mini-code:free</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I142" s="22" t="n">
-        <v>200000</v>
+        <v>256000</v>
       </c>
       <c r="J142" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K142" s="8" t="inlineStr">
@@ -12228,19 +12228,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L142" s="8" t="inlineStr">
+      <c r="L142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N142" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="M142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="O142" s="18" t="n">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12284,12 +12284,12 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
+          <t>openrouter/free</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
@@ -12298,21 +12298,21 @@
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>128000</v>
+        <v>200000</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K143" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M143" s="9" t="inlineStr">
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12366,35 +12366,35 @@
       </c>
       <c r="F144" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
-        </is>
-      </c>
-      <c r="H144" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>openai/gpt-live-1</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="J144" s="18" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K144" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K144" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L144" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M144" s="24" t="inlineStr">
@@ -12408,16 +12408,16 @@
         </is>
       </c>
       <c r="O144" s="18" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P144" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q144" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R144" s="18" t="n">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="H145" s="34" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12530,35 +12530,35 @@
       </c>
       <c r="F146" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
-        </is>
-      </c>
-      <c r="H146" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
+          <t>voxtral-small-latest</t>
+        </is>
+      </c>
+      <c r="H146" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I146" s="22" t="n">
-        <v>4096</v>
+        <v>32768</v>
       </c>
       <c r="J146" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K146" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L146" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K146" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L146" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M146" s="24" t="inlineStr">
@@ -12572,16 +12572,16 @@
         </is>
       </c>
       <c r="O146" s="18" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P146" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q146" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R146" s="18" t="n">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>alibaba/happyhorse-1.1</t>
         </is>
       </c>
       <c r="H147" s="38" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R147" s="2" t="n">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12802,9 +12802,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L149" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L149" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M149" s="9" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R149" s="2" t="n">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12884,9 +12884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L150" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M150" s="24" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="Q150" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R150" s="18" t="n">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="Q153" s="5" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R153" s="2" t="n">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13268,33 +13268,35 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
-        </is>
-      </c>
-      <c r="H155" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I155" s="7" t="n"/>
+          <t>wanx/wan-v3-0</t>
+        </is>
+      </c>
+      <c r="H155" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="n">
+        <v>4096</v>
+      </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K155" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L155" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K155" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L155" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M155" s="9" t="inlineStr">
@@ -13308,16 +13310,16 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q155" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R155" s="2" t="n">
@@ -13330,7 +13332,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13348,12 +13350,12 @@
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>nvidia/ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="H156" s="21" t="inlineStr">
@@ -13388,7 +13390,7 @@
         </is>
       </c>
       <c r="O156" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P156" s="18" t="inlineStr">
         <is>
@@ -13410,7 +13412,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13433,7 +13435,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13490,7 +13492,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13513,7 +13515,7 @@
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13570,7 +13572,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13588,12 +13590,12 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13628,7 +13630,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
@@ -13650,7 +13652,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13668,12 +13670,12 @@
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13708,7 +13710,7 @@
         </is>
       </c>
       <c r="O160" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P160" s="18" t="inlineStr">
         <is>
@@ -13730,7 +13732,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13753,7 +13755,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13810,7 +13812,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13833,7 +13835,7 @@
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13890,7 +13892,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13908,12 +13910,12 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13942,13 +13944,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N163" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N163" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
@@ -13957,7 +13959,7 @@
       </c>
       <c r="Q163" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R163" s="2" t="n">
@@ -13970,7 +13972,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13993,7 +13995,7 @@
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14022,9 +14024,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N164" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N164" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O164" s="18" t="n">
@@ -14037,7 +14039,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14050,7 +14052,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14063,7 +14065,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -14073,7 +14075,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14087,9 +14089,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K165" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K165" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L165" s="23" t="inlineStr">
@@ -14108,7 +14110,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
@@ -14117,7 +14119,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14130,7 +14132,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14143,7 +14145,7 @@
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -14153,7 +14155,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14167,9 +14169,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K166" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K166" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -14188,7 +14190,7 @@
         </is>
       </c>
       <c r="O166" s="18" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P166" s="18" t="inlineStr">
         <is>
@@ -14197,7 +14199,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14210,7 +14212,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14233,7 +14235,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14277,7 +14279,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14290,7 +14292,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14313,7 +14315,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14357,7 +14359,7 @@
       </c>
       <c r="Q168" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R168" s="18" t="n">
@@ -14370,7 +14372,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14393,7 +14395,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14450,7 +14452,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14468,12 +14470,12 @@
       </c>
       <c r="F170" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14508,7 +14510,7 @@
         </is>
       </c>
       <c r="O170" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P170" s="18" t="inlineStr">
         <is>
@@ -14530,7 +14532,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14553,7 +14555,7 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14610,7 +14612,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14633,7 +14635,7 @@
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14677,7 +14679,7 @@
       </c>
       <c r="Q172" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R172" s="18" t="n">
@@ -14690,7 +14692,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14708,12 +14710,12 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14748,7 +14750,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
@@ -14757,7 +14759,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R173" s="2" t="n">
@@ -14770,7 +14772,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14793,7 +14795,7 @@
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14850,7 +14852,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14868,12 +14870,12 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14887,14 +14889,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K175" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L175" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K175" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L175" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M175" s="9" t="inlineStr">
@@ -14908,16 +14910,16 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q175" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R175" s="2" t="n">
@@ -14930,7 +14932,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14943,17 +14945,17 @@
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14972,9 +14974,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L176" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="L176" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M176" s="24" t="inlineStr">
@@ -14988,16 +14990,16 @@
         </is>
       </c>
       <c r="O176" s="18" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P176" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q176" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R176" s="18" t="n">
@@ -15010,7 +15012,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>step-5-preview</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15023,7 +15025,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
@@ -15033,7 +15035,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>stepfun-ai/step-5-preview</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15047,9 +15049,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K177" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K177" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L177" s="23" t="inlineStr">
@@ -15068,7 +15070,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
@@ -15077,7 +15079,7 @@
       </c>
       <c r="Q177" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R177" s="2" t="n">
@@ -15090,7 +15092,7 @@
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>yi-large</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C178" s="39" t="inlineStr">
@@ -15113,7 +15115,7 @@
       </c>
       <c r="G178" s="20" t="inlineStr">
         <is>
-          <t>01-ai/yi-large</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H178" s="21" t="inlineStr">
@@ -15164,1571 +15166,1651 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="41" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>yi-large</t>
+        </is>
+      </c>
+      <c r="C179" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>01-ai/yi-large</t>
+        </is>
+      </c>
+      <c r="H179" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I179" s="7" t="n"/>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K179" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L179" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M179" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N179" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q179" s="5" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="41" t="inlineStr">
         <is>
           <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="30" customHeight="1">
-      <c r="A181" s="1" t="inlineStr">
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B181" s="1" t="inlineStr">
+      <c r="B182" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="D181" s="1" t="inlineStr">
+      <c r="D182" s="1" t="inlineStr">
         <is>
           <t>Tier (1-5)</t>
         </is>
       </c>
-      <c r="E181" s="1" t="inlineStr">
+      <c r="E182" s="1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="F181" s="1" t="inlineStr">
+      <c r="F182" s="1" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="G181" s="1" t="inlineStr">
+      <c r="G182" s="1" t="inlineStr">
         <is>
           <t>Gateway model id</t>
         </is>
       </c>
-      <c r="H181" s="1" t="inlineStr">
+      <c r="H182" s="1" t="inlineStr">
         <is>
           <t>Context class</t>
         </is>
       </c>
-      <c r="I181" s="1" t="inlineStr">
+      <c r="I182" s="1" t="inlineStr">
         <is>
           <t>Context (tokens)</t>
         </is>
       </c>
-      <c r="J181" s="1" t="inlineStr">
+      <c r="J182" s="1" t="inlineStr">
         <is>
           <t>Modality</t>
         </is>
       </c>
-      <c r="K181" s="1" t="inlineStr">
+      <c r="K182" s="1" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="L181" s="1" t="inlineStr">
+      <c r="L182" s="1" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="M181" s="1" t="inlineStr">
+      <c r="M182" s="1" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="N181" s="1" t="inlineStr">
+      <c r="N182" s="1" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="O181" s="1" t="inlineStr">
+      <c r="O182" s="1" t="inlineStr">
         <is>
           <t>Speed (0-100)</t>
         </is>
       </c>
-      <c r="P181" s="1" t="inlineStr">
+      <c r="P182" s="1" t="inlineStr">
         <is>
           <t>Free type</t>
         </is>
       </c>
-      <c r="Q181" s="1" t="inlineStr">
+      <c r="Q182" s="1" t="inlineStr">
         <is>
           <t>Best for</t>
         </is>
       </c>
-      <c r="R181" s="1" t="inlineStr">
+      <c r="R182" s="1" t="inlineStr">
         <is>
           <t>Gateways in group</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C183" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D182" s="2" t="n">
+      <c r="D183" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>120B</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G182" s="5" t="inlineStr">
+      <c r="G183" s="5" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="H182" s="21" t="inlineStr">
+      <c r="H183" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I182" s="7" t="n"/>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="I183" s="7" t="n"/>
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K182" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L182" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M182" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N182" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O182" s="2" t="n">
+      <c r="K183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N183" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="P182" s="2" t="inlineStr">
+      <c r="P183" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q182" s="5" t="inlineStr">
+      <c r="Q183" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R182" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="18" t="n">
+      <c r="R183" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B183" s="19" t="inlineStr">
+      <c r="B184" s="19" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D183" s="18" t="n">
+      <c r="D184" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E183" s="18" t="inlineStr">
+      <c r="E184" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F183" s="20" t="inlineStr">
+      <c r="F184" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G183" s="20" t="inlineStr">
+      <c r="G184" s="20" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="H183" s="6" t="inlineStr">
+      <c r="H184" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I183" s="22" t="n">
+      <c r="I184" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J183" s="18" t="inlineStr">
+      <c r="J184" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M183" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N183" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O183" s="18" t="n">
+      <c r="K184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M184" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N184" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P183" s="18" t="inlineStr">
+      <c r="P184" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q183" s="20" t="inlineStr">
+      <c r="Q184" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R183" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="R184" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D184" s="2" t="n">
+      <c r="D185" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr">
+      <c r="G185" s="5" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H184" s="6" t="inlineStr">
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I184" s="7" t="n">
+      <c r="I185" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M184" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N184" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="2" t="n">
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N185" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P184" s="2" t="inlineStr">
+      <c r="P185" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q184" s="5" t="inlineStr">
+      <c r="Q185" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R184" s="2" t="n">
+      <c r="R185" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="10" t="n">
+    <row r="186">
+      <c r="A186" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B185" s="11" t="inlineStr">
+      <c r="B186" s="11" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C185" s="12" t="inlineStr">
+      <c r="C186" s="12" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D185" s="10" t="n">
+      <c r="D186" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E185" s="10" t="inlineStr">
+      <c r="E186" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F185" s="13" t="inlineStr">
+      <c r="F186" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G185" s="13" t="inlineStr">
+      <c r="G186" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H185" s="30" t="inlineStr">
+      <c r="H186" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I185" s="15" t="n">
+      <c r="I186" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J185" s="10" t="inlineStr">
+      <c r="J186" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L185" s="30" t="inlineStr">
+      <c r="K186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L186" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M185" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="10" t="n">
+      <c r="M186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P185" s="10" t="inlineStr">
+      <c r="P186" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q185" s="13" t="inlineStr">
+      <c r="Q186" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R185" s="10" t="n">
+      <c r="R186" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="18" t="n">
+    <row r="187">
+      <c r="A187" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B186" s="19" t="inlineStr">
+      <c r="B187" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
+      <c r="C187" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D186" s="18" t="n">
+      <c r="D187" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E186" s="18" t="inlineStr">
+      <c r="E187" s="18" t="inlineStr">
         <is>
           <t>90B</t>
         </is>
       </c>
-      <c r="F186" s="20" t="inlineStr">
+      <c r="F187" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G186" s="20" t="inlineStr">
+      <c r="G187" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="H186" s="21" t="inlineStr">
+      <c r="H187" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I186" s="22" t="n"/>
-      <c r="J186" s="18" t="inlineStr">
+      <c r="I187" s="22" t="n"/>
+      <c r="J187" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M186" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N186" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="18" t="n">
+      <c r="K187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M187" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="P186" s="18" t="inlineStr">
+      <c r="P187" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q186" s="20" t="inlineStr">
+      <c r="Q187" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R186" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="R187" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B187" s="3" t="inlineStr">
+      <c r="B188" s="3" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C187" s="31" t="inlineStr">
+      <c r="C188" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D187" s="2" t="n">
+      <c r="D188" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G187" s="5" t="inlineStr">
+      <c r="G188" s="5" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I187" s="7" t="n">
+      <c r="I188" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N187" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="2" t="n">
+      <c r="K188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N188" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P187" s="2" t="inlineStr">
+      <c r="P188" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q187" s="5" t="inlineStr">
+      <c r="Q188" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R187" s="2" t="n">
+      <c r="R188" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="10" t="n">
+    <row r="189">
+      <c r="A189" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B188" s="11" t="inlineStr">
+      <c r="B189" s="11" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C188" s="32" t="inlineStr">
+      <c r="C189" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D188" s="10" t="n">
+      <c r="D189" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E188" s="10" t="inlineStr">
+      <c r="E189" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F188" s="13" t="inlineStr">
+      <c r="F189" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G188" s="13" t="inlineStr">
+      <c r="G189" s="13" t="inlineStr">
         <is>
           <t>google/gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H188" s="42" t="inlineStr">
+      <c r="H189" s="42" t="inlineStr">
         <is>
           <t>Medium (8K-32K)</t>
         </is>
       </c>
-      <c r="I188" s="15" t="n">
+      <c r="I189" s="15" t="n">
         <v>32768</v>
       </c>
-      <c r="J188" s="10" t="inlineStr">
+      <c r="J189" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K188" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L188" s="30" t="inlineStr">
+      <c r="K189" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L189" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M188" s="30" t="inlineStr">
+      <c r="M189" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N188" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="10" t="n">
+      <c r="N189" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P188" s="10" t="inlineStr">
+      <c r="P189" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q188" s="13" t="inlineStr">
+      <c r="Q189" s="13" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, fast</t>
         </is>
       </c>
-      <c r="R188" s="10" t="n">
+      <c r="R189" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="18" t="n">
+    <row r="190">
+      <c r="A190" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B189" s="19" t="inlineStr">
+      <c r="B190" s="19" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="C189" s="31" t="inlineStr">
+      <c r="C190" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D189" s="18" t="n">
+      <c r="D190" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E189" s="18" t="inlineStr">
+      <c r="E190" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F189" s="20" t="inlineStr">
+      <c r="F190" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G189" s="20" t="inlineStr">
+      <c r="G190" s="20" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I189" s="22" t="n">
+      <c r="I190" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J189" s="18" t="inlineStr">
+      <c r="J190" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M189" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N189" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="18" t="n">
+      <c r="K190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M190" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N190" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P189" s="18" t="inlineStr">
+      <c r="P190" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q189" s="20" t="inlineStr">
+      <c r="Q190" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R189" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="R190" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B190" s="3" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C190" s="31" t="inlineStr">
+      <c r="C191" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D190" s="2" t="n">
+      <c r="D191" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
+      <c r="F191" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G190" s="5" t="inlineStr">
+      <c r="G191" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="H191" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I190" s="7" t="n">
+      <c r="I191" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M190" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N190" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="2" t="n">
+      <c r="K191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M191" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P190" s="2" t="inlineStr">
+      <c r="P191" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q190" s="5" t="inlineStr">
+      <c r="Q191" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R190" s="2" t="n">
+      <c r="R191" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="10" t="n">
+    <row r="192">
+      <c r="A192" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B191" s="11" t="inlineStr">
+      <c r="B192" s="11" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C191" s="32" t="inlineStr">
+      <c r="C192" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D191" s="10" t="n">
+      <c r="D192" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E191" s="10" t="inlineStr">
+      <c r="E192" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F191" s="13" t="inlineStr">
+      <c r="F192" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G191" s="13" t="inlineStr">
+      <c r="G192" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H191" s="30" t="inlineStr">
+      <c r="H192" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I191" s="15" t="n">
+      <c r="I192" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J191" s="10" t="inlineStr">
+      <c r="J192" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K191" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L191" s="30" t="inlineStr">
+      <c r="K192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L192" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M191" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="10" t="n">
+      <c r="M192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P191" s="10" t="inlineStr">
+      <c r="P192" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q191" s="13" t="inlineStr">
+      <c r="Q192" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R191" s="10" t="n">
+      <c r="R192" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="18" t="n">
+    <row r="193">
+      <c r="A193" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B192" s="19" t="inlineStr">
+      <c r="B193" s="19" t="inlineStr">
         <is>
           <t>neva-22b</t>
         </is>
       </c>
-      <c r="C192" s="35" t="inlineStr">
+      <c r="C193" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D192" s="18" t="n">
+      <c r="D193" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E192" s="18" t="inlineStr">
+      <c r="E193" s="18" t="inlineStr">
         <is>
           <t>22B</t>
         </is>
       </c>
-      <c r="F192" s="20" t="inlineStr">
+      <c r="F193" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G192" s="20" t="inlineStr">
+      <c r="G193" s="20" t="inlineStr">
         <is>
           <t>nvidia/neva-22b</t>
         </is>
       </c>
-      <c r="H192" s="21" t="inlineStr">
+      <c r="H193" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I192" s="22" t="n"/>
-      <c r="J192" s="18" t="inlineStr">
+      <c r="I193" s="22" t="n"/>
+      <c r="J193" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M192" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="18" t="n">
+      <c r="K193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="P192" s="18" t="inlineStr">
+      <c r="P193" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q192" s="20" t="inlineStr">
+      <c r="Q193" s="20" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R192" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="R193" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B193" s="3" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="C193" s="35" t="inlineStr">
+      <c r="C194" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D193" s="2" t="n">
+      <c r="D194" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F193" s="5" t="inlineStr">
+      <c r="F194" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G193" s="5" t="inlineStr">
+      <c r="G194" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="H193" s="6" t="inlineStr">
+      <c r="H194" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I193" s="7" t="n">
+      <c r="I194" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M193" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="2" t="n">
+      <c r="K194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P193" s="2" t="inlineStr">
+      <c r="P194" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q193" s="5" t="inlineStr">
+      <c r="Q194" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R193" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="n">
+      <c r="R194" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B194" s="19" t="inlineStr">
+      <c r="B195" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="C194" s="37" t="inlineStr">
+      <c r="C195" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D194" s="18" t="n">
+      <c r="D195" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E194" s="18" t="inlineStr">
+      <c r="E195" s="18" t="inlineStr">
         <is>
           <t>11B</t>
         </is>
       </c>
-      <c r="F194" s="20" t="inlineStr">
+      <c r="F195" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G194" s="20" t="inlineStr">
+      <c r="G195" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="H194" s="21" t="inlineStr">
+      <c r="H195" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I194" s="22" t="n"/>
-      <c r="J194" s="18" t="inlineStr">
+      <c r="I195" s="22" t="n"/>
+      <c r="J195" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="18" t="n">
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="P194" s="18" t="inlineStr">
+      <c r="P195" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q194" s="20" t="inlineStr">
+      <c r="Q195" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R194" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="R195" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>fuyu-8b</t>
         </is>
       </c>
-      <c r="C195" s="37" t="inlineStr">
+      <c r="C196" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D195" s="2" t="n">
+      <c r="D196" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>8B</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G195" s="5" t="inlineStr">
+      <c r="G196" s="5" t="inlineStr">
         <is>
           <t>adept/fuyu-8b</t>
         </is>
       </c>
-      <c r="H195" s="21" t="inlineStr">
+      <c r="H196" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I195" s="7" t="n"/>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="I196" s="7" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="2" t="n">
+      <c r="K196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P195" s="2" t="inlineStr">
+      <c r="P196" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q195" s="5" t="inlineStr">
+      <c r="Q196" s="5" t="inlineStr">
         <is>
           <t>extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R195" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="18" t="n">
+      <c r="R196" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B196" s="19" t="inlineStr">
+      <c r="B197" s="19" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl</t>
         </is>
       </c>
-      <c r="C196" s="39" t="inlineStr">
+      <c r="C197" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D196" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E196" s="18" t="inlineStr">
+      <c r="D197" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F196" s="20" t="inlineStr">
+      <c r="F197" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G196" s="20" t="inlineStr">
+      <c r="G197" s="20" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl:free</t>
         </is>
       </c>
-      <c r="H196" s="6" t="inlineStr">
+      <c r="H197" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I196" s="22" t="n">
+      <c r="I197" s="22" t="n">
         <v>1000000</v>
       </c>
-      <c r="J196" s="18" t="inlineStr">
+      <c r="J197" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K196" s="8" t="inlineStr">
+      <c r="K197" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L196" s="8" t="inlineStr">
+      <c r="L197" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M196" s="8" t="inlineStr">
+      <c r="M197" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="18" t="n">
+      <c r="N197" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P196" s="18" t="inlineStr">
+      <c r="P197" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q196" s="20" t="inlineStr">
+      <c r="Q197" s="20" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R196" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="R197" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B197" s="3" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>kosmos-2</t>
         </is>
       </c>
-      <c r="C197" s="39" t="inlineStr">
+      <c r="C198" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D197" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="D198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F197" s="5" t="inlineStr">
+      <c r="F198" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G197" s="5" t="inlineStr">
+      <c r="G198" s="5" t="inlineStr">
         <is>
           <t>microsoft/kosmos-2</t>
         </is>
       </c>
-      <c r="H197" s="21" t="inlineStr">
+      <c r="H198" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I197" s="7" t="n"/>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="I198" s="7" t="n"/>
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="2" t="n">
+      <c r="K198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P197" s="2" t="inlineStr">
+      <c r="P198" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q197" s="5" t="inlineStr">
+      <c r="Q198" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R197" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="18" t="n">
+      <c r="R198" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B198" s="19" t="inlineStr">
+      <c r="B199" s="19" t="inlineStr">
         <is>
           <t>phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="C198" s="39" t="inlineStr">
+      <c r="C199" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D198" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="18" t="inlineStr">
+      <c r="D199" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F198" s="20" t="inlineStr">
+      <c r="F199" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G198" s="20" t="inlineStr">
+      <c r="G199" s="20" t="inlineStr">
         <is>
           <t>microsoft/phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="H198" s="21" t="inlineStr">
+      <c r="H199" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I198" s="22" t="n"/>
-      <c r="J198" s="18" t="inlineStr">
+      <c r="I199" s="22" t="n"/>
+      <c r="J199" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M198" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N198" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O198" s="18" t="n">
+      <c r="K199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M199" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N199" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="P198" s="18" t="inlineStr">
+      <c r="P199" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q198" s="20" t="inlineStr">
+      <c r="Q199" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R198" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="R199" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B199" s="3" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>vila</t>
         </is>
       </c>
-      <c r="C199" s="39" t="inlineStr">
+      <c r="C200" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D199" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="D200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F199" s="5" t="inlineStr">
+      <c r="F200" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G199" s="5" t="inlineStr">
+      <c r="G200" s="5" t="inlineStr">
         <is>
           <t>nvidia/vila</t>
         </is>
       </c>
-      <c r="H199" s="21" t="inlineStr">
+      <c r="H200" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I199" s="7" t="n"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I200" s="7" t="n"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O199" s="2" t="n">
+      <c r="K200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P199" s="2" t="inlineStr">
+      <c r="P200" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q199" s="5" t="inlineStr">
+      <c r="Q200" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R199" s="2" t="n">
+      <c r="R200" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R178"/>
+  <autoFilter ref="A1:R179"/>
   <mergeCells count="1">
-    <mergeCell ref="A180:R180"/>
+    <mergeCell ref="A181:R181"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O178">
+  <conditionalFormatting sqref="O2:O179">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16964,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-19T04:46:02Z (source: live)</t>
+          <t>Registry updated 2026-10-19T13:23:49Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-19T13:23:49Z (source: live)</t>
+          <t>Registry updated 2026-10-19T22:23:41Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-19T22:23:41Z (source: live)</t>
+          <t>Registry updated 2026-10-20T04:55:39Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-20T04:55:39Z (source: live)</t>
+          <t>Registry updated 2026-10-20T11:43:29Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-20T11:43:29Z (source: live)</t>
+          <t>Registry updated 2026-10-20T17:12:41Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-20T17:12:41Z (source: live)</t>
+          <t>Registry updated 2026-10-20T21:40:07Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-20T21:40:07Z (source: live)</t>
+          <t>Registry updated 2026-10-21T04:54:14Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-21T04:54:14Z (source: live)</t>
+          <t>Registry updated 2026-10-21T11:55:17Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17046,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-21T11:55:17Z (source: live)</t>
+          <t>Registry updated 2026-10-21T17:15:55Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R200"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>flint-v1.0</t>
         </is>
       </c>
       <c r="C132" s="39" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>recursive/flint-v1.0:free</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
@@ -11426,16 +11426,16 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="C133" s="39" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>laguna-s-2.1</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="C134" s="39" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>poolside/laguna-s-2.1:free</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
@@ -11574,9 +11574,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L134" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M134" s="9" t="inlineStr">
@@ -11590,16 +11590,16 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R134" s="2" t="n">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>laguna-xs-2.1</t>
+          <t>laguna-s-2.1</t>
         </is>
       </c>
       <c r="C135" s="39" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="G135" s="20" t="inlineStr">
         <is>
-          <t>poolside/laguna-xs-2.1:free</t>
+          <t>poolside/laguna-s-2.1:free</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -11685,169 +11685,169 @@
         </is>
       </c>
       <c r="R135" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="C136" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>poolside/laguna-xs-2.1:free</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="n">
+        <v>262144</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K136" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q136" s="5" t="inlineStr">
+        <is>
+          <t>agent, long_doc</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="25" t="n">
-        <v>118</v>
-      </c>
-      <c r="B136" s="26" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="C136" s="40" t="inlineStr">
+      <c r="C137" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D136" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="25" t="inlineStr">
+      <c r="D137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F136" s="27" t="inlineStr">
+      <c r="F137" s="13" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G136" s="27" t="inlineStr">
+      <c r="G137" s="13" t="inlineStr">
         <is>
           <t>poolside/laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="H136" s="14" t="inlineStr">
+      <c r="H137" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I136" s="28" t="n"/>
-      <c r="J136" s="25" t="inlineStr">
+      <c r="I137" s="15" t="n"/>
+      <c r="J137" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K136" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L136" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M136" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N136" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O136" s="25" t="n">
+      <c r="K137" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L137" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M137" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="P136" s="25" t="inlineStr">
+      <c r="P137" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q136" s="27" t="inlineStr">
+      <c r="Q137" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R136" s="25" t="n">
+      <c r="R137" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="C137" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>mistral</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I137" s="7" t="n">
-        <v>262144</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K137" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M137" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N137" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O137" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="P137" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q137" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R137" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="Q138" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R138" s="18" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12052,11 +12052,11 @@
         </is>
       </c>
       <c r="I140" s="22" t="n">
-        <v>256000</v>
+        <v>262144</v>
       </c>
       <c r="J140" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K140" s="8" t="inlineStr">
@@ -12074,9 +12074,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N140" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N140" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O140" s="18" t="n">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="Q140" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R140" s="18" t="n">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -12228,9 +12228,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M142" s="24" t="inlineStr">
@@ -12244,16 +12244,16 @@
         </is>
       </c>
       <c r="O142" s="18" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P142" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12289,20 +12289,20 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>cohere/north-mini-code:free</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>200000</v>
+        <v>256000</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K143" s="8" t="inlineStr">
@@ -12310,19 +12310,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L143" s="8" t="inlineStr">
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N143" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="M143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="O143" s="2" t="n">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="F144" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
+          <t>openrouter/free</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
@@ -12380,21 +12380,21 @@
         </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>128000</v>
+        <v>200000</v>
       </c>
       <c r="J144" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K144" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L144" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K144" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L144" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M144" s="24" t="inlineStr">
@@ -12408,7 +12408,7 @@
         </is>
       </c>
       <c r="O144" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P144" s="18" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="Q144" s="20" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R144" s="18" t="n">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12448,35 +12448,35 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
-        </is>
-      </c>
-      <c r="H145" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>openai/gpt-live-1</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -12490,16 +12490,16 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R145" s="2" t="n">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12612,35 +12612,35 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
-        </is>
-      </c>
-      <c r="H147" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
+          <t>voxtral-small-latest</t>
+        </is>
+      </c>
+      <c r="H147" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I147" s="7" t="n">
-        <v>4096</v>
+        <v>32768</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L147" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K147" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M147" s="9" t="inlineStr">
@@ -12654,16 +12654,16 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R147" s="2" t="n">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>alibaba/happyhorse-1.1</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="J148" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K148" s="24" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="Q148" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R148" s="18" t="n">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12884,9 +12884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L150" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L150" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M150" s="24" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="Q150" s="20" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R150" s="18" t="n">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -12966,9 +12966,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M151" s="9" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R151" s="2" t="n">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K154" s="24" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Q154" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R154" s="18" t="n">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H155" s="38" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13350,33 +13350,35 @@
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
-        </is>
-      </c>
-      <c r="H156" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I156" s="22" t="n"/>
+          <t>wanx/wan-v3-0</t>
+        </is>
+      </c>
+      <c r="H156" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="n">
+        <v>4096</v>
+      </c>
       <c r="J156" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K156" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L156" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K156" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L156" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M156" s="24" t="inlineStr">
@@ -13390,16 +13392,16 @@
         </is>
       </c>
       <c r="O156" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P156" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q156" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R156" s="18" t="n">
@@ -13412,7 +13414,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13430,12 +13432,12 @@
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>nvidia/ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13470,7 +13472,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
@@ -13492,7 +13494,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13515,7 +13517,7 @@
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13572,7 +13574,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13595,7 +13597,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13652,7 +13654,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13670,12 +13672,12 @@
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13710,7 +13712,7 @@
         </is>
       </c>
       <c r="O160" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P160" s="18" t="inlineStr">
         <is>
@@ -13732,7 +13734,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13750,12 +13752,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13790,7 +13792,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
@@ -13812,7 +13814,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13835,7 +13837,7 @@
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13892,7 +13894,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13915,7 +13917,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13972,7 +13974,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13990,12 +13992,12 @@
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14024,13 +14026,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N164" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N164" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O164" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
@@ -14039,7 +14041,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14052,7 +14054,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14075,7 +14077,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14104,9 +14106,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N165" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N165" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O165" s="2" t="n">
@@ -14119,7 +14121,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14132,7 +14134,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14145,7 +14147,7 @@
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -14155,7 +14157,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14169,9 +14171,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K166" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K166" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -14190,7 +14192,7 @@
         </is>
       </c>
       <c r="O166" s="18" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P166" s="18" t="inlineStr">
         <is>
@@ -14199,7 +14201,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14212,7 +14214,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14225,7 +14227,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -14235,7 +14237,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14249,9 +14251,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K167" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K167" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L167" s="23" t="inlineStr">
@@ -14270,7 +14272,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
@@ -14279,7 +14281,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14292,7 +14294,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14315,7 +14317,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14359,7 +14361,7 @@
       </c>
       <c r="Q168" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R168" s="18" t="n">
@@ -14372,7 +14374,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14395,7 +14397,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14439,7 +14441,7 @@
       </c>
       <c r="Q169" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R169" s="2" t="n">
@@ -14452,7 +14454,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14475,7 +14477,7 @@
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14532,7 +14534,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14550,12 +14552,12 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14590,7 +14592,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
@@ -14612,7 +14614,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14635,7 +14637,7 @@
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14692,7 +14694,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14715,7 +14717,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14759,7 +14761,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R173" s="2" t="n">
@@ -14772,7 +14774,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14790,12 +14792,12 @@
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14830,7 +14832,7 @@
         </is>
       </c>
       <c r="O174" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P174" s="18" t="inlineStr">
         <is>
@@ -14839,7 +14841,7 @@
       </c>
       <c r="Q174" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R174" s="18" t="n">
@@ -14852,7 +14854,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14875,7 +14877,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14932,7 +14934,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14950,12 +14952,12 @@
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14969,14 +14971,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K176" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L176" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K176" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L176" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M176" s="24" t="inlineStr">
@@ -14990,16 +14992,16 @@
         </is>
       </c>
       <c r="O176" s="18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P176" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q176" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R176" s="18" t="n">
@@ -15012,7 +15014,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15025,17 +15027,17 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15054,9 +15056,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L177" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="L177" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M177" s="9" t="inlineStr">
@@ -15070,16 +15072,16 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q177" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R177" s="2" t="n">
@@ -15092,7 +15094,7 @@
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>step-5-preview</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C178" s="39" t="inlineStr">
@@ -15105,7 +15107,7 @@
       </c>
       <c r="E178" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
@@ -15115,7 +15117,7 @@
       </c>
       <c r="G178" s="20" t="inlineStr">
         <is>
-          <t>stepfun-ai/step-5-preview</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H178" s="21" t="inlineStr">
@@ -15129,9 +15131,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K178" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K178" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L178" s="23" t="inlineStr">
@@ -15150,7 +15152,7 @@
         </is>
       </c>
       <c r="O178" s="18" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P178" s="18" t="inlineStr">
         <is>
@@ -15159,7 +15161,7 @@
       </c>
       <c r="Q178" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R178" s="18" t="n">
@@ -15172,7 +15174,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>yi-large</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C179" s="39" t="inlineStr">
@@ -15195,7 +15197,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>01-ai/yi-large</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H179" s="21" t="inlineStr">
@@ -15246,1571 +15248,1651 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="41" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="18" t="n">
+        <v>162</v>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>yi-large</t>
+        </is>
+      </c>
+      <c r="C180" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F180" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G180" s="20" t="inlineStr">
+        <is>
+          <t>01-ai/yi-large</t>
+        </is>
+      </c>
+      <c r="H180" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I180" s="22" t="n"/>
+      <c r="J180" s="18" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K180" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L180" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M180" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N180" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O180" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P180" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q180" s="20" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R180" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="41" t="inlineStr">
         <is>
           <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="30" customHeight="1">
-      <c r="A182" s="1" t="inlineStr">
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B182" s="1" t="inlineStr">
+      <c r="B183" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="D182" s="1" t="inlineStr">
+      <c r="D183" s="1" t="inlineStr">
         <is>
           <t>Tier (1-5)</t>
         </is>
       </c>
-      <c r="E182" s="1" t="inlineStr">
+      <c r="E183" s="1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="F182" s="1" t="inlineStr">
+      <c r="F183" s="1" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr">
+      <c r="G183" s="1" t="inlineStr">
         <is>
           <t>Gateway model id</t>
         </is>
       </c>
-      <c r="H182" s="1" t="inlineStr">
+      <c r="H183" s="1" t="inlineStr">
         <is>
           <t>Context class</t>
         </is>
       </c>
-      <c r="I182" s="1" t="inlineStr">
+      <c r="I183" s="1" t="inlineStr">
         <is>
           <t>Context (tokens)</t>
         </is>
       </c>
-      <c r="J182" s="1" t="inlineStr">
+      <c r="J183" s="1" t="inlineStr">
         <is>
           <t>Modality</t>
         </is>
       </c>
-      <c r="K182" s="1" t="inlineStr">
+      <c r="K183" s="1" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="L182" s="1" t="inlineStr">
+      <c r="L183" s="1" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="M182" s="1" t="inlineStr">
+      <c r="M183" s="1" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="N182" s="1" t="inlineStr">
+      <c r="N183" s="1" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="O182" s="1" t="inlineStr">
+      <c r="O183" s="1" t="inlineStr">
         <is>
           <t>Speed (0-100)</t>
         </is>
       </c>
-      <c r="P182" s="1" t="inlineStr">
+      <c r="P183" s="1" t="inlineStr">
         <is>
           <t>Free type</t>
         </is>
       </c>
-      <c r="Q182" s="1" t="inlineStr">
+      <c r="Q183" s="1" t="inlineStr">
         <is>
           <t>Best for</t>
         </is>
       </c>
-      <c r="R182" s="1" t="inlineStr">
+      <c r="R183" s="1" t="inlineStr">
         <is>
           <t>Gateways in group</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
+      <c r="D184" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>120B</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G183" s="5" t="inlineStr">
+      <c r="G184" s="5" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="H183" s="21" t="inlineStr">
+      <c r="H184" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I183" s="7" t="n"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="7" t="n"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N183" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O183" s="2" t="n">
+      <c r="K184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N184" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="P183" s="2" t="inlineStr">
+      <c r="P184" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q183" s="5" t="inlineStr">
+      <c r="Q184" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R183" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="18" t="n">
+      <c r="R184" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B184" s="19" t="inlineStr">
+      <c r="B185" s="19" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D184" s="18" t="n">
+      <c r="D185" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E184" s="18" t="inlineStr">
+      <c r="E185" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F184" s="20" t="inlineStr">
+      <c r="F185" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G184" s="20" t="inlineStr">
+      <c r="G185" s="20" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="H184" s="6" t="inlineStr">
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I184" s="22" t="n">
+      <c r="I185" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J184" s="18" t="inlineStr">
+      <c r="J185" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M184" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N184" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="18" t="n">
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N185" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P184" s="18" t="inlineStr">
+      <c r="P185" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q184" s="20" t="inlineStr">
+      <c r="Q185" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R184" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="R185" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n">
+      <c r="D186" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G185" s="5" t="inlineStr">
+      <c r="G186" s="5" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I185" s="7" t="n">
+      <c r="I186" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="2" t="n">
+      <c r="K186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M186" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N186" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P185" s="2" t="inlineStr">
+      <c r="P186" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q185" s="5" t="inlineStr">
+      <c r="Q186" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R185" s="2" t="n">
+      <c r="R186" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="10" t="n">
+    <row r="187">
+      <c r="A187" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B186" s="11" t="inlineStr">
+      <c r="B187" s="11" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C186" s="12" t="inlineStr">
+      <c r="C187" s="12" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D186" s="10" t="n">
+      <c r="D187" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E186" s="10" t="inlineStr">
+      <c r="E187" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F186" s="13" t="inlineStr">
+      <c r="F187" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G186" s="13" t="inlineStr">
+      <c r="G187" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H186" s="30" t="inlineStr">
+      <c r="H187" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I186" s="15" t="n">
+      <c r="I187" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J186" s="10" t="inlineStr">
+      <c r="J187" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K186" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L186" s="30" t="inlineStr">
+      <c r="K187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L187" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M186" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N186" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="10" t="n">
+      <c r="M187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P186" s="10" t="inlineStr">
+      <c r="P187" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q186" s="13" t="inlineStr">
+      <c r="Q187" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R186" s="10" t="n">
+      <c r="R187" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="18" t="n">
+    <row r="188">
+      <c r="A188" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B187" s="19" t="inlineStr">
+      <c r="B188" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="C187" s="4" t="inlineStr">
+      <c r="C188" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D187" s="18" t="n">
+      <c r="D188" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E187" s="18" t="inlineStr">
+      <c r="E188" s="18" t="inlineStr">
         <is>
           <t>90B</t>
         </is>
       </c>
-      <c r="F187" s="20" t="inlineStr">
+      <c r="F188" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G187" s="20" t="inlineStr">
+      <c r="G188" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="H187" s="21" t="inlineStr">
+      <c r="H188" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I187" s="22" t="n"/>
-      <c r="J187" s="18" t="inlineStr">
+      <c r="I188" s="22" t="n"/>
+      <c r="J188" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M187" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N187" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="18" t="n">
+      <c r="K188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M188" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N188" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="P187" s="18" t="inlineStr">
+      <c r="P188" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q187" s="20" t="inlineStr">
+      <c r="Q188" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R187" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="R188" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C188" s="31" t="inlineStr">
+      <c r="C189" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D188" s="2" t="n">
+      <c r="D189" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G188" s="5" t="inlineStr">
+      <c r="G189" s="5" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I188" s="7" t="n">
+      <c r="I189" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N188" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="2" t="n">
+      <c r="K189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N189" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P188" s="2" t="inlineStr">
+      <c r="P189" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q188" s="5" t="inlineStr">
+      <c r="Q189" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R188" s="2" t="n">
+      <c r="R189" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="10" t="n">
+    <row r="190">
+      <c r="A190" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B189" s="11" t="inlineStr">
+      <c r="B190" s="11" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C189" s="32" t="inlineStr">
+      <c r="C190" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D189" s="10" t="n">
+      <c r="D190" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E189" s="10" t="inlineStr">
+      <c r="E190" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F189" s="13" t="inlineStr">
+      <c r="F190" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G189" s="13" t="inlineStr">
+      <c r="G190" s="13" t="inlineStr">
         <is>
           <t>google/gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H189" s="42" t="inlineStr">
+      <c r="H190" s="42" t="inlineStr">
         <is>
           <t>Medium (8K-32K)</t>
         </is>
       </c>
-      <c r="I189" s="15" t="n">
+      <c r="I190" s="15" t="n">
         <v>32768</v>
       </c>
-      <c r="J189" s="10" t="inlineStr">
+      <c r="J190" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K189" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L189" s="30" t="inlineStr">
+      <c r="K190" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L190" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M189" s="30" t="inlineStr">
+      <c r="M190" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N189" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="10" t="n">
+      <c r="N190" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P189" s="10" t="inlineStr">
+      <c r="P190" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q189" s="13" t="inlineStr">
+      <c r="Q190" s="13" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, fast</t>
         </is>
       </c>
-      <c r="R189" s="10" t="n">
+      <c r="R190" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="18" t="n">
+    <row r="191">
+      <c r="A191" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B190" s="19" t="inlineStr">
+      <c r="B191" s="19" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="C190" s="31" t="inlineStr">
+      <c r="C191" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D190" s="18" t="n">
+      <c r="D191" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E190" s="18" t="inlineStr">
+      <c r="E191" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F190" s="20" t="inlineStr">
+      <c r="F191" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G190" s="20" t="inlineStr">
+      <c r="G191" s="20" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="H191" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I190" s="22" t="n">
+      <c r="I191" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J190" s="18" t="inlineStr">
+      <c r="J191" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M190" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N190" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="18" t="n">
+      <c r="K191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M191" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P190" s="18" t="inlineStr">
+      <c r="P191" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q190" s="20" t="inlineStr">
+      <c r="Q191" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R190" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="R191" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C191" s="31" t="inlineStr">
+      <c r="C192" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D191" s="2" t="n">
+      <c r="D192" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
+      <c r="F192" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G191" s="5" t="inlineStr">
+      <c r="G192" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H191" s="6" t="inlineStr">
+      <c r="H192" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I191" s="7" t="n">
+      <c r="I192" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M191" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="2" t="n">
+      <c r="K192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M192" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P191" s="2" t="inlineStr">
+      <c r="P192" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q191" s="5" t="inlineStr">
+      <c r="Q192" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R191" s="2" t="n">
+      <c r="R192" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="10" t="n">
+    <row r="193">
+      <c r="A193" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B192" s="11" t="inlineStr">
+      <c r="B193" s="11" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C192" s="32" t="inlineStr">
+      <c r="C193" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D192" s="10" t="n">
+      <c r="D193" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E192" s="10" t="inlineStr">
+      <c r="E193" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F192" s="13" t="inlineStr">
+      <c r="F193" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G192" s="13" t="inlineStr">
+      <c r="G193" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H192" s="30" t="inlineStr">
+      <c r="H193" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I192" s="15" t="n">
+      <c r="I193" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J192" s="10" t="inlineStr">
+      <c r="J193" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K192" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L192" s="30" t="inlineStr">
+      <c r="K193" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L193" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M192" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="10" t="n">
+      <c r="M193" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P192" s="10" t="inlineStr">
+      <c r="P193" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q192" s="13" t="inlineStr">
+      <c r="Q193" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R192" s="10" t="n">
+      <c r="R193" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="18" t="n">
+    <row r="194">
+      <c r="A194" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B193" s="19" t="inlineStr">
+      <c r="B194" s="19" t="inlineStr">
         <is>
           <t>neva-22b</t>
         </is>
       </c>
-      <c r="C193" s="35" t="inlineStr">
+      <c r="C194" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D193" s="18" t="n">
+      <c r="D194" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E193" s="18" t="inlineStr">
+      <c r="E194" s="18" t="inlineStr">
         <is>
           <t>22B</t>
         </is>
       </c>
-      <c r="F193" s="20" t="inlineStr">
+      <c r="F194" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G193" s="20" t="inlineStr">
+      <c r="G194" s="20" t="inlineStr">
         <is>
           <t>nvidia/neva-22b</t>
         </is>
       </c>
-      <c r="H193" s="21" t="inlineStr">
+      <c r="H194" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I193" s="22" t="n"/>
-      <c r="J193" s="18" t="inlineStr">
+      <c r="I194" s="22" t="n"/>
+      <c r="J194" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M193" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="18" t="n">
+      <c r="K194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M194" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="P193" s="18" t="inlineStr">
+      <c r="P194" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q193" s="20" t="inlineStr">
+      <c r="Q194" s="20" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R193" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="R194" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="C194" s="35" t="inlineStr">
+      <c r="C195" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D194" s="2" t="n">
+      <c r="D195" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F194" s="5" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G194" s="5" t="inlineStr">
+      <c r="G195" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="H194" s="6" t="inlineStr">
+      <c r="H195" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I194" s="7" t="n">
+      <c r="I195" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="2" t="n">
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P194" s="2" t="inlineStr">
+      <c r="P195" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q194" s="5" t="inlineStr">
+      <c r="Q195" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R194" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="18" t="n">
+      <c r="R195" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B195" s="19" t="inlineStr">
+      <c r="B196" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="C195" s="37" t="inlineStr">
+      <c r="C196" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D195" s="18" t="n">
+      <c r="D196" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E195" s="18" t="inlineStr">
+      <c r="E196" s="18" t="inlineStr">
         <is>
           <t>11B</t>
         </is>
       </c>
-      <c r="F195" s="20" t="inlineStr">
+      <c r="F196" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G195" s="20" t="inlineStr">
+      <c r="G196" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="H195" s="21" t="inlineStr">
+      <c r="H196" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I195" s="22" t="n"/>
-      <c r="J195" s="18" t="inlineStr">
+      <c r="I196" s="22" t="n"/>
+      <c r="J196" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N195" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="18" t="n">
+      <c r="K196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M196" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="P195" s="18" t="inlineStr">
+      <c r="P196" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q195" s="20" t="inlineStr">
+      <c r="Q196" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R195" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="R196" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>fuyu-8b</t>
         </is>
       </c>
-      <c r="C196" s="37" t="inlineStr">
+      <c r="C197" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D196" s="2" t="n">
+      <c r="D197" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>8B</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
+      <c r="F197" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G196" s="5" t="inlineStr">
+      <c r="G197" s="5" t="inlineStr">
         <is>
           <t>adept/fuyu-8b</t>
         </is>
       </c>
-      <c r="H196" s="21" t="inlineStr">
+      <c r="H197" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I196" s="7" t="n"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="7" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M196" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N196" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="2" t="n">
+      <c r="K197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M197" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N197" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P196" s="2" t="inlineStr">
+      <c r="P197" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q196" s="5" t="inlineStr">
+      <c r="Q197" s="5" t="inlineStr">
         <is>
           <t>extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R196" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="18" t="n">
+      <c r="R197" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B197" s="19" t="inlineStr">
+      <c r="B198" s="19" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl</t>
         </is>
       </c>
-      <c r="C197" s="39" t="inlineStr">
+      <c r="C198" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D197" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" s="18" t="inlineStr">
+      <c r="D198" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F197" s="20" t="inlineStr">
+      <c r="F198" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G197" s="20" t="inlineStr">
+      <c r="G198" s="20" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl:free</t>
         </is>
       </c>
-      <c r="H197" s="6" t="inlineStr">
+      <c r="H198" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I197" s="22" t="n">
+      <c r="I198" s="22" t="n">
         <v>1000000</v>
       </c>
-      <c r="J197" s="18" t="inlineStr">
+      <c r="J198" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K197" s="8" t="inlineStr">
+      <c r="K198" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L197" s="8" t="inlineStr">
+      <c r="L198" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M197" s="8" t="inlineStr">
+      <c r="M198" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N197" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="18" t="n">
+      <c r="N198" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P197" s="18" t="inlineStr">
+      <c r="P198" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q197" s="20" t="inlineStr">
+      <c r="Q198" s="20" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R197" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="R198" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>kosmos-2</t>
         </is>
       </c>
-      <c r="C198" s="39" t="inlineStr">
+      <c r="C199" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="D199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F198" s="5" t="inlineStr">
+      <c r="F199" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G198" s="5" t="inlineStr">
+      <c r="G199" s="5" t="inlineStr">
         <is>
           <t>microsoft/kosmos-2</t>
         </is>
       </c>
-      <c r="H198" s="21" t="inlineStr">
+      <c r="H199" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I198" s="7" t="n"/>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="I199" s="7" t="n"/>
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M198" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N198" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O198" s="2" t="n">
+      <c r="K199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M199" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N199" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P198" s="2" t="inlineStr">
+      <c r="P199" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q198" s="5" t="inlineStr">
+      <c r="Q199" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R198" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="18" t="n">
+      <c r="R199" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B199" s="19" t="inlineStr">
+      <c r="B200" s="19" t="inlineStr">
         <is>
           <t>phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="C199" s="39" t="inlineStr">
+      <c r="C200" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D199" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="18" t="inlineStr">
+      <c r="D200" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F199" s="20" t="inlineStr">
+      <c r="F200" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G199" s="20" t="inlineStr">
+      <c r="G200" s="20" t="inlineStr">
         <is>
           <t>microsoft/phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="H199" s="21" t="inlineStr">
+      <c r="H200" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I199" s="22" t="n"/>
-      <c r="J199" s="18" t="inlineStr">
+      <c r="I200" s="22" t="n"/>
+      <c r="J200" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M199" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N199" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O199" s="18" t="n">
+      <c r="K200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M200" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N200" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O200" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="P199" s="18" t="inlineStr">
+      <c r="P200" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q199" s="20" t="inlineStr">
+      <c r="Q200" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R199" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="R200" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>vila</t>
         </is>
       </c>
-      <c r="C200" s="39" t="inlineStr">
+      <c r="C201" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D200" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="D201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F200" s="5" t="inlineStr">
+      <c r="F201" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G200" s="5" t="inlineStr">
+      <c r="G201" s="5" t="inlineStr">
         <is>
           <t>nvidia/vila</t>
         </is>
       </c>
-      <c r="H200" s="21" t="inlineStr">
+      <c r="H201" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I200" s="7" t="n"/>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="I201" s="7" t="n"/>
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M200" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N200" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O200" s="2" t="n">
+      <c r="K201" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L201" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M201" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N201" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P200" s="2" t="inlineStr">
+      <c r="P201" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q200" s="5" t="inlineStr">
+      <c r="Q201" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R200" s="2" t="n">
+      <c r="R201" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R179"/>
+  <autoFilter ref="A1:R180"/>
   <mergeCells count="1">
-    <mergeCell ref="A181:R181"/>
+    <mergeCell ref="A182:R182"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O179">
+  <conditionalFormatting sqref="O2:O180">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17046,7 +17128,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-21T17:15:55Z (source: live)</t>
+          <t>Registry updated 2026-10-21T21:45:54Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17128,7 +17128,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-21T21:45:54Z (source: live)</t>
+          <t>Registry updated 2026-10-22T04:53:57Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17128,7 +17128,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-22T04:53:57Z (source: live)</t>
+          <t>Registry updated 2026-10-22T11:57:56Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>minimax-m3.1-flash</t>
+          <t>dots-3-note-preview</t>
         </is>
       </c>
       <c r="C129" s="39" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>minimax/minimax-m3.1-flash:free</t>
+          <t>dots-studio/dots-3-note-preview:free</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>1000000</v>
+        <v>512000</v>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Q129" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>dots-3-note-preview</t>
+          <t>wan-v2-6</t>
         </is>
       </c>
       <c r="C130" s="39" t="inlineStr">
@@ -11220,12 +11220,12 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>dots-studio/dots-3-note-preview:free</t>
+          <t>wanx/wan-v2-6</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>512000</v>
+        <v>400000</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K130" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M130" s="9" t="inlineStr">
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R130" s="2" t="n">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>wan-v2-6</t>
+          <t>flint-v1.0</t>
         </is>
       </c>
       <c r="C131" s="39" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-6</t>
+          <t>recursive/flint-v1.0:free</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -11316,21 +11316,21 @@
         </is>
       </c>
       <c r="I131" s="22" t="n">
-        <v>400000</v>
+        <v>262144</v>
       </c>
       <c r="J131" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K131" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L131" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K131" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M131" s="24" t="inlineStr">
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="O131" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P131" s="18" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="Q131" s="20" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R131" s="18" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>flint-v1.0</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="C132" s="39" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>recursive/flint-v1.0:free</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
@@ -11426,16 +11426,16 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="C133" s="39" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>laguna-s-2.1</t>
         </is>
       </c>
       <c r="C134" s="39" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>poolside/laguna-s-2.1:free</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
@@ -11574,9 +11574,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L134" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L134" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M134" s="9" t="inlineStr">
@@ -11590,16 +11590,16 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>agent, long_doc</t>
         </is>
       </c>
       <c r="R134" s="2" t="n">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>laguna-s-2.1</t>
+          <t>laguna-xs-2.1</t>
         </is>
       </c>
       <c r="C135" s="39" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="G135" s="20" t="inlineStr">
         <is>
-          <t>poolside/laguna-s-2.1:free</t>
+          <t>poolside/laguna-xs-2.1:free</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -11685,169 +11685,169 @@
         </is>
       </c>
       <c r="R135" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="25" t="n">
+        <v>118</v>
+      </c>
+      <c r="B136" s="26" t="inlineStr">
+        <is>
+          <t>laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="C136" s="40" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D136" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F136" s="27" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G136" s="27" t="inlineStr">
+        <is>
+          <t>poolside/laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I136" s="28" t="n"/>
+      <c r="J136" s="25" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K136" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L136" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M136" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="P136" s="25" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q136" s="27" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R136" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>laguna-xs-2.1</t>
-        </is>
-      </c>
-      <c r="C136" s="39" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>mistral-vibe-cli-fast</t>
+        </is>
+      </c>
+      <c r="C137" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="D137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>poolside/laguna-xs-2.1:free</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>mistral-vibe-cli-fast</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I136" s="7" t="n">
+      <c r="I137" s="7" t="n">
         <v>262144</v>
       </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K136" s="8" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K137" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L136" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M136" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N136" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O136" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="P136" s="2" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q136" s="5" t="inlineStr">
-        <is>
-          <t>agent, long_doc</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="B137" s="11" t="inlineStr">
-        <is>
-          <t>laguna-xs-2.1</t>
-        </is>
-      </c>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F137" s="13" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G137" s="13" t="inlineStr">
-        <is>
-          <t>poolside/laguna-xs-2.1</t>
-        </is>
-      </c>
-      <c r="H137" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I137" s="15" t="n"/>
-      <c r="J137" s="10" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K137" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L137" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M137" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N137" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O137" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="P137" s="10" t="inlineStr">
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M137" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q137" s="13" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R137" s="10" t="n">
-        <v>2</v>
+      <c r="Q137" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-fast</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-fast</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="Q138" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R138" s="18" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12052,11 +12052,11 @@
         </is>
       </c>
       <c r="I140" s="22" t="n">
-        <v>262144</v>
+        <v>256000</v>
       </c>
       <c r="J140" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K140" s="8" t="inlineStr">
@@ -12074,9 +12074,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N140" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N140" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O140" s="18" t="n">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="Q140" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R140" s="18" t="n">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>cohere/north-mini-code:free</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -12228,32 +12228,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L142" s="8" t="inlineStr">
+      <c r="L142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N142" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N142" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O142" s="18" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P142" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12289,20 +12289,20 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
-        </is>
-      </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
+          <t>openrouter/free</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>256000</v>
+        <v>200000</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K143" s="8" t="inlineStr">
@@ -12310,9 +12310,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M143" s="9" t="inlineStr">
@@ -12320,9 +12320,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N143" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O143" s="2" t="n">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="F144" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
+          <t>openai/gpt-live-1</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
@@ -12380,21 +12380,21 @@
         </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>200000</v>
+        <v>128000</v>
       </c>
       <c r="J144" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K144" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K144" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L144" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M144" s="24" t="inlineStr">
@@ -12408,7 +12408,7 @@
         </is>
       </c>
       <c r="O144" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P144" s="18" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="Q144" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R144" s="18" t="n">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12448,35 +12448,35 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>voxtral-small-2507</t>
+        </is>
+      </c>
+      <c r="H145" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>128000</v>
+        <v>32768</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K145" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L145" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K145" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -12490,16 +12490,16 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R145" s="2" t="n">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12612,35 +12612,35 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
-        </is>
-      </c>
-      <c r="H147" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>alibaba/happyhorse-1.1</t>
+        </is>
+      </c>
+      <c r="H147" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
         </is>
       </c>
       <c r="I147" s="7" t="n">
-        <v>32768</v>
+        <v>4096</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K147" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L147" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L147" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M147" s="9" t="inlineStr">
@@ -12654,16 +12654,16 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R147" s="2" t="n">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="J148" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K148" s="24" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="Q148" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R148" s="18" t="n">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12884,9 +12884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L150" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M150" s="24" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="Q150" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R150" s="18" t="n">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -12966,9 +12966,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L151" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M151" s="9" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R151" s="2" t="n">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K154" s="24" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="Q154" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R154" s="18" t="n">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>wanx/wan-v3-0</t>
         </is>
       </c>
       <c r="H155" s="38" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13350,35 +13350,33 @@
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
-        </is>
-      </c>
-      <c r="H156" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
-        </is>
-      </c>
-      <c r="I156" s="22" t="n">
-        <v>4096</v>
-      </c>
+          <t>nvidia/ai-synthetic-video-detector</t>
+        </is>
+      </c>
+      <c r="H156" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="n"/>
       <c r="J156" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K156" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L156" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K156" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L156" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M156" s="24" t="inlineStr">
@@ -13392,16 +13390,16 @@
         </is>
       </c>
       <c r="O156" s="18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P156" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q156" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R156" s="18" t="n">
@@ -13414,7 +13412,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13432,12 +13430,12 @@
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13472,7 +13470,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
@@ -13494,7 +13492,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13517,7 +13515,7 @@
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13574,7 +13572,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13597,7 +13595,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13654,7 +13652,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13672,12 +13670,12 @@
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13712,7 +13710,7 @@
         </is>
       </c>
       <c r="O160" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P160" s="18" t="inlineStr">
         <is>
@@ -13734,7 +13732,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13752,12 +13750,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13792,7 +13790,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
@@ -13814,7 +13812,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13837,7 +13835,7 @@
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13894,7 +13892,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13917,7 +13915,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13974,7 +13972,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13992,12 +13990,12 @@
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14026,13 +14024,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N164" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N164" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O164" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
@@ -14041,7 +14039,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14054,7 +14052,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14077,7 +14075,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14106,9 +14104,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N165" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N165" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O165" s="2" t="n">
@@ -14121,7 +14119,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14134,7 +14132,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14147,7 +14145,7 @@
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -14157,7 +14155,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14171,9 +14169,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K166" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K166" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -14192,7 +14190,7 @@
         </is>
       </c>
       <c r="O166" s="18" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P166" s="18" t="inlineStr">
         <is>
@@ -14201,7 +14199,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14214,7 +14212,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14227,7 +14225,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -14237,7 +14235,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14251,9 +14249,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K167" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K167" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L167" s="23" t="inlineStr">
@@ -14272,7 +14270,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
@@ -14281,7 +14279,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14294,7 +14292,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14317,7 +14315,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14361,7 +14359,7 @@
       </c>
       <c r="Q168" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R168" s="18" t="n">
@@ -14374,7 +14372,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14397,7 +14395,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14441,7 +14439,7 @@
       </c>
       <c r="Q169" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R169" s="2" t="n">
@@ -14454,7 +14452,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14477,7 +14475,7 @@
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14534,7 +14532,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14552,12 +14550,12 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14592,7 +14590,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
@@ -14614,7 +14612,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14637,7 +14635,7 @@
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14694,7 +14692,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14717,7 +14715,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14761,7 +14759,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R173" s="2" t="n">
@@ -14774,7 +14772,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14792,12 +14790,12 @@
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14832,7 +14830,7 @@
         </is>
       </c>
       <c r="O174" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P174" s="18" t="inlineStr">
         <is>
@@ -14841,7 +14839,7 @@
       </c>
       <c r="Q174" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R174" s="18" t="n">
@@ -14854,7 +14852,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14877,7 +14875,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14934,7 +14932,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14952,12 +14950,12 @@
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14971,14 +14969,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K176" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L176" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K176" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L176" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M176" s="24" t="inlineStr">
@@ -14992,16 +14990,16 @@
         </is>
       </c>
       <c r="O176" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P176" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q176" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R176" s="18" t="n">
@@ -15014,7 +15012,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15027,17 +15025,17 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15056,9 +15054,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L177" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L177" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M177" s="9" t="inlineStr">
@@ -15072,16 +15070,16 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q177" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R177" s="2" t="n">
@@ -15094,7 +15092,7 @@
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C178" s="39" t="inlineStr">
@@ -15107,7 +15105,7 @@
       </c>
       <c r="E178" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
@@ -15117,7 +15115,7 @@
       </c>
       <c r="G178" s="20" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H178" s="21" t="inlineStr">
@@ -15131,9 +15129,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K178" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K178" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L178" s="23" t="inlineStr">
@@ -15152,7 +15150,7 @@
         </is>
       </c>
       <c r="O178" s="18" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P178" s="18" t="inlineStr">
         <is>
@@ -15161,7 +15159,7 @@
       </c>
       <c r="Q178" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R178" s="18" t="n">
@@ -15174,7 +15172,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>step-5-preview</t>
+          <t>yi-large</t>
         </is>
       </c>
       <c r="C179" s="39" t="inlineStr">
@@ -15197,7 +15195,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>stepfun-ai/step-5-preview</t>
+          <t>01-ai/yi-large</t>
         </is>
       </c>
       <c r="H179" s="21" t="inlineStr">
@@ -15248,1651 +15246,1571 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="18" t="n">
-        <v>162</v>
-      </c>
-      <c r="B180" s="19" t="inlineStr">
-        <is>
-          <t>yi-large</t>
-        </is>
-      </c>
-      <c r="C180" s="39" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="41" t="inlineStr">
+        <is>
+          <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>Tier (1-5)</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G182" s="1" t="inlineStr">
+        <is>
+          <t>Gateway model id</t>
+        </is>
+      </c>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>Context class</t>
+        </is>
+      </c>
+      <c r="I182" s="1" t="inlineStr">
+        <is>
+          <t>Context (tokens)</t>
+        </is>
+      </c>
+      <c r="J182" s="1" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="K182" s="1" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="L182" s="1" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="M182" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="N182" s="1" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="O182" s="1" t="inlineStr">
+        <is>
+          <t>Speed (0-100)</t>
+        </is>
+      </c>
+      <c r="P182" s="1" t="inlineStr">
+        <is>
+          <t>Free type</t>
+        </is>
+      </c>
+      <c r="Q182" s="1" t="inlineStr">
+        <is>
+          <t>Best for</t>
+        </is>
+      </c>
+      <c r="R182" s="1" t="inlineStr">
+        <is>
+          <t>Gateways in group</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>nemotron-3.5-super-vl-120b-a12b</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>120B</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
+        </is>
+      </c>
+      <c r="H183" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I183" s="7" t="n"/>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N183" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q183" s="5" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D184" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E184" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F184" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G184" s="20" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I184" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J184" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M184" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N184" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P184" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q184" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R184" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I185" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N185" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q185" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E186" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F186" s="13" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G186" s="13" t="inlineStr">
+        <is>
+          <t>google/gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H186" s="30" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I186" s="15" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J186" s="10" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L186" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="P186" s="10" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q186" s="13" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R186" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D187" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E187" s="18" t="inlineStr">
+        <is>
+          <t>90B</t>
+        </is>
+      </c>
+      <c r="F187" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G187" s="20" t="inlineStr">
+        <is>
+          <t>meta/llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="H187" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I187" s="22" t="n"/>
+      <c r="J187" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M187" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P187" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q187" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R187" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="C188" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N188" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q188" s="5" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="C189" s="32" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E189" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F189" s="13" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G189" s="13" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="H189" s="42" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
+        </is>
+      </c>
+      <c r="I189" s="15" t="n">
+        <v>32768</v>
+      </c>
+      <c r="J189" s="10" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K189" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L189" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M189" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N189" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="P189" s="10" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q189" s="13" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, fast</t>
+        </is>
+      </c>
+      <c r="R189" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B190" s="19" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image</t>
+        </is>
+      </c>
+      <c r="C190" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D190" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E190" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F190" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G190" s="20" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I190" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J190" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M190" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N190" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P190" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q190" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R190" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="C191" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M191" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q191" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="C192" s="32" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F192" s="13" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G192" s="13" t="inlineStr">
+        <is>
+          <t>google/gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="H192" s="30" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I192" s="15" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J192" s="10" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L192" s="30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="P192" s="10" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q192" s="13" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R192" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>neva-22b</t>
+        </is>
+      </c>
+      <c r="C193" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="D193" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E193" s="18" t="inlineStr">
+        <is>
+          <t>22B</t>
+        </is>
+      </c>
+      <c r="F193" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G193" s="20" t="inlineStr">
+        <is>
+          <t>nvidia/neva-22b</t>
+        </is>
+      </c>
+      <c r="H193" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I193" s="22" t="n"/>
+      <c r="J193" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="P193" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q193" s="20" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R193" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="C194" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q194" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>llama-3.2-11b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="C195" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="D195" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" s="18" t="inlineStr">
+        <is>
+          <t>11B</t>
+        </is>
+      </c>
+      <c r="F195" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G195" s="20" t="inlineStr">
+        <is>
+          <t>meta/llama-3.2-11b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="H195" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I195" s="22" t="n"/>
+      <c r="J195" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="P195" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q195" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, fast</t>
+        </is>
+      </c>
+      <c r="R195" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>fuyu-8b</t>
+        </is>
+      </c>
+      <c r="C196" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>adept/fuyu-8b</t>
+        </is>
+      </c>
+      <c r="H196" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q196" s="5" t="inlineStr">
+        <is>
+          <t>extraction, agent, fast</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>nemotron-3.5-super-vl</t>
+        </is>
+      </c>
+      <c r="C197" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D180" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" s="18" t="inlineStr">
+      <c r="D197" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F180" s="20" t="inlineStr">
+      <c r="F197" s="20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G197" s="20" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-super-vl:free</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I197" s="22" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J197" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K197" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L197" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M197" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N197" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="P197" s="18" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q197" s="20" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent, long_doc</t>
+        </is>
+      </c>
+      <c r="R197" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>kosmos-2</t>
+        </is>
+      </c>
+      <c r="C198" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G180" s="20" t="inlineStr">
-        <is>
-          <t>01-ai/yi-large</t>
-        </is>
-      </c>
-      <c r="H180" s="21" t="inlineStr">
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>microsoft/kosmos-2</t>
+        </is>
+      </c>
+      <c r="H198" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I180" s="22" t="n"/>
-      <c r="J180" s="18" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K180" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L180" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M180" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N180" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O180" s="18" t="n">
+      <c r="I198" s="7" t="n"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P180" s="18" t="inlineStr">
+      <c r="P198" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q180" s="20" t="inlineStr">
+      <c r="Q198" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R180" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="41" t="inlineStr">
-        <is>
-          <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B183" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C183" s="1" t="inlineStr">
-        <is>
-          <t>Intelligence</t>
-        </is>
-      </c>
-      <c r="D183" s="1" t="inlineStr">
-        <is>
-          <t>Tier (1-5)</t>
-        </is>
-      </c>
-      <c r="E183" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F183" s="1" t="inlineStr">
-        <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="G183" s="1" t="inlineStr">
-        <is>
-          <t>Gateway model id</t>
-        </is>
-      </c>
-      <c r="H183" s="1" t="inlineStr">
-        <is>
-          <t>Context class</t>
-        </is>
-      </c>
-      <c r="I183" s="1" t="inlineStr">
-        <is>
-          <t>Context (tokens)</t>
-        </is>
-      </c>
-      <c r="J183" s="1" t="inlineStr">
-        <is>
-          <t>Modality</t>
-        </is>
-      </c>
-      <c r="K183" s="1" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="L183" s="1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="M183" s="1" t="inlineStr">
-        <is>
-          <t>Reasoning</t>
-        </is>
-      </c>
-      <c r="N183" s="1" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
-      </c>
-      <c r="O183" s="1" t="inlineStr">
-        <is>
-          <t>Speed (0-100)</t>
-        </is>
-      </c>
-      <c r="P183" s="1" t="inlineStr">
-        <is>
-          <t>Free type</t>
-        </is>
-      </c>
-      <c r="Q183" s="1" t="inlineStr">
-        <is>
-          <t>Best for</t>
-        </is>
-      </c>
-      <c r="R183" s="1" t="inlineStr">
-        <is>
-          <t>Gateways in group</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>nemotron-3.5-super-vl-120b-a12b</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>120B</t>
-        </is>
-      </c>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="R198" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B199" s="19" t="inlineStr">
+        <is>
+          <t>phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="C199" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D199" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F199" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
-        </is>
-      </c>
-      <c r="H184" s="21" t="inlineStr">
+      <c r="G199" s="20" t="inlineStr">
+        <is>
+          <t>microsoft/phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="H199" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I184" s="7" t="n"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I199" s="22" t="n"/>
+      <c r="J199" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N184" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="P184" s="2" t="inlineStr">
+      <c r="K199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M199" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N199" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P199" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q184" s="5" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R184" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B185" s="19" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D185" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E185" s="18" t="inlineStr">
+      <c r="Q199" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R199" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>vila</t>
+        </is>
+      </c>
+      <c r="C200" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F185" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G185" s="20" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image</t>
-        </is>
-      </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I185" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J185" s="18" t="inlineStr">
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>nvidia/vila</t>
+        </is>
+      </c>
+      <c r="H200" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I200" s="7" t="n"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P185" s="18" t="inlineStr">
+      <c r="K200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q185" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R185" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I186" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M186" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N186" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P186" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q186" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R186" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="C187" s="12" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E187" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F187" s="13" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G187" s="13" t="inlineStr">
-        <is>
-          <t>google/gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="H187" s="30" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I187" s="15" t="n">
-        <v>65536</v>
-      </c>
-      <c r="J187" s="10" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L187" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="P187" s="10" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q187" s="13" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R187" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B188" s="19" t="inlineStr">
-        <is>
-          <t>llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D188" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E188" s="18" t="inlineStr">
-        <is>
-          <t>90B</t>
-        </is>
-      </c>
-      <c r="F188" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G188" s="20" t="inlineStr">
-        <is>
-          <t>meta/llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H188" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I188" s="22" t="n"/>
-      <c r="J188" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="P188" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q188" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R188" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="C189" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I189" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J189" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N189" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P189" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q189" s="5" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R189" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="C190" s="32" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D190" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E190" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F190" s="13" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G190" s="13" t="inlineStr">
-        <is>
-          <t>google/gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="H190" s="42" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
-        </is>
-      </c>
-      <c r="I190" s="15" t="n">
-        <v>32768</v>
-      </c>
-      <c r="J190" s="10" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L190" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M190" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="P190" s="10" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q190" s="13" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, fast</t>
-        </is>
-      </c>
-      <c r="R190" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B191" s="19" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="C191" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D191" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E191" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F191" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G191" s="20" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="H191" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I191" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J191" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P191" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q191" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R191" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="C192" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I192" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J192" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P192" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q192" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R192" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B193" s="11" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="C193" s="32" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D193" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E193" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F193" s="13" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G193" s="13" t="inlineStr">
-        <is>
-          <t>google/gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="H193" s="30" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I193" s="15" t="n">
-        <v>65536</v>
-      </c>
-      <c r="J193" s="10" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L193" s="30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="P193" s="10" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q193" s="13" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R193" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B194" s="19" t="inlineStr">
-        <is>
-          <t>neva-22b</t>
-        </is>
-      </c>
-      <c r="C194" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D194" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E194" s="18" t="inlineStr">
-        <is>
-          <t>22B</t>
-        </is>
-      </c>
-      <c r="F194" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G194" s="20" t="inlineStr">
-        <is>
-          <t>nvidia/neva-22b</t>
-        </is>
-      </c>
-      <c r="H194" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I194" s="22" t="n"/>
-      <c r="J194" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="18" t="n">
-        <v>33</v>
-      </c>
-      <c r="P194" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q194" s="20" t="inlineStr">
+      <c r="Q200" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R194" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="C195" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="H195" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I195" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P195" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q195" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R195" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B196" s="19" t="inlineStr">
-        <is>
-          <t>llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C196" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="D196" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E196" s="18" t="inlineStr">
-        <is>
-          <t>11B</t>
-        </is>
-      </c>
-      <c r="F196" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G196" s="20" t="inlineStr">
-        <is>
-          <t>meta/llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H196" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I196" s="22" t="n"/>
-      <c r="J196" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="18" t="n">
-        <v>41</v>
-      </c>
-      <c r="P196" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q196" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, fast</t>
-        </is>
-      </c>
-      <c r="R196" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>fuyu-8b</t>
-        </is>
-      </c>
-      <c r="C197" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>adept/fuyu-8b</t>
-        </is>
-      </c>
-      <c r="H197" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I197" s="7" t="n"/>
-      <c r="J197" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="P197" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q197" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent, fast</t>
-        </is>
-      </c>
-      <c r="R197" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B198" s="19" t="inlineStr">
-        <is>
-          <t>nemotron-3.5-super-vl</t>
-        </is>
-      </c>
-      <c r="C198" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D198" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F198" s="20" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
-      <c r="G198" s="20" t="inlineStr">
-        <is>
-          <t>nvidia/nemotron-3.5-super-vl:free</t>
-        </is>
-      </c>
-      <c r="H198" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I198" s="22" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="J198" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K198" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L198" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M198" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N198" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O198" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="P198" s="18" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q198" s="20" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, agent, long_doc</t>
-        </is>
-      </c>
-      <c r="R198" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>kosmos-2</t>
-        </is>
-      </c>
-      <c r="C199" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>microsoft/kosmos-2</t>
-        </is>
-      </c>
-      <c r="H199" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I199" s="7" t="n"/>
-      <c r="J199" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O199" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="P199" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q199" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R199" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B200" s="19" t="inlineStr">
-        <is>
-          <t>phi-3-vision-128k-instruct</t>
-        </is>
-      </c>
-      <c r="C200" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D200" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F200" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G200" s="20" t="inlineStr">
-        <is>
-          <t>microsoft/phi-3-vision-128k-instruct</t>
-        </is>
-      </c>
-      <c r="H200" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I200" s="22" t="n"/>
-      <c r="J200" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M200" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N200" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O200" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="P200" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q200" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R200" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>vila</t>
-        </is>
-      </c>
-      <c r="C201" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/vila</t>
-        </is>
-      </c>
-      <c r="H201" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I201" s="7" t="n"/>
-      <c r="J201" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K201" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L201" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M201" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N201" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O201" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="P201" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q201" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R201" s="2" t="n">
+      <c r="R200" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R180"/>
+  <autoFilter ref="A1:R179"/>
   <mergeCells count="1">
-    <mergeCell ref="A182:R182"/>
+    <mergeCell ref="A181:R181"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O180">
+  <conditionalFormatting sqref="O2:O179">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17128,7 +17046,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-22T11:57:56Z (source: live)</t>
+          <t>Registry updated 2026-10-22T17:14:12Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R200"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>nemotron-parse</t>
+          <t>nemotron-3.5-bolt-e4b</t>
         </is>
       </c>
       <c r="C121" s="39" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="G121" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse</t>
+          <t>nvidia/nemotron-3.5-bolt-e4b</t>
         </is>
       </c>
       <c r="H121" s="21" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>nemotron-parse-2.0</t>
+          <t>nemotron-parse</t>
         </is>
       </c>
       <c r="C122" s="39" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse-2.0</t>
+          <t>nvidia/nemotron-parse</t>
         </is>
       </c>
       <c r="H122" s="21" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
-          <t>lfm-2.5-2.6b</t>
+          <t>nemotron-parse-2.0</t>
         </is>
       </c>
       <c r="C123" s="39" t="inlineStr">
@@ -10645,45 +10645,43 @@
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
-          <t>2.6B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G123" s="20" t="inlineStr">
         <is>
-          <t>liquid/lfm-2.5-2.6b:free</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>65536</v>
-      </c>
+          <t>nvidia/nemotron-parse-2.0</t>
+        </is>
+      </c>
+      <c r="H123" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I123" s="22" t="n"/>
       <c r="J123" s="18" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K123" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M123" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K123" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L123" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M123" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="N123" s="24" t="inlineStr">
@@ -10692,16 +10690,16 @@
         </is>
       </c>
       <c r="O123" s="18" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="P123" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q123" s="20" t="inlineStr">
         <is>
-          <t>long_doc, fast</t>
+          <t>reasoning, extraction, agent</t>
         </is>
       </c>
       <c r="R123" s="18" t="n">
@@ -10714,404 +10712,404 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
+          <t>lfm-2.5-2.6b</t>
+        </is>
+      </c>
+      <c r="C124" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2.6B</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>liquid/lfm-2.5-2.6b:free</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C124" s="39" t="inlineStr">
+      <c r="C125" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="D125" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G125" s="20" t="inlineStr">
         <is>
           <t>google/lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H125" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I124" s="7" t="n">
+      <c r="I125" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J125" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
+      <c r="K125" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="n">
+      <c r="M125" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O125" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P124" s="2" t="inlineStr">
+      <c r="P125" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q124" s="5" t="inlineStr">
+      <c r="Q125" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R124" s="2" t="n">
+      <c r="R125" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="10" t="n">
-        <v>109</v>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="B126" s="26" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C125" s="40" t="inlineStr">
+      <c r="C126" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D125" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="10" t="inlineStr">
+      <c r="D126" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F125" s="13" t="inlineStr">
+      <c r="F126" s="27" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G125" s="13" t="inlineStr">
+      <c r="G126" s="27" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H125" s="14" t="inlineStr">
+      <c r="H126" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I125" s="15" t="n"/>
-      <c r="J125" s="10" t="inlineStr">
+      <c r="I126" s="28" t="n"/>
+      <c r="J126" s="25" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K125" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L125" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M125" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N125" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O125" s="10" t="n">
+      <c r="K126" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L126" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M126" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O126" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="P125" s="10" t="inlineStr">
+      <c r="P126" s="25" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q125" s="13" t="inlineStr">
+      <c r="Q126" s="27" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R125" s="10" t="n">
+      <c r="R126" s="25" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="18" t="n">
-        <v>110</v>
-      </c>
-      <c r="B126" s="19" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C126" s="39" t="inlineStr">
+      <c r="C127" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D126" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="18" t="inlineStr">
+      <c r="D127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F126" s="20" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G126" s="20" t="inlineStr">
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>google/lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H126" s="6" t="inlineStr">
+      <c r="H127" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I126" s="22" t="n">
+      <c r="I127" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J126" s="18" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K126" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L126" s="8" t="inlineStr">
+      <c r="K127" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L127" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M126" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N126" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O126" s="18" t="n">
+      <c r="M127" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="P126" s="18" t="inlineStr">
+      <c r="P127" s="2" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q126" s="20" t="inlineStr">
+      <c r="Q127" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R126" s="18" t="n">
+      <c r="R127" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="25" t="n">
-        <v>110</v>
-      </c>
-      <c r="B127" s="26" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C127" s="40" t="inlineStr">
+      <c r="C128" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D127" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="25" t="inlineStr">
+      <c r="D128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F127" s="27" t="inlineStr">
+      <c r="F128" s="13" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G127" s="27" t="inlineStr">
+      <c r="G128" s="13" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H127" s="14" t="inlineStr">
+      <c r="H128" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I127" s="28" t="n"/>
-      <c r="J127" s="25" t="inlineStr">
+      <c r="I128" s="15" t="n"/>
+      <c r="J128" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K127" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L127" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M127" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N127" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O127" s="25" t="n">
+      <c r="K128" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L128" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M128" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N128" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O128" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="P127" s="25" t="inlineStr">
+      <c r="P128" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q127" s="27" t="inlineStr">
+      <c r="Q128" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R127" s="25" t="n">
+      <c r="R128" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C128" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>fastrouter/auto</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I128" s="7" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O128" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="P128" s="2" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q128" s="5" t="inlineStr">
-        <is>
-          <t>vision, long_doc</t>
-        </is>
-      </c>
-      <c r="R128" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -11120,7 +11118,7 @@
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>dots-3-note-preview</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C129" s="39" t="inlineStr">
@@ -11138,12 +11136,12 @@
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>dots-studio/dots-3-note-preview:free</t>
+          <t>fastrouter/auto</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -11152,21 +11150,21 @@
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>512000</v>
+        <v>1000000</v>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K129" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L129" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K129" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L129" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M129" s="24" t="inlineStr">
@@ -11180,7 +11178,7 @@
         </is>
       </c>
       <c r="O129" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P129" s="18" t="inlineStr">
         <is>
@@ -11189,7 +11187,7 @@
       </c>
       <c r="Q129" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -11202,7 +11200,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-6</t>
+          <t>dots-3-note-preview</t>
         </is>
       </c>
       <c r="C130" s="39" t="inlineStr">
@@ -11220,12 +11218,12 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-6</t>
+          <t>dots-studio/dots-3-note-preview:free</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -11234,21 +11232,21 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>400000</v>
+        <v>512000</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K130" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M130" s="9" t="inlineStr">
@@ -11262,7 +11260,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
@@ -11271,7 +11269,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R130" s="2" t="n">
@@ -11284,7 +11282,7 @@
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>flint-v1.0</t>
+          <t>wan-v2-6</t>
         </is>
       </c>
       <c r="C131" s="39" t="inlineStr">
@@ -11302,12 +11300,12 @@
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>recursive/flint-v1.0:free</t>
+          <t>wanx/wan-v2-6</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -11316,21 +11314,21 @@
         </is>
       </c>
       <c r="I131" s="22" t="n">
-        <v>262144</v>
+        <v>400000</v>
       </c>
       <c r="J131" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K131" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L131" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K131" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L131" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M131" s="24" t="inlineStr">
@@ -11344,7 +11342,7 @@
         </is>
       </c>
       <c r="O131" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P131" s="18" t="inlineStr">
         <is>
@@ -11353,7 +11351,7 @@
       </c>
       <c r="Q131" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R131" s="18" t="n">
@@ -11366,7 +11364,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>flint-v1.0</t>
         </is>
       </c>
       <c r="C132" s="39" t="inlineStr">
@@ -11384,12 +11382,12 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>recursive/flint-v1.0:free</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -11402,7 +11400,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
@@ -11426,16 +11424,16 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -11448,7 +11446,7 @@
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="C133" s="39" t="inlineStr">
@@ -11471,7 +11469,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -11530,7 +11528,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>laguna-s-2.1</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="C134" s="39" t="inlineStr">
@@ -11548,12 +11546,12 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>poolside/laguna-s-2.1:free</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -11566,7 +11564,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
@@ -11574,9 +11572,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L134" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M134" s="9" t="inlineStr">
@@ -11590,16 +11588,16 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R134" s="2" t="n">
@@ -11612,7 +11610,7 @@
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>laguna-xs-2.1</t>
+          <t>laguna-s-2.1</t>
         </is>
       </c>
       <c r="C135" s="39" t="inlineStr">
@@ -11635,7 +11633,7 @@
       </c>
       <c r="G135" s="20" t="inlineStr">
         <is>
-          <t>poolside/laguna-xs-2.1:free</t>
+          <t>poolside/laguna-s-2.1:free</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -11685,169 +11683,169 @@
         </is>
       </c>
       <c r="R135" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="C136" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>poolside/laguna-xs-2.1:free</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="n">
+        <v>262144</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K136" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q136" s="5" t="inlineStr">
+        <is>
+          <t>agent, long_doc</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="25" t="n">
-        <v>118</v>
-      </c>
-      <c r="B136" s="26" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="C136" s="40" t="inlineStr">
+      <c r="C137" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D136" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="25" t="inlineStr">
+      <c r="D137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F136" s="27" t="inlineStr">
+      <c r="F137" s="13" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G136" s="27" t="inlineStr">
+      <c r="G137" s="13" t="inlineStr">
         <is>
           <t>poolside/laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="H136" s="14" t="inlineStr">
+      <c r="H137" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I136" s="28" t="n"/>
-      <c r="J136" s="25" t="inlineStr">
+      <c r="I137" s="15" t="n"/>
+      <c r="J137" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K136" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L136" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M136" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N136" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O136" s="25" t="n">
+      <c r="K137" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L137" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M137" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="P136" s="25" t="inlineStr">
+      <c r="P137" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q136" s="27" t="inlineStr">
+      <c r="Q137" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R136" s="25" t="n">
+      <c r="R137" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="C137" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>mistral</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I137" s="7" t="n">
-        <v>262144</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K137" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M137" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N137" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O137" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="P137" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q137" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R137" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11856,7 +11854,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11879,7 +11877,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11925,7 +11923,7 @@
       </c>
       <c r="Q138" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R138" s="18" t="n">
@@ -11938,7 +11936,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11961,7 +11959,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -12020,7 +12018,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12043,7 +12041,7 @@
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12052,11 +12050,11 @@
         </is>
       </c>
       <c r="I140" s="22" t="n">
-        <v>256000</v>
+        <v>262144</v>
       </c>
       <c r="J140" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K140" s="8" t="inlineStr">
@@ -12074,9 +12072,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N140" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N140" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O140" s="18" t="n">
@@ -12089,7 +12087,7 @@
       </c>
       <c r="Q140" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R140" s="18" t="n">
@@ -12102,7 +12100,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12125,7 +12123,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -12184,7 +12182,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12202,12 +12200,12 @@
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -12228,9 +12226,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M142" s="24" t="inlineStr">
@@ -12244,16 +12242,16 @@
         </is>
       </c>
       <c r="O142" s="18" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P142" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12266,7 +12264,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12289,20 +12287,20 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>cohere/north-mini-code:free</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>200000</v>
+        <v>256000</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K143" s="8" t="inlineStr">
@@ -12310,19 +12308,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L143" s="8" t="inlineStr">
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N143" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="M143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="O143" s="2" t="n">
@@ -12335,7 +12333,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12348,7 +12346,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12366,12 +12364,12 @@
       </c>
       <c r="F144" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
+          <t>openrouter/free</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
@@ -12380,21 +12378,21 @@
         </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>128000</v>
+        <v>200000</v>
       </c>
       <c r="J144" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K144" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L144" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K144" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L144" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M144" s="24" t="inlineStr">
@@ -12408,7 +12406,7 @@
         </is>
       </c>
       <c r="O144" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P144" s="18" t="inlineStr">
         <is>
@@ -12417,7 +12415,7 @@
       </c>
       <c r="Q144" s="20" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R144" s="18" t="n">
@@ -12430,7 +12428,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12448,35 +12446,35 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
-        </is>
-      </c>
-      <c r="H145" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>openai/gpt-live-1</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -12490,16 +12488,16 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R145" s="2" t="n">
@@ -12512,7 +12510,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12535,7 +12533,7 @@
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -12594,7 +12592,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12612,35 +12610,35 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
-        </is>
-      </c>
-      <c r="H147" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
+          <t>voxtral-small-latest</t>
+        </is>
+      </c>
+      <c r="H147" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I147" s="7" t="n">
-        <v>4096</v>
+        <v>32768</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L147" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K147" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M147" s="9" t="inlineStr">
@@ -12654,16 +12652,16 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R147" s="2" t="n">
@@ -12676,7 +12674,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12699,7 +12697,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>alibaba/happyhorse-1.1</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12712,7 +12710,7 @@
       </c>
       <c r="J148" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K148" s="24" t="inlineStr">
@@ -12745,7 +12743,7 @@
       </c>
       <c r="Q148" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R148" s="18" t="n">
@@ -12758,7 +12756,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12781,7 +12779,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12840,7 +12838,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12863,7 +12861,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12884,9 +12882,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L150" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L150" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M150" s="24" t="inlineStr">
@@ -12909,7 +12907,7 @@
       </c>
       <c r="Q150" s="20" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R150" s="18" t="n">
@@ -12922,7 +12920,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12945,7 +12943,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -12966,9 +12964,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M151" s="9" t="inlineStr">
@@ -12991,7 +12989,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R151" s="2" t="n">
@@ -13004,7 +13002,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13027,7 +13025,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13086,7 +13084,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13109,7 +13107,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13168,7 +13166,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13191,7 +13189,7 @@
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -13204,7 +13202,7 @@
       </c>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K154" s="24" t="inlineStr">
@@ -13237,7 +13235,7 @@
       </c>
       <c r="Q154" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R154" s="18" t="n">
@@ -13250,7 +13248,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13273,7 +13271,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H155" s="38" t="inlineStr">
@@ -13332,7 +13330,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13350,33 +13348,35 @@
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
-        </is>
-      </c>
-      <c r="H156" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I156" s="22" t="n"/>
+          <t>wanx/wan-v3-0</t>
+        </is>
+      </c>
+      <c r="H156" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="n">
+        <v>4096</v>
+      </c>
       <c r="J156" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K156" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L156" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K156" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L156" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M156" s="24" t="inlineStr">
@@ -13390,16 +13390,16 @@
         </is>
       </c>
       <c r="O156" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P156" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q156" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R156" s="18" t="n">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13430,12 +13430,12 @@
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>nvidia/ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="O160" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P160" s="18" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13790,7 +13790,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13990,12 +13990,12 @@
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14024,13 +14024,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N164" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N164" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O164" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14104,9 +14104,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N165" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N165" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O165" s="2" t="n">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14169,9 +14169,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K166" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K166" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="O166" s="18" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P166" s="18" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14249,9 +14249,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K167" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K167" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L167" s="23" t="inlineStr">
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="Q168" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R168" s="18" t="n">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="Q169" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R169" s="2" t="n">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R173" s="2" t="n">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="O174" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P174" s="18" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="Q174" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R174" s="18" t="n">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14950,12 +14950,12 @@
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14969,14 +14969,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K176" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L176" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K176" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L176" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M176" s="24" t="inlineStr">
@@ -14990,16 +14990,16 @@
         </is>
       </c>
       <c r="O176" s="18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P176" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q176" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R176" s="18" t="n">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15025,17 +15025,17 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15054,9 +15054,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L177" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="L177" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M177" s="9" t="inlineStr">
@@ -15070,16 +15070,16 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q177" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R177" s="2" t="n">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>step-5-preview</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C178" s="39" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="E178" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="G178" s="20" t="inlineStr">
         <is>
-          <t>stepfun-ai/step-5-preview</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H178" s="21" t="inlineStr">
@@ -15129,9 +15129,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K178" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K178" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L178" s="23" t="inlineStr">
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="O178" s="18" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P178" s="18" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="Q178" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R178" s="18" t="n">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>yi-large</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C179" s="39" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>01-ai/yi-large</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H179" s="21" t="inlineStr">
@@ -15246,1571 +15246,1651 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="41" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="18" t="n">
+        <v>162</v>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>yi-large</t>
+        </is>
+      </c>
+      <c r="C180" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F180" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G180" s="20" t="inlineStr">
+        <is>
+          <t>01-ai/yi-large</t>
+        </is>
+      </c>
+      <c r="H180" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I180" s="22" t="n"/>
+      <c r="J180" s="18" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K180" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L180" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M180" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N180" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O180" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P180" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q180" s="20" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R180" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="41" t="inlineStr">
         <is>
           <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="30" customHeight="1">
-      <c r="A182" s="1" t="inlineStr">
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B182" s="1" t="inlineStr">
+      <c r="B183" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="D182" s="1" t="inlineStr">
+      <c r="D183" s="1" t="inlineStr">
         <is>
           <t>Tier (1-5)</t>
         </is>
       </c>
-      <c r="E182" s="1" t="inlineStr">
+      <c r="E183" s="1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="F182" s="1" t="inlineStr">
+      <c r="F183" s="1" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr">
+      <c r="G183" s="1" t="inlineStr">
         <is>
           <t>Gateway model id</t>
         </is>
       </c>
-      <c r="H182" s="1" t="inlineStr">
+      <c r="H183" s="1" t="inlineStr">
         <is>
           <t>Context class</t>
         </is>
       </c>
-      <c r="I182" s="1" t="inlineStr">
+      <c r="I183" s="1" t="inlineStr">
         <is>
           <t>Context (tokens)</t>
         </is>
       </c>
-      <c r="J182" s="1" t="inlineStr">
+      <c r="J183" s="1" t="inlineStr">
         <is>
           <t>Modality</t>
         </is>
       </c>
-      <c r="K182" s="1" t="inlineStr">
+      <c r="K183" s="1" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="L182" s="1" t="inlineStr">
+      <c r="L183" s="1" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="M182" s="1" t="inlineStr">
+      <c r="M183" s="1" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="N182" s="1" t="inlineStr">
+      <c r="N183" s="1" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="O182" s="1" t="inlineStr">
+      <c r="O183" s="1" t="inlineStr">
         <is>
           <t>Speed (0-100)</t>
         </is>
       </c>
-      <c r="P182" s="1" t="inlineStr">
+      <c r="P183" s="1" t="inlineStr">
         <is>
           <t>Free type</t>
         </is>
       </c>
-      <c r="Q182" s="1" t="inlineStr">
+      <c r="Q183" s="1" t="inlineStr">
         <is>
           <t>Best for</t>
         </is>
       </c>
-      <c r="R182" s="1" t="inlineStr">
+      <c r="R183" s="1" t="inlineStr">
         <is>
           <t>Gateways in group</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D183" s="2" t="n">
+      <c r="D184" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>120B</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G183" s="5" t="inlineStr">
+      <c r="G184" s="5" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="H183" s="21" t="inlineStr">
+      <c r="H184" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I183" s="7" t="n"/>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="I184" s="7" t="n"/>
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M183" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N183" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O183" s="2" t="n">
+      <c r="K184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N184" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="P183" s="2" t="inlineStr">
+      <c r="P184" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q183" s="5" t="inlineStr">
+      <c r="Q184" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R183" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="18" t="n">
+      <c r="R184" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B184" s="19" t="inlineStr">
+      <c r="B185" s="19" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D184" s="18" t="n">
+      <c r="D185" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E184" s="18" t="inlineStr">
+      <c r="E185" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F184" s="20" t="inlineStr">
+      <c r="F185" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G184" s="20" t="inlineStr">
+      <c r="G185" s="20" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="H184" s="6" t="inlineStr">
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I184" s="22" t="n">
+      <c r="I185" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J184" s="18" t="inlineStr">
+      <c r="J185" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M184" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N184" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="18" t="n">
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N185" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P184" s="18" t="inlineStr">
+      <c r="P185" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q184" s="20" t="inlineStr">
+      <c r="Q185" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R184" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="R185" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n">
+      <c r="D186" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G185" s="5" t="inlineStr">
+      <c r="G186" s="5" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I185" s="7" t="n">
+      <c r="I186" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="2" t="n">
+      <c r="K186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M186" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N186" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P185" s="2" t="inlineStr">
+      <c r="P186" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q185" s="5" t="inlineStr">
+      <c r="Q186" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R185" s="2" t="n">
+      <c r="R186" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="10" t="n">
+    <row r="187">
+      <c r="A187" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B186" s="11" t="inlineStr">
+      <c r="B187" s="11" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C186" s="12" t="inlineStr">
+      <c r="C187" s="12" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D186" s="10" t="n">
+      <c r="D187" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E186" s="10" t="inlineStr">
+      <c r="E187" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F186" s="13" t="inlineStr">
+      <c r="F187" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G186" s="13" t="inlineStr">
+      <c r="G187" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H186" s="30" t="inlineStr">
+      <c r="H187" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I186" s="15" t="n">
+      <c r="I187" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J186" s="10" t="inlineStr">
+      <c r="J187" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K186" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L186" s="30" t="inlineStr">
+      <c r="K187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L187" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M186" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N186" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="10" t="n">
+      <c r="M187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P186" s="10" t="inlineStr">
+      <c r="P187" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q186" s="13" t="inlineStr">
+      <c r="Q187" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R186" s="10" t="n">
+      <c r="R187" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="18" t="n">
+    <row r="188">
+      <c r="A188" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B187" s="19" t="inlineStr">
+      <c r="B188" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="C187" s="4" t="inlineStr">
+      <c r="C188" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D187" s="18" t="n">
+      <c r="D188" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E187" s="18" t="inlineStr">
+      <c r="E188" s="18" t="inlineStr">
         <is>
           <t>90B</t>
         </is>
       </c>
-      <c r="F187" s="20" t="inlineStr">
+      <c r="F188" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G187" s="20" t="inlineStr">
+      <c r="G188" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="H187" s="21" t="inlineStr">
+      <c r="H188" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I187" s="22" t="n"/>
-      <c r="J187" s="18" t="inlineStr">
+      <c r="I188" s="22" t="n"/>
+      <c r="J188" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L187" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M187" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N187" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="18" t="n">
+      <c r="K188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M188" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N188" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="P187" s="18" t="inlineStr">
+      <c r="P188" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q187" s="20" t="inlineStr">
+      <c r="Q188" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R187" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="R188" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C188" s="31" t="inlineStr">
+      <c r="C189" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D188" s="2" t="n">
+      <c r="D189" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G188" s="5" t="inlineStr">
+      <c r="G189" s="5" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I188" s="7" t="n">
+      <c r="I189" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N188" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="2" t="n">
+      <c r="K189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N189" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P188" s="2" t="inlineStr">
+      <c r="P189" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q188" s="5" t="inlineStr">
+      <c r="Q189" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R188" s="2" t="n">
+      <c r="R189" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="10" t="n">
+    <row r="190">
+      <c r="A190" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B189" s="11" t="inlineStr">
+      <c r="B190" s="11" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C189" s="32" t="inlineStr">
+      <c r="C190" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D189" s="10" t="n">
+      <c r="D190" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E189" s="10" t="inlineStr">
+      <c r="E190" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F189" s="13" t="inlineStr">
+      <c r="F190" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G189" s="13" t="inlineStr">
+      <c r="G190" s="13" t="inlineStr">
         <is>
           <t>google/gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H189" s="42" t="inlineStr">
+      <c r="H190" s="42" t="inlineStr">
         <is>
           <t>Medium (8K-32K)</t>
         </is>
       </c>
-      <c r="I189" s="15" t="n">
+      <c r="I190" s="15" t="n">
         <v>32768</v>
       </c>
-      <c r="J189" s="10" t="inlineStr">
+      <c r="J190" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K189" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L189" s="30" t="inlineStr">
+      <c r="K190" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L190" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M189" s="30" t="inlineStr">
+      <c r="M190" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N189" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="10" t="n">
+      <c r="N190" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P189" s="10" t="inlineStr">
+      <c r="P190" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q189" s="13" t="inlineStr">
+      <c r="Q190" s="13" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, fast</t>
         </is>
       </c>
-      <c r="R189" s="10" t="n">
+      <c r="R190" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="18" t="n">
+    <row r="191">
+      <c r="A191" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B190" s="19" t="inlineStr">
+      <c r="B191" s="19" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="C190" s="31" t="inlineStr">
+      <c r="C191" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D190" s="18" t="n">
+      <c r="D191" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E190" s="18" t="inlineStr">
+      <c r="E191" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F190" s="20" t="inlineStr">
+      <c r="F191" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G190" s="20" t="inlineStr">
+      <c r="G191" s="20" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="H191" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I190" s="22" t="n">
+      <c r="I191" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J190" s="18" t="inlineStr">
+      <c r="J191" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L190" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M190" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N190" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="18" t="n">
+      <c r="K191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M191" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P190" s="18" t="inlineStr">
+      <c r="P191" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q190" s="20" t="inlineStr">
+      <c r="Q191" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R190" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="R191" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C191" s="31" t="inlineStr">
+      <c r="C192" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D191" s="2" t="n">
+      <c r="D192" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
+      <c r="F192" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G191" s="5" t="inlineStr">
+      <c r="G192" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H191" s="6" t="inlineStr">
+      <c r="H192" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I191" s="7" t="n">
+      <c r="I192" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M191" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="2" t="n">
+      <c r="K192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M192" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P191" s="2" t="inlineStr">
+      <c r="P192" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q191" s="5" t="inlineStr">
+      <c r="Q192" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R191" s="2" t="n">
+      <c r="R192" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="10" t="n">
+    <row r="193">
+      <c r="A193" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B192" s="11" t="inlineStr">
+      <c r="B193" s="11" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C192" s="32" t="inlineStr">
+      <c r="C193" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D192" s="10" t="n">
+      <c r="D193" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E192" s="10" t="inlineStr">
+      <c r="E193" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F192" s="13" t="inlineStr">
+      <c r="F193" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G192" s="13" t="inlineStr">
+      <c r="G193" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H192" s="30" t="inlineStr">
+      <c r="H193" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I192" s="15" t="n">
+      <c r="I193" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J192" s="10" t="inlineStr">
+      <c r="J193" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K192" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L192" s="30" t="inlineStr">
+      <c r="K193" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L193" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M192" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="10" t="n">
+      <c r="M193" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P192" s="10" t="inlineStr">
+      <c r="P193" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q192" s="13" t="inlineStr">
+      <c r="Q193" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R192" s="10" t="n">
+      <c r="R193" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="18" t="n">
+    <row r="194">
+      <c r="A194" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B193" s="19" t="inlineStr">
+      <c r="B194" s="19" t="inlineStr">
         <is>
           <t>neva-22b</t>
         </is>
       </c>
-      <c r="C193" s="35" t="inlineStr">
+      <c r="C194" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D193" s="18" t="n">
+      <c r="D194" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E193" s="18" t="inlineStr">
+      <c r="E194" s="18" t="inlineStr">
         <is>
           <t>22B</t>
         </is>
       </c>
-      <c r="F193" s="20" t="inlineStr">
+      <c r="F194" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G193" s="20" t="inlineStr">
+      <c r="G194" s="20" t="inlineStr">
         <is>
           <t>nvidia/neva-22b</t>
         </is>
       </c>
-      <c r="H193" s="21" t="inlineStr">
+      <c r="H194" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I193" s="22" t="n"/>
-      <c r="J193" s="18" t="inlineStr">
+      <c r="I194" s="22" t="n"/>
+      <c r="J194" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L193" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M193" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="18" t="n">
+      <c r="K194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M194" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="P193" s="18" t="inlineStr">
+      <c r="P194" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q193" s="20" t="inlineStr">
+      <c r="Q194" s="20" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R193" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="R194" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="C194" s="35" t="inlineStr">
+      <c r="C195" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D194" s="2" t="n">
+      <c r="D195" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F194" s="5" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G194" s="5" t="inlineStr">
+      <c r="G195" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="H194" s="6" t="inlineStr">
+      <c r="H195" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I194" s="7" t="n">
+      <c r="I195" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="2" t="n">
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P194" s="2" t="inlineStr">
+      <c r="P195" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q194" s="5" t="inlineStr">
+      <c r="Q195" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R194" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="18" t="n">
+      <c r="R195" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B195" s="19" t="inlineStr">
+      <c r="B196" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="C195" s="37" t="inlineStr">
+      <c r="C196" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D195" s="18" t="n">
+      <c r="D196" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E195" s="18" t="inlineStr">
+      <c r="E196" s="18" t="inlineStr">
         <is>
           <t>11B</t>
         </is>
       </c>
-      <c r="F195" s="20" t="inlineStr">
+      <c r="F196" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G195" s="20" t="inlineStr">
+      <c r="G196" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="H195" s="21" t="inlineStr">
+      <c r="H196" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I195" s="22" t="n"/>
-      <c r="J195" s="18" t="inlineStr">
+      <c r="I196" s="22" t="n"/>
+      <c r="J196" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N195" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="18" t="n">
+      <c r="K196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M196" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="P195" s="18" t="inlineStr">
+      <c r="P196" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q195" s="20" t="inlineStr">
+      <c r="Q196" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R195" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="R196" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>fuyu-8b</t>
         </is>
       </c>
-      <c r="C196" s="37" t="inlineStr">
+      <c r="C197" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D196" s="2" t="n">
+      <c r="D197" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>8B</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
+      <c r="F197" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G196" s="5" t="inlineStr">
+      <c r="G197" s="5" t="inlineStr">
         <is>
           <t>adept/fuyu-8b</t>
         </is>
       </c>
-      <c r="H196" s="21" t="inlineStr">
+      <c r="H197" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I196" s="7" t="n"/>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="I197" s="7" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M196" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N196" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="2" t="n">
+      <c r="K197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M197" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N197" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P196" s="2" t="inlineStr">
+      <c r="P197" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q196" s="5" t="inlineStr">
+      <c r="Q197" s="5" t="inlineStr">
         <is>
           <t>extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R196" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="18" t="n">
+      <c r="R197" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B197" s="19" t="inlineStr">
+      <c r="B198" s="19" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl</t>
         </is>
       </c>
-      <c r="C197" s="39" t="inlineStr">
+      <c r="C198" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D197" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" s="18" t="inlineStr">
+      <c r="D198" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F197" s="20" t="inlineStr">
+      <c r="F198" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G197" s="20" t="inlineStr">
+      <c r="G198" s="20" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl:free</t>
         </is>
       </c>
-      <c r="H197" s="6" t="inlineStr">
+      <c r="H198" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I197" s="22" t="n">
+      <c r="I198" s="22" t="n">
         <v>1000000</v>
       </c>
-      <c r="J197" s="18" t="inlineStr">
+      <c r="J198" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K197" s="8" t="inlineStr">
+      <c r="K198" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L197" s="8" t="inlineStr">
+      <c r="L198" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M197" s="8" t="inlineStr">
+      <c r="M198" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N197" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="18" t="n">
+      <c r="N198" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P197" s="18" t="inlineStr">
+      <c r="P198" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q197" s="20" t="inlineStr">
+      <c r="Q198" s="20" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R197" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="R198" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>kosmos-2</t>
         </is>
       </c>
-      <c r="C198" s="39" t="inlineStr">
+      <c r="C199" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="D199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F198" s="5" t="inlineStr">
+      <c r="F199" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G198" s="5" t="inlineStr">
+      <c r="G199" s="5" t="inlineStr">
         <is>
           <t>microsoft/kosmos-2</t>
         </is>
       </c>
-      <c r="H198" s="21" t="inlineStr">
+      <c r="H199" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I198" s="7" t="n"/>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="I199" s="7" t="n"/>
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L198" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M198" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N198" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O198" s="2" t="n">
+      <c r="K199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M199" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N199" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P198" s="2" t="inlineStr">
+      <c r="P199" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q198" s="5" t="inlineStr">
+      <c r="Q199" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R198" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="18" t="n">
+      <c r="R199" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B199" s="19" t="inlineStr">
+      <c r="B200" s="19" t="inlineStr">
         <is>
           <t>phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="C199" s="39" t="inlineStr">
+      <c r="C200" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D199" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="18" t="inlineStr">
+      <c r="D200" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F199" s="20" t="inlineStr">
+      <c r="F200" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G199" s="20" t="inlineStr">
+      <c r="G200" s="20" t="inlineStr">
         <is>
           <t>microsoft/phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="H199" s="21" t="inlineStr">
+      <c r="H200" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I199" s="22" t="n"/>
-      <c r="J199" s="18" t="inlineStr">
+      <c r="I200" s="22" t="n"/>
+      <c r="J200" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M199" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N199" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O199" s="18" t="n">
+      <c r="K200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M200" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N200" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O200" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="P199" s="18" t="inlineStr">
+      <c r="P200" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q199" s="20" t="inlineStr">
+      <c r="Q200" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R199" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="R200" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>vila</t>
         </is>
       </c>
-      <c r="C200" s="39" t="inlineStr">
+      <c r="C201" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D200" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="D201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F200" s="5" t="inlineStr">
+      <c r="F201" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G200" s="5" t="inlineStr">
+      <c r="G201" s="5" t="inlineStr">
         <is>
           <t>nvidia/vila</t>
         </is>
       </c>
-      <c r="H200" s="21" t="inlineStr">
+      <c r="H201" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I200" s="7" t="n"/>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="I201" s="7" t="n"/>
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M200" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N200" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O200" s="2" t="n">
+      <c r="K201" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L201" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M201" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N201" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P200" s="2" t="inlineStr">
+      <c r="P201" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q200" s="5" t="inlineStr">
+      <c r="Q201" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R200" s="2" t="n">
+      <c r="R201" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R179"/>
+  <autoFilter ref="A1:R180"/>
   <mergeCells count="1">
-    <mergeCell ref="A181:R181"/>
+    <mergeCell ref="A182:R182"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O179">
+  <conditionalFormatting sqref="O2:O180">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17046,7 +17126,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-22T17:14:12Z (source: live)</t>
+          <t>Registry updated 2026-10-22T21:39:34Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>nemotron-3.5-bolt-e4b</t>
+          <t>nemotron-parse</t>
         </is>
       </c>
       <c r="C121" s="39" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="G121" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-3.5-bolt-e4b</t>
+          <t>nvidia/nemotron-parse</t>
         </is>
       </c>
       <c r="H121" s="21" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>nemotron-parse</t>
+          <t>nemotron-parse-2.0</t>
         </is>
       </c>
       <c r="C122" s="39" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse</t>
+          <t>nvidia/nemotron-parse-2.0</t>
         </is>
       </c>
       <c r="H122" s="21" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
-          <t>nemotron-parse-2.0</t>
+          <t>lfm-2.5-2.6b</t>
         </is>
       </c>
       <c r="C123" s="39" t="inlineStr">
@@ -10645,43 +10645,45 @@
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2.6B</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G123" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse-2.0</t>
-        </is>
-      </c>
-      <c r="H123" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I123" s="22" t="n"/>
+          <t>liquid/lfm-2.5-2.6b:free</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I123" s="22" t="n">
+        <v>65536</v>
+      </c>
       <c r="J123" s="18" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K123" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L123" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M123" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K123" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M123" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N123" s="24" t="inlineStr">
@@ -10690,16 +10692,16 @@
         </is>
       </c>
       <c r="O123" s="18" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="P123" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q123" s="20" t="inlineStr">
         <is>
-          <t>reasoning, extraction, agent</t>
+          <t>long_doc, fast</t>
         </is>
       </c>
       <c r="R123" s="18" t="n">
@@ -10712,7 +10714,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>lfm-2.5-2.6b</t>
+          <t>lyria-3-clip-preview</t>
         </is>
       </c>
       <c r="C124" s="39" t="inlineStr">
@@ -10725,7 +10727,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2.6B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -10735,381 +10737,381 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>liquid/lfm-2.5-2.6b:free</t>
-        </is>
-      </c>
-      <c r="H124" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>google/lyria-3-clip-preview</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I124" s="7" t="n">
-        <v>65536</v>
+        <v>1048576</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>lyria-3-clip-preview</t>
+        </is>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>lyria-3-clip-preview</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I125" s="15" t="n"/>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K124" s="8" t="inlineStr">
+      <c r="K125" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L125" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M125" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O125" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="P125" s="10" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q125" s="13" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R125" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>lyria-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="C126" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D126" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F126" s="20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G126" s="20" t="inlineStr">
+        <is>
+          <t>google/lyria-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I126" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J126" s="18" t="inlineStr">
+        <is>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K126" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L124" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="P124" s="2" t="inlineStr">
+      <c r="M126" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O126" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="P126" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q124" s="5" t="inlineStr">
-        <is>
-          <t>long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R124" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="18" t="n">
+      <c r="Q126" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc</t>
+        </is>
+      </c>
+      <c r="R126" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="25" t="n">
         <v>110</v>
       </c>
-      <c r="B125" s="19" t="inlineStr">
-        <is>
-          <t>lyria-3-clip-preview</t>
-        </is>
-      </c>
-      <c r="C125" s="39" t="inlineStr">
+      <c r="B127" s="26" t="inlineStr">
+        <is>
+          <t>lyria-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="C127" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D125" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="18" t="inlineStr">
+      <c r="D127" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F125" s="20" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
-      <c r="G125" s="20" t="inlineStr">
-        <is>
-          <t>google/lyria-3-clip-preview</t>
-        </is>
-      </c>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="F127" s="27" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G127" s="27" t="inlineStr">
+        <is>
+          <t>lyria-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I127" s="28" t="n"/>
+      <c r="J127" s="25" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K127" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L127" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M127" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N127" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O127" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="P127" s="25" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q127" s="27" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R127" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C128" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>fastrouter/auto</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I125" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J125" s="18" t="inlineStr">
+      <c r="I128" s="7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K125" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L125" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M125" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N125" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O125" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="P125" s="18" t="inlineStr">
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M128" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N128" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q125" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc</t>
-        </is>
-      </c>
-      <c r="R125" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="25" t="n">
-        <v>110</v>
-      </c>
-      <c r="B126" s="26" t="inlineStr">
-        <is>
-          <t>lyria-3-clip-preview</t>
-        </is>
-      </c>
-      <c r="C126" s="40" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D126" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F126" s="27" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G126" s="27" t="inlineStr">
-        <is>
-          <t>lyria-3-clip-preview</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I126" s="28" t="n"/>
-      <c r="J126" s="25" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K126" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L126" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M126" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N126" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O126" s="25" t="n">
-        <v>49</v>
-      </c>
-      <c r="P126" s="25" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q126" s="27" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R126" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>lyria-3-pro-preview</t>
-        </is>
-      </c>
-      <c r="C127" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>google/lyria-3-pro-preview</t>
-        </is>
-      </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I127" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K127" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L127" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M127" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N127" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="P127" s="2" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q127" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc</t>
-        </is>
-      </c>
-      <c r="R127" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="10" t="n">
-        <v>111</v>
-      </c>
-      <c r="B128" s="11" t="inlineStr">
-        <is>
-          <t>lyria-3-pro-preview</t>
-        </is>
-      </c>
-      <c r="C128" s="40" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F128" s="13" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G128" s="13" t="inlineStr">
-        <is>
-          <t>lyria-3-pro-preview</t>
-        </is>
-      </c>
-      <c r="H128" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I128" s="15" t="n"/>
-      <c r="J128" s="10" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K128" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L128" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M128" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N128" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O128" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="P128" s="10" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q128" s="13" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R128" s="10" t="n">
-        <v>2</v>
+      <c r="Q128" s="5" t="inlineStr">
+        <is>
+          <t>vision, long_doc</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -11118,7 +11120,7 @@
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>dots-3-note-preview</t>
         </is>
       </c>
       <c r="C129" s="39" t="inlineStr">
@@ -11136,12 +11138,12 @@
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>fastrouter/auto</t>
+          <t>dots-studio/dots-3-note-preview:free</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -11150,21 +11152,21 @@
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>1000000</v>
+        <v>512000</v>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K129" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L129" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K129" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M129" s="24" t="inlineStr">
@@ -11178,7 +11180,7 @@
         </is>
       </c>
       <c r="O129" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P129" s="18" t="inlineStr">
         <is>
@@ -11187,7 +11189,7 @@
       </c>
       <c r="Q129" s="20" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -11200,7 +11202,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>dots-3-note-preview</t>
+          <t>wan-v2-6</t>
         </is>
       </c>
       <c r="C130" s="39" t="inlineStr">
@@ -11218,12 +11220,12 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>dots-studio/dots-3-note-preview:free</t>
+          <t>wanx/wan-v2-6</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -11232,21 +11234,21 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>512000</v>
+        <v>400000</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K130" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M130" s="9" t="inlineStr">
@@ -11260,7 +11262,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
@@ -11269,7 +11271,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R130" s="2" t="n">
@@ -11282,7 +11284,7 @@
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>wan-v2-6</t>
+          <t>flint-v1.0</t>
         </is>
       </c>
       <c r="C131" s="39" t="inlineStr">
@@ -11300,12 +11302,12 @@
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-6</t>
+          <t>recursive/flint-v1.0:free</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -11314,21 +11316,21 @@
         </is>
       </c>
       <c r="I131" s="22" t="n">
-        <v>400000</v>
+        <v>262144</v>
       </c>
       <c r="J131" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K131" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L131" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K131" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M131" s="24" t="inlineStr">
@@ -11342,7 +11344,7 @@
         </is>
       </c>
       <c r="O131" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P131" s="18" t="inlineStr">
         <is>
@@ -11351,7 +11353,7 @@
       </c>
       <c r="Q131" s="20" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R131" s="18" t="n">
@@ -11364,7 +11366,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>flint-v1.0</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="C132" s="39" t="inlineStr">
@@ -11382,12 +11384,12 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>recursive/flint-v1.0:free</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -11400,7 +11402,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
@@ -11424,16 +11426,16 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -11446,7 +11448,7 @@
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="C133" s="39" t="inlineStr">
@@ -11469,7 +11471,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -11528,7 +11530,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>laguna-s-2.1</t>
         </is>
       </c>
       <c r="C134" s="39" t="inlineStr">
@@ -11546,12 +11548,12 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>poolside/laguna-s-2.1:free</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -11564,7 +11566,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
@@ -11572,9 +11574,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L134" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L134" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M134" s="9" t="inlineStr">
@@ -11588,16 +11590,16 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>agent, long_doc</t>
         </is>
       </c>
       <c r="R134" s="2" t="n">
@@ -11610,7 +11612,7 @@
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>laguna-s-2.1</t>
+          <t>laguna-xs-2.1</t>
         </is>
       </c>
       <c r="C135" s="39" t="inlineStr">
@@ -11633,7 +11635,7 @@
       </c>
       <c r="G135" s="20" t="inlineStr">
         <is>
-          <t>poolside/laguna-s-2.1:free</t>
+          <t>poolside/laguna-xs-2.1:free</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -11683,169 +11685,169 @@
         </is>
       </c>
       <c r="R135" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="25" t="n">
+        <v>118</v>
+      </c>
+      <c r="B136" s="26" t="inlineStr">
+        <is>
+          <t>laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="C136" s="40" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D136" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F136" s="27" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G136" s="27" t="inlineStr">
+        <is>
+          <t>poolside/laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I136" s="28" t="n"/>
+      <c r="J136" s="25" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K136" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L136" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M136" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="P136" s="25" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q136" s="27" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R136" s="25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>laguna-xs-2.1</t>
-        </is>
-      </c>
-      <c r="C136" s="39" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>mistral-vibe-cli-fast</t>
+        </is>
+      </c>
+      <c r="C137" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="D137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>poolside/laguna-xs-2.1:free</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>mistral-vibe-cli-fast</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I136" s="7" t="n">
+      <c r="I137" s="7" t="n">
         <v>262144</v>
       </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K136" s="8" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K137" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L136" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M136" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N136" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O136" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="P136" s="2" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q136" s="5" t="inlineStr">
-        <is>
-          <t>agent, long_doc</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="B137" s="11" t="inlineStr">
-        <is>
-          <t>laguna-xs-2.1</t>
-        </is>
-      </c>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F137" s="13" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G137" s="13" t="inlineStr">
-        <is>
-          <t>poolside/laguna-xs-2.1</t>
-        </is>
-      </c>
-      <c r="H137" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I137" s="15" t="n"/>
-      <c r="J137" s="10" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K137" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L137" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M137" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N137" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O137" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="P137" s="10" t="inlineStr">
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M137" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q137" s="13" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R137" s="10" t="n">
-        <v>2</v>
+      <c r="Q137" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11854,7 +11856,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-fast</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11877,7 +11879,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-fast</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11923,7 +11925,7 @@
       </c>
       <c r="Q138" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R138" s="18" t="n">
@@ -11936,7 +11938,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11959,7 +11961,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -12018,7 +12020,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12041,7 +12043,7 @@
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12050,11 +12052,11 @@
         </is>
       </c>
       <c r="I140" s="22" t="n">
-        <v>262144</v>
+        <v>256000</v>
       </c>
       <c r="J140" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K140" s="8" t="inlineStr">
@@ -12072,9 +12074,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N140" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N140" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O140" s="18" t="n">
@@ -12087,7 +12089,7 @@
       </c>
       <c r="Q140" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R140" s="18" t="n">
@@ -12100,7 +12102,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12123,7 +12125,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -12182,7 +12184,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12200,12 +12202,12 @@
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>cohere/north-mini-code:free</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -12226,32 +12228,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L142" s="8" t="inlineStr">
+      <c r="L142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M142" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N142" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N142" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O142" s="18" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P142" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12264,7 +12266,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12287,20 +12289,20 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
-        </is>
-      </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
+          <t>openrouter/free</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>256000</v>
+        <v>200000</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K143" s="8" t="inlineStr">
@@ -12308,9 +12310,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M143" s="9" t="inlineStr">
@@ -12318,9 +12320,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N143" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O143" s="2" t="n">
@@ -12333,7 +12335,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12346,7 +12348,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12364,12 +12366,12 @@
       </c>
       <c r="F144" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
+          <t>openai/gpt-live-1</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
@@ -12378,21 +12380,21 @@
         </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>200000</v>
+        <v>128000</v>
       </c>
       <c r="J144" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K144" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K144" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L144" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M144" s="24" t="inlineStr">
@@ -12406,7 +12408,7 @@
         </is>
       </c>
       <c r="O144" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P144" s="18" t="inlineStr">
         <is>
@@ -12415,7 +12417,7 @@
       </c>
       <c r="Q144" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R144" s="18" t="n">
@@ -12428,7 +12430,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12446,35 +12448,35 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>voxtral-small-2507</t>
+        </is>
+      </c>
+      <c r="H145" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>128000</v>
+        <v>32768</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K145" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L145" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K145" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -12488,16 +12490,16 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R145" s="2" t="n">
@@ -12510,7 +12512,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12533,7 +12535,7 @@
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -12592,7 +12594,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12610,35 +12612,35 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
-        </is>
-      </c>
-      <c r="H147" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>alibaba/happyhorse-1.1</t>
+        </is>
+      </c>
+      <c r="H147" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
         </is>
       </c>
       <c r="I147" s="7" t="n">
-        <v>32768</v>
+        <v>4096</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K147" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L147" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L147" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M147" s="9" t="inlineStr">
@@ -12652,16 +12654,16 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R147" s="2" t="n">
@@ -12674,7 +12676,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12697,7 +12699,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12710,7 +12712,7 @@
       </c>
       <c r="J148" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K148" s="24" t="inlineStr">
@@ -12743,7 +12745,7 @@
       </c>
       <c r="Q148" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R148" s="18" t="n">
@@ -12756,7 +12758,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12779,7 +12781,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12838,7 +12840,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12861,7 +12863,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12882,9 +12884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L150" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M150" s="24" t="inlineStr">
@@ -12907,7 +12909,7 @@
       </c>
       <c r="Q150" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R150" s="18" t="n">
@@ -12920,7 +12922,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12943,7 +12945,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -12964,9 +12966,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L151" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M151" s="9" t="inlineStr">
@@ -12989,7 +12991,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R151" s="2" t="n">
@@ -13002,7 +13004,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13025,7 +13027,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13084,7 +13086,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13107,7 +13109,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13166,7 +13168,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13189,7 +13191,7 @@
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -13202,7 +13204,7 @@
       </c>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K154" s="24" t="inlineStr">
@@ -13235,7 +13237,7 @@
       </c>
       <c r="Q154" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R154" s="18" t="n">
@@ -13248,7 +13250,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13271,7 +13273,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>wanx/wan-v3-0</t>
         </is>
       </c>
       <c r="H155" s="38" t="inlineStr">
@@ -13330,7 +13332,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13348,35 +13350,33 @@
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
-        </is>
-      </c>
-      <c r="H156" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
-        </is>
-      </c>
-      <c r="I156" s="22" t="n">
-        <v>4096</v>
-      </c>
+          <t>nvidia/ai-synthetic-video-detector</t>
+        </is>
+      </c>
+      <c r="H156" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="n"/>
       <c r="J156" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K156" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L156" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K156" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L156" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M156" s="24" t="inlineStr">
@@ -13390,16 +13390,16 @@
         </is>
       </c>
       <c r="O156" s="18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P156" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q156" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R156" s="18" t="n">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13430,12 +13430,12 @@
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="O160" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P160" s="18" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13790,7 +13790,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13990,12 +13990,12 @@
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14024,13 +14024,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N164" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N164" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O164" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14104,9 +14104,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N165" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N165" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O165" s="2" t="n">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14169,9 +14169,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K166" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K166" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="O166" s="18" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P166" s="18" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14249,9 +14249,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K167" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K167" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L167" s="23" t="inlineStr">
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="Q168" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R168" s="18" t="n">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="Q169" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R169" s="2" t="n">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14710,12 +14710,12 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>minimaxai/minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R173" s="2" t="n">
@@ -17126,7 +17126,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-22T21:39:34Z (source: live)</t>
+          <t>Registry updated 2026-10-23T04:56:22Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17126,7 +17126,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-23T04:56:22Z (source: live)</t>
+          <t>Registry updated 2026-10-23T11:43:41Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:R202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>nemotron-parse</t>
+          <t>nemotron-3.5-bolt-e4b</t>
         </is>
       </c>
       <c r="C121" s="39" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="G121" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse</t>
+          <t>nvidia/nemotron-3.5-bolt-e4b</t>
         </is>
       </c>
       <c r="H121" s="21" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>nemotron-parse-2.0</t>
+          <t>nemotron-parse</t>
         </is>
       </c>
       <c r="C122" s="39" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nemotron-parse-2.0</t>
+          <t>nvidia/nemotron-parse</t>
         </is>
       </c>
       <c r="H122" s="21" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
-          <t>lfm-2.5-2.6b</t>
+          <t>nemotron-parse-2.0</t>
         </is>
       </c>
       <c r="C123" s="39" t="inlineStr">
@@ -10645,45 +10645,43 @@
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
-          <t>2.6B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G123" s="20" t="inlineStr">
         <is>
-          <t>liquid/lfm-2.5-2.6b:free</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>65536</v>
-      </c>
+          <t>nvidia/nemotron-parse-2.0</t>
+        </is>
+      </c>
+      <c r="H123" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I123" s="22" t="n"/>
       <c r="J123" s="18" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K123" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M123" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K123" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L123" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M123" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="N123" s="24" t="inlineStr">
@@ -10692,16 +10690,16 @@
         </is>
       </c>
       <c r="O123" s="18" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="P123" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q123" s="20" t="inlineStr">
         <is>
-          <t>long_doc, fast</t>
+          <t>reasoning, extraction, agent</t>
         </is>
       </c>
       <c r="R123" s="18" t="n">
@@ -10714,404 +10712,404 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
+          <t>lfm-2.5-2.6b</t>
+        </is>
+      </c>
+      <c r="C124" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2.6B</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>liquid/lfm-2.5-2.6b:free</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C124" s="39" t="inlineStr">
+      <c r="C125" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="D125" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G125" s="20" t="inlineStr">
         <is>
           <t>google/lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H125" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I124" s="7" t="n">
+      <c r="I125" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J125" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
+      <c r="K125" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N124" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="n">
+      <c r="M125" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O125" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P124" s="2" t="inlineStr">
+      <c r="P125" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q124" s="5" t="inlineStr">
+      <c r="Q125" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R124" s="2" t="n">
+      <c r="R125" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="10" t="n">
-        <v>109</v>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="B126" s="26" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="C125" s="40" t="inlineStr">
+      <c r="C126" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D125" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="10" t="inlineStr">
+      <c r="D126" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F125" s="13" t="inlineStr">
+      <c r="F126" s="27" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G125" s="13" t="inlineStr">
+      <c r="G126" s="27" t="inlineStr">
         <is>
           <t>lyria-3-clip-preview</t>
         </is>
       </c>
-      <c r="H125" s="14" t="inlineStr">
+      <c r="H126" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I125" s="15" t="n"/>
-      <c r="J125" s="10" t="inlineStr">
+      <c r="I126" s="28" t="n"/>
+      <c r="J126" s="25" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K125" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L125" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M125" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N125" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O125" s="10" t="n">
+      <c r="K126" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L126" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M126" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O126" s="25" t="n">
         <v>49</v>
       </c>
-      <c r="P125" s="10" t="inlineStr">
+      <c r="P126" s="25" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q125" s="13" t="inlineStr">
+      <c r="Q126" s="27" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R125" s="10" t="n">
+      <c r="R126" s="25" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="18" t="n">
-        <v>110</v>
-      </c>
-      <c r="B126" s="19" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C126" s="39" t="inlineStr">
+      <c r="C127" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D126" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="18" t="inlineStr">
+      <c r="D127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F126" s="20" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G126" s="20" t="inlineStr">
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>google/lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H126" s="6" t="inlineStr">
+      <c r="H127" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I126" s="22" t="n">
+      <c r="I127" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J126" s="18" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K126" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L126" s="8" t="inlineStr">
+      <c r="K127" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L127" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M126" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N126" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O126" s="18" t="n">
+      <c r="M127" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="P126" s="18" t="inlineStr">
+      <c r="P127" s="2" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q126" s="20" t="inlineStr">
+      <c r="Q127" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc</t>
         </is>
       </c>
-      <c r="R126" s="18" t="n">
+      <c r="R127" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="25" t="n">
-        <v>110</v>
-      </c>
-      <c r="B127" s="26" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="C127" s="40" t="inlineStr">
+      <c r="C128" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D127" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="25" t="inlineStr">
+      <c r="D128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F127" s="27" t="inlineStr">
+      <c r="F128" s="13" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G127" s="27" t="inlineStr">
+      <c r="G128" s="13" t="inlineStr">
         <is>
           <t>lyria-3-pro-preview</t>
         </is>
       </c>
-      <c r="H127" s="14" t="inlineStr">
+      <c r="H128" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I127" s="28" t="n"/>
-      <c r="J127" s="25" t="inlineStr">
+      <c r="I128" s="15" t="n"/>
+      <c r="J128" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K127" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L127" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M127" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N127" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O127" s="25" t="n">
+      <c r="K128" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L128" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M128" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N128" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O128" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="P127" s="25" t="inlineStr">
+      <c r="P128" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q127" s="27" t="inlineStr">
+      <c r="Q128" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R127" s="25" t="n">
+      <c r="R128" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C128" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>fastrouter/auto</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I128" s="7" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N128" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O128" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="P128" s="2" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q128" s="5" t="inlineStr">
-        <is>
-          <t>vision, long_doc</t>
-        </is>
-      </c>
-      <c r="R128" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -11120,7 +11118,7 @@
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>dots-3-note-preview</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="C129" s="39" t="inlineStr">
@@ -11138,12 +11136,12 @@
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>dots-studio/dots-3-note-preview:free</t>
+          <t>fastrouter/auto</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -11152,21 +11150,21 @@
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>512000</v>
+        <v>1000000</v>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K129" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L129" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K129" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L129" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M129" s="24" t="inlineStr">
@@ -11180,7 +11178,7 @@
         </is>
       </c>
       <c r="O129" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P129" s="18" t="inlineStr">
         <is>
@@ -11189,7 +11187,7 @@
       </c>
       <c r="Q129" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R129" s="18" t="n">
@@ -11202,7 +11200,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>wan-v2-6</t>
+          <t>dots-3-note-preview</t>
         </is>
       </c>
       <c r="C130" s="39" t="inlineStr">
@@ -11220,12 +11218,12 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-6</t>
+          <t>dots-studio/dots-3-note-preview:free</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -11234,21 +11232,21 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>400000</v>
+        <v>512000</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Text + Vision</t>
         </is>
       </c>
-      <c r="K130" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M130" s="9" t="inlineStr">
@@ -11262,7 +11260,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
@@ -11271,7 +11269,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>vision, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R130" s="2" t="n">
@@ -11284,7 +11282,7 @@
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>flint-v1.0</t>
+          <t>wan-v2-6</t>
         </is>
       </c>
       <c r="C131" s="39" t="inlineStr">
@@ -11302,12 +11300,12 @@
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>recursive/flint-v1.0:free</t>
+          <t>wanx/wan-v2-6</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -11316,21 +11314,21 @@
         </is>
       </c>
       <c r="I131" s="22" t="n">
-        <v>262144</v>
+        <v>400000</v>
       </c>
       <c r="J131" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K131" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L131" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K131" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L131" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M131" s="24" t="inlineStr">
@@ -11344,7 +11342,7 @@
         </is>
       </c>
       <c r="O131" s="18" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P131" s="18" t="inlineStr">
         <is>
@@ -11353,7 +11351,7 @@
       </c>
       <c r="Q131" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, long_doc</t>
+          <t>vision, long_doc</t>
         </is>
       </c>
       <c r="R131" s="18" t="n">
@@ -11366,7 +11364,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>flint-v1.0</t>
         </is>
       </c>
       <c r="C132" s="39" t="inlineStr">
@@ -11384,12 +11382,12 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5</t>
+          <t>recursive/flint-v1.0:free</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -11402,7 +11400,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
@@ -11426,16 +11424,16 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -11448,7 +11446,7 @@
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="C133" s="39" t="inlineStr">
@@ -11471,7 +11469,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>labs-leanstral-1-5-1</t>
+          <t>labs-leanstral-1-5</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -11530,7 +11528,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>laguna-s-2.1</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="C134" s="39" t="inlineStr">
@@ -11548,12 +11546,12 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>poolside/laguna-s-2.1:free</t>
+          <t>labs-leanstral-1-5-1</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -11566,7 +11564,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
@@ -11574,9 +11572,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L134" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M134" s="9" t="inlineStr">
@@ -11590,16 +11588,16 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R134" s="2" t="n">
@@ -11612,7 +11610,7 @@
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>laguna-xs-2.1</t>
+          <t>laguna-s-2.1</t>
         </is>
       </c>
       <c r="C135" s="39" t="inlineStr">
@@ -11635,7 +11633,7 @@
       </c>
       <c r="G135" s="20" t="inlineStr">
         <is>
-          <t>poolside/laguna-xs-2.1:free</t>
+          <t>poolside/laguna-s-2.1:free</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -11685,169 +11683,169 @@
         </is>
       </c>
       <c r="R135" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>laguna-xs-2.1</t>
+        </is>
+      </c>
+      <c r="C136" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>poolside/laguna-xs-2.1:free</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="n">
+        <v>262144</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K136" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q136" s="5" t="inlineStr">
+        <is>
+          <t>agent, long_doc</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="25" t="n">
-        <v>118</v>
-      </c>
-      <c r="B136" s="26" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
         <is>
           <t>laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="C136" s="40" t="inlineStr">
+      <c r="C137" s="40" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D136" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="25" t="inlineStr">
+      <c r="D137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F136" s="27" t="inlineStr">
+      <c r="F137" s="13" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G136" s="27" t="inlineStr">
+      <c r="G137" s="13" t="inlineStr">
         <is>
           <t>poolside/laguna-xs-2.1</t>
         </is>
       </c>
-      <c r="H136" s="14" t="inlineStr">
+      <c r="H137" s="14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I136" s="28" t="n"/>
-      <c r="J136" s="25" t="inlineStr">
+      <c r="I137" s="15" t="n"/>
+      <c r="J137" s="10" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K136" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L136" s="16" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M136" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N136" s="29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O136" s="25" t="n">
+      <c r="K137" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L137" s="16" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M137" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="P136" s="25" t="inlineStr">
+      <c r="P137" s="10" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q136" s="27" t="inlineStr">
+      <c r="Q137" s="13" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R136" s="25" t="n">
+      <c r="R137" s="10" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="C137" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>mistral</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>mistral-vibe-cli-fast</t>
-        </is>
-      </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I137" s="7" t="n">
-        <v>262144</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K137" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M137" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N137" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O137" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="P137" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q137" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R137" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11856,7 +11854,7 @@
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="C138" s="39" t="inlineStr">
@@ -11879,7 +11877,7 @@
       </c>
       <c r="G138" s="20" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-latest</t>
+          <t>mistral-vibe-cli-fast</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11925,7 +11923,7 @@
       </c>
       <c r="Q138" s="20" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R138" s="18" t="n">
@@ -11938,7 +11936,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="C139" s="39" t="inlineStr">
@@ -11961,7 +11959,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>mistral-vibe-cli-with-tools</t>
+          <t>mistral-vibe-cli-latest</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -12020,7 +12018,7 @@
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="C140" s="39" t="inlineStr">
@@ -12043,7 +12041,7 @@
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>mistral-code-fim-latest</t>
+          <t>mistral-vibe-cli-with-tools</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -12052,11 +12050,11 @@
         </is>
       </c>
       <c r="I140" s="22" t="n">
-        <v>256000</v>
+        <v>262144</v>
       </c>
       <c r="J140" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K140" s="8" t="inlineStr">
@@ -12074,9 +12072,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N140" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="N140" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O140" s="18" t="n">
@@ -12089,7 +12087,7 @@
       </c>
       <c r="Q140" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R140" s="18" t="n">
@@ -12102,7 +12100,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="C141" s="39" t="inlineStr">
@@ -12125,7 +12123,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>mistral-code-latest</t>
+          <t>mistral-code-fim-latest</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -12184,7 +12182,7 @@
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>north-mini-code</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="C142" s="39" t="inlineStr">
@@ -12202,12 +12200,12 @@
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>cohere/north-mini-code:free</t>
+          <t>mistral-code-latest</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -12228,9 +12226,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L142" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M142" s="24" t="inlineStr">
@@ -12244,16 +12242,16 @@
         </is>
       </c>
       <c r="O142" s="18" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P142" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q142" s="20" t="inlineStr">
         <is>
-          <t>coding, agent, long_doc, fast</t>
+          <t>coding, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R142" s="18" t="n">
@@ -12266,7 +12264,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>north-mini-code</t>
         </is>
       </c>
       <c r="C143" s="39" t="inlineStr">
@@ -12289,20 +12287,20 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
+          <t>cohere/north-mini-code:free</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>200000</v>
+        <v>256000</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K143" s="8" t="inlineStr">
@@ -12310,19 +12308,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L143" s="8" t="inlineStr">
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N143" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="M143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N143" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="O143" s="2" t="n">
@@ -12335,7 +12333,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>vision, extraction, agent, long_doc</t>
+          <t>coding, agent, long_doc, fast</t>
         </is>
       </c>
       <c r="R143" s="2" t="n">
@@ -12348,7 +12346,7 @@
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>gpt-live-1</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C144" s="39" t="inlineStr">
@@ -12366,12 +12364,12 @@
       </c>
       <c r="F144" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="G144" s="20" t="inlineStr">
         <is>
-          <t>openai/gpt-live-1</t>
+          <t>openrouter/free</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
@@ -12380,21 +12378,21 @@
         </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>128000</v>
+        <v>200000</v>
       </c>
       <c r="J144" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K144" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L144" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K144" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L144" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M144" s="24" t="inlineStr">
@@ -12408,7 +12406,7 @@
         </is>
       </c>
       <c r="O144" s="18" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P144" s="18" t="inlineStr">
         <is>
@@ -12417,7 +12415,7 @@
       </c>
       <c r="Q144" s="20" t="inlineStr">
         <is>
-          <t>long_doc</t>
+          <t>vision, extraction, agent, long_doc</t>
         </is>
       </c>
       <c r="R144" s="18" t="n">
@@ -12430,7 +12428,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
+          <t>gpt-live-1</t>
         </is>
       </c>
       <c r="C145" s="39" t="inlineStr">
@@ -12448,35 +12446,35 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>voxtral-small-2507</t>
-        </is>
-      </c>
-      <c r="H145" s="34" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
+          <t>openai/gpt-live-1</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="K145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -12490,16 +12488,16 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>long_doc</t>
         </is>
       </c>
       <c r="R145" s="2" t="n">
@@ -12512,7 +12510,7 @@
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="C146" s="39" t="inlineStr">
@@ -12535,7 +12533,7 @@
       </c>
       <c r="G146" s="20" t="inlineStr">
         <is>
-          <t>voxtral-small-latest</t>
+          <t>voxtral-small-2507</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -12594,7 +12592,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>happyhorse-1.1</t>
+          <t>voxtral-small-latest</t>
         </is>
       </c>
       <c r="C147" s="39" t="inlineStr">
@@ -12612,35 +12610,35 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>alibaba/happyhorse-1.1</t>
-        </is>
-      </c>
-      <c r="H147" s="38" t="inlineStr">
-        <is>
-          <t>Short (&lt;=8K)</t>
+          <t>voxtral-small-latest</t>
+        </is>
+      </c>
+      <c r="H147" s="34" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
         </is>
       </c>
       <c r="I147" s="7" t="n">
-        <v>4096</v>
+        <v>32768</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L147" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K147" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M147" s="9" t="inlineStr">
@@ -12654,16 +12652,16 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R147" s="2" t="n">
@@ -12676,7 +12674,7 @@
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>lucid-origin</t>
+          <t>happyhorse-1.1</t>
         </is>
       </c>
       <c r="C148" s="39" t="inlineStr">
@@ -12699,7 +12697,7 @@
       </c>
       <c r="G148" s="20" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-origin</t>
+          <t>alibaba/happyhorse-1.1</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -12712,7 +12710,7 @@
       </c>
       <c r="J148" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text + Vision</t>
         </is>
       </c>
       <c r="K148" s="24" t="inlineStr">
@@ -12745,7 +12743,7 @@
       </c>
       <c r="Q148" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R148" s="18" t="n">
@@ -12758,7 +12756,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>lucid-realism</t>
+          <t>lucid-origin</t>
         </is>
       </c>
       <c r="C149" s="39" t="inlineStr">
@@ -12781,7 +12779,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/lucid-realism</t>
+          <t>leonardo-ai/lucid-origin</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -12840,7 +12838,7 @@
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>nova-3</t>
+          <t>lucid-realism</t>
         </is>
       </c>
       <c r="C150" s="39" t="inlineStr">
@@ -12863,7 +12861,7 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>deepgram/nova-3</t>
+          <t>leonardo-ai/lucid-realism</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -12884,9 +12882,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L150" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="L150" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M150" s="24" t="inlineStr">
@@ -12909,7 +12907,7 @@
       </c>
       <c r="Q150" s="20" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R150" s="18" t="n">
@@ -12922,7 +12920,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>phoenix</t>
+          <t>nova-3</t>
         </is>
       </c>
       <c r="C151" s="39" t="inlineStr">
@@ -12945,7 +12943,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>leonardo-ai/phoenix</t>
+          <t>deepgram/nova-3</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -12966,9 +12964,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M151" s="9" t="inlineStr">
@@ -12991,7 +12989,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="R151" s="2" t="n">
@@ -13004,7 +13002,7 @@
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>seedream-4.0</t>
+          <t>phoenix</t>
         </is>
       </c>
       <c r="C152" s="39" t="inlineStr">
@@ -13027,7 +13025,7 @@
       </c>
       <c r="G152" s="20" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.0</t>
+          <t>leonardo-ai/phoenix</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -13086,7 +13084,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>seedream-4.5</t>
+          <t>seedream-4.0</t>
         </is>
       </c>
       <c r="C153" s="39" t="inlineStr">
@@ -13109,7 +13107,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>bytedance/seedream-4.5</t>
+          <t>bytedance/seedream-4.0</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -13168,7 +13166,7 @@
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>wan-v2-7</t>
+          <t>seedream-4.5</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -13191,7 +13189,7 @@
       </c>
       <c r="G154" s="20" t="inlineStr">
         <is>
-          <t>wanx/wan-v2-7</t>
+          <t>bytedance/seedream-4.5</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -13204,7 +13202,7 @@
       </c>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>Text + Vision</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="K154" s="24" t="inlineStr">
@@ -13237,7 +13235,7 @@
       </c>
       <c r="Q154" s="20" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R154" s="18" t="n">
@@ -13250,7 +13248,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>wan-v3-0</t>
+          <t>wan-v2-7</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -13273,7 +13271,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>wanx/wan-v3-0</t>
+          <t>wanx/wan-v2-7</t>
         </is>
       </c>
       <c r="H155" s="38" t="inlineStr">
@@ -13332,7 +13330,7 @@
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>ai-synthetic-video-detector</t>
+          <t>wan-v3-0</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -13350,33 +13348,35 @@
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G156" s="20" t="inlineStr">
         <is>
-          <t>nvidia/ai-synthetic-video-detector</t>
-        </is>
-      </c>
-      <c r="H156" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I156" s="22" t="n"/>
+          <t>wanx/wan-v3-0</t>
+        </is>
+      </c>
+      <c r="H156" s="38" t="inlineStr">
+        <is>
+          <t>Short (&lt;=8K)</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="n">
+        <v>4096</v>
+      </c>
       <c r="J156" s="18" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K156" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L156" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+          <t>Text + Vision</t>
+        </is>
+      </c>
+      <c r="K156" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L156" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M156" s="24" t="inlineStr">
@@ -13390,16 +13390,16 @@
         </is>
       </c>
       <c r="O156" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P156" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q156" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="R156" s="18" t="n">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -13430,12 +13430,12 @@
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-05-2026</t>
+          <t>nvidia/ai-synthetic-video-detector</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="G158" s="20" t="inlineStr">
         <is>
-          <t>antigravity-preview-09-2026</t>
+          <t>antigravity-preview-05-2026</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="C159" s="39" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>antigravity-preview-latest</t>
+          <t>antigravity-preview-09-2026</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G160" s="20" t="inlineStr">
         <is>
-          <t>databricks/dbrx-instruct</t>
+          <t>antigravity-preview-latest</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="O160" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P160" s="18" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>dbrx-instruct</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>deep-research-max-preview-04-2026</t>
+          <t>databricks/dbrx-instruct</t>
         </is>
       </c>
       <c r="H161" s="21" t="inlineStr">
@@ -13790,7 +13790,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="G162" s="20" t="inlineStr">
         <is>
-          <t>deep-research-preview-04-2026</t>
+          <t>deep-research-max-preview-04-2026</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>deep-research-pro-preview-12-2025</t>
+          <t>deep-research-preview-04-2026</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -13990,12 +13990,12 @@
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G164" s="20" t="inlineStr">
         <is>
-          <t>deepseek-ai/deepseek-v4.1-flash</t>
+          <t>deep-research-pro-preview-12-2025</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -14024,13 +14024,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N164" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="N164" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O164" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="Q164" s="20" t="inlineStr">
         <is>
-          <t>coding, extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R164" s="18" t="n">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>deplot</t>
+          <t>deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="C165" s="39" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>google/deplot</t>
+          <t>deepseek-ai/deepseek-v4.1-flash</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
@@ -14104,9 +14104,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N165" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="N165" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="O165" s="2" t="n">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>coding, extraction, agent, fast</t>
         </is>
       </c>
       <c r="R165" s="2" t="n">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>gemma-2b</t>
+          <t>deplot</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G166" s="20" t="inlineStr">
         <is>
-          <t>google/gemma-2b</t>
+          <t>google/deplot</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -14169,9 +14169,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K166" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K166" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="O166" s="18" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P166" s="18" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="Q166" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R166" s="18" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>gemma-2b</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>google/gemma-2b</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14249,9 +14249,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K167" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K167" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L167" s="23" t="inlineStr">
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R167" s="2" t="n">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>glm-5.3</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G168" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="Q168" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R168" s="18" t="n">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="Q169" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R169" s="2" t="n">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="G170" s="20" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>minimax-m3.1-flash</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14710,12 +14710,12 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>minimaxai/minimax-m3.1-flash</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R173" s="2" t="n">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>minimaxai/minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="O174" s="18" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P174" s="18" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14870,12 +14870,12 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="Q175" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R175" s="2" t="n">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="G176" s="20" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15030,12 +15030,12 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15049,14 +15049,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K177" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L177" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K177" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L177" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M177" s="9" t="inlineStr">
@@ -15070,16 +15070,16 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q177" s="5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R177" s="2" t="n">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C178" s="39" t="inlineStr">
@@ -15105,17 +15105,17 @@
       </c>
       <c r="E178" s="18" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G178" s="20" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H178" s="21" t="inlineStr">
@@ -15134,9 +15134,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L178" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="L178" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M178" s="24" t="inlineStr">
@@ -15150,16 +15150,16 @@
         </is>
       </c>
       <c r="O178" s="18" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P178" s="18" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q178" s="20" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R178" s="18" t="n">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>step-5-preview</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C179" s="39" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>stepfun-ai/step-5-preview</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H179" s="21" t="inlineStr">
@@ -15209,9 +15209,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K179" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K179" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="L179" s="23" t="inlineStr">
@@ -15230,7 +15230,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="Q179" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R179" s="2" t="n">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="B180" s="19" t="inlineStr">
         <is>
-          <t>yi-large</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C180" s="39" t="inlineStr">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="G180" s="20" t="inlineStr">
         <is>
-          <t>01-ai/yi-large</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H180" s="21" t="inlineStr">
@@ -15326,1571 +15326,1651 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="41" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>yi-large</t>
+        </is>
+      </c>
+      <c r="C181" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>01-ai/yi-large</t>
+        </is>
+      </c>
+      <c r="H181" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="n"/>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="K181" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L181" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M181" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N181" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q181" s="5" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="41" t="inlineStr">
         <is>
           <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="1" t="inlineStr">
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B183" s="1" t="inlineStr">
+      <c r="B184" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C184" s="1" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="D183" s="1" t="inlineStr">
+      <c r="D184" s="1" t="inlineStr">
         <is>
           <t>Tier (1-5)</t>
         </is>
       </c>
-      <c r="E183" s="1" t="inlineStr">
+      <c r="E184" s="1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="F183" s="1" t="inlineStr">
+      <c r="F184" s="1" t="inlineStr">
         <is>
           <t>Gateway</t>
         </is>
       </c>
-      <c r="G183" s="1" t="inlineStr">
+      <c r="G184" s="1" t="inlineStr">
         <is>
           <t>Gateway model id</t>
         </is>
       </c>
-      <c r="H183" s="1" t="inlineStr">
+      <c r="H184" s="1" t="inlineStr">
         <is>
           <t>Context class</t>
         </is>
       </c>
-      <c r="I183" s="1" t="inlineStr">
+      <c r="I184" s="1" t="inlineStr">
         <is>
           <t>Context (tokens)</t>
         </is>
       </c>
-      <c r="J183" s="1" t="inlineStr">
+      <c r="J184" s="1" t="inlineStr">
         <is>
           <t>Modality</t>
         </is>
       </c>
-      <c r="K183" s="1" t="inlineStr">
+      <c r="K184" s="1" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="L183" s="1" t="inlineStr">
+      <c r="L184" s="1" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="M183" s="1" t="inlineStr">
+      <c r="M184" s="1" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="N183" s="1" t="inlineStr">
+      <c r="N184" s="1" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="O183" s="1" t="inlineStr">
+      <c r="O184" s="1" t="inlineStr">
         <is>
           <t>Speed (0-100)</t>
         </is>
       </c>
-      <c r="P183" s="1" t="inlineStr">
+      <c r="P184" s="1" t="inlineStr">
         <is>
           <t>Free type</t>
         </is>
       </c>
-      <c r="Q183" s="1" t="inlineStr">
+      <c r="Q184" s="1" t="inlineStr">
         <is>
           <t>Best for</t>
         </is>
       </c>
-      <c r="R183" s="1" t="inlineStr">
+      <c r="R184" s="1" t="inlineStr">
         <is>
           <t>Gateways in group</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D184" s="2" t="n">
+      <c r="D185" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>120B</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr">
+      <c r="G185" s="5" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
         </is>
       </c>
-      <c r="H184" s="21" t="inlineStr">
+      <c r="H185" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I184" s="7" t="n"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I185" s="7" t="n"/>
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N184" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="2" t="n">
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N185" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="P184" s="2" t="inlineStr">
+      <c r="P185" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q184" s="5" t="inlineStr">
+      <c r="Q185" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R184" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="18" t="n">
+      <c r="R185" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B185" s="19" t="inlineStr">
+      <c r="B186" s="19" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D185" s="18" t="n">
+      <c r="D186" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E185" s="18" t="inlineStr">
+      <c r="E186" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F185" s="20" t="inlineStr">
+      <c r="F186" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G185" s="20" t="inlineStr">
+      <c r="G186" s="20" t="inlineStr">
         <is>
           <t>gemini-3-pro-image</t>
         </is>
       </c>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I185" s="22" t="n">
+      <c r="I186" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J185" s="18" t="inlineStr">
+      <c r="J186" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="18" t="n">
+      <c r="K186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L186" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M186" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N186" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P185" s="18" t="inlineStr">
+      <c r="P186" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q185" s="20" t="inlineStr">
+      <c r="Q186" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R185" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="R186" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
+      <c r="C187" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D186" s="2" t="n">
+      <c r="D187" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G186" s="5" t="inlineStr">
+      <c r="G187" s="5" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I186" s="7" t="n">
+      <c r="I187" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M186" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N186" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="2" t="n">
+      <c r="K187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M187" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P186" s="2" t="inlineStr">
+      <c r="P187" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q186" s="5" t="inlineStr">
+      <c r="Q187" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R186" s="2" t="n">
+      <c r="R187" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="10" t="n">
+    <row r="188">
+      <c r="A188" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B187" s="11" t="inlineStr">
+      <c r="B188" s="11" t="inlineStr">
         <is>
           <t>gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="C187" s="12" t="inlineStr">
+      <c r="C188" s="12" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D187" s="10" t="n">
+      <c r="D188" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E187" s="10" t="inlineStr">
+      <c r="E188" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F187" s="13" t="inlineStr">
+      <c r="F188" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G187" s="13" t="inlineStr">
+      <c r="G188" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3-pro-image-preview</t>
         </is>
       </c>
-      <c r="H187" s="30" t="inlineStr">
+      <c r="H188" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I187" s="15" t="n">
+      <c r="I188" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J187" s="10" t="inlineStr">
+      <c r="J188" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L187" s="30" t="inlineStr">
+      <c r="K188" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L188" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="10" t="n">
+      <c r="M188" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N188" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P187" s="10" t="inlineStr">
+      <c r="P188" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q187" s="13" t="inlineStr">
+      <c r="Q188" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R187" s="10" t="n">
+      <c r="R188" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="18" t="n">
+    <row r="189">
+      <c r="A189" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B188" s="19" t="inlineStr">
+      <c r="B189" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="C188" s="4" t="inlineStr">
+      <c r="C189" s="4" t="inlineStr">
         <is>
           <t>Top</t>
         </is>
       </c>
-      <c r="D188" s="18" t="n">
+      <c r="D189" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E188" s="18" t="inlineStr">
+      <c r="E189" s="18" t="inlineStr">
         <is>
           <t>90B</t>
         </is>
       </c>
-      <c r="F188" s="20" t="inlineStr">
+      <c r="F189" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G188" s="20" t="inlineStr">
+      <c r="G189" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-90b-vision-instruct</t>
         </is>
       </c>
-      <c r="H188" s="21" t="inlineStr">
+      <c r="H189" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I188" s="22" t="n"/>
-      <c r="J188" s="18" t="inlineStr">
+      <c r="I189" s="22" t="n"/>
+      <c r="J189" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="18" t="n">
+      <c r="K189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L189" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M189" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N189" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="P188" s="18" t="inlineStr">
+      <c r="P189" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q188" s="20" t="inlineStr">
+      <c r="Q189" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R188" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="R189" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C189" s="31" t="inlineStr">
+      <c r="C190" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D189" s="2" t="n">
+      <c r="D190" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G189" s="5" t="inlineStr">
+      <c r="G190" s="5" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I189" s="7" t="n">
+      <c r="I190" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N189" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="2" t="n">
+      <c r="K190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N190" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P189" s="2" t="inlineStr">
+      <c r="P190" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q189" s="5" t="inlineStr">
+      <c r="Q190" s="5" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R189" s="2" t="n">
+      <c r="R190" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="10" t="n">
+    <row r="191">
+      <c r="A191" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B190" s="11" t="inlineStr">
+      <c r="B191" s="11" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="C190" s="32" t="inlineStr">
+      <c r="C191" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D190" s="10" t="n">
+      <c r="D191" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E190" s="10" t="inlineStr">
+      <c r="E191" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F190" s="13" t="inlineStr">
+      <c r="F191" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G190" s="13" t="inlineStr">
+      <c r="G191" s="13" t="inlineStr">
         <is>
           <t>google/gemini-2.5-flash-image</t>
         </is>
       </c>
-      <c r="H190" s="42" t="inlineStr">
+      <c r="H191" s="42" t="inlineStr">
         <is>
           <t>Medium (8K-32K)</t>
         </is>
       </c>
-      <c r="I190" s="15" t="n">
+      <c r="I191" s="15" t="n">
         <v>32768</v>
       </c>
-      <c r="J190" s="10" t="inlineStr">
+      <c r="J191" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L190" s="30" t="inlineStr">
+      <c r="K191" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L191" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M190" s="30" t="inlineStr">
+      <c r="M191" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="10" t="n">
+      <c r="N191" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P190" s="10" t="inlineStr">
+      <c r="P191" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q190" s="13" t="inlineStr">
+      <c r="Q191" s="13" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, fast</t>
         </is>
       </c>
-      <c r="R190" s="10" t="n">
+      <c r="R191" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="18" t="n">
+    <row r="192">
+      <c r="A192" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B191" s="19" t="inlineStr">
+      <c r="B192" s="19" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="C191" s="31" t="inlineStr">
+      <c r="C192" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D191" s="18" t="n">
+      <c r="D192" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E191" s="18" t="inlineStr">
+      <c r="E192" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F191" s="20" t="inlineStr">
+      <c r="F192" s="20" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G191" s="20" t="inlineStr">
+      <c r="G192" s="20" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image</t>
         </is>
       </c>
-      <c r="H191" s="6" t="inlineStr">
+      <c r="H192" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I191" s="22" t="n">
+      <c r="I192" s="22" t="n">
         <v>1048576</v>
       </c>
-      <c r="J191" s="18" t="inlineStr">
+      <c r="J192" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="18" t="n">
+      <c r="K192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L192" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M192" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="P191" s="18" t="inlineStr">
+      <c r="P192" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q191" s="20" t="inlineStr">
+      <c r="Q192" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R191" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="R192" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C192" s="31" t="inlineStr">
+      <c r="C193" s="31" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D192" s="2" t="n">
+      <c r="D193" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F192" s="5" t="inlineStr">
+      <c r="F193" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G192" s="5" t="inlineStr">
+      <c r="G193" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H192" s="6" t="inlineStr">
+      <c r="H193" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I192" s="7" t="n">
+      <c r="I193" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="2" t="n">
+      <c r="K193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M193" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P192" s="2" t="inlineStr">
+      <c r="P193" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q192" s="5" t="inlineStr">
+      <c r="Q193" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R192" s="2" t="n">
+      <c r="R193" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="10" t="n">
+    <row r="194">
+      <c r="A194" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B193" s="11" t="inlineStr">
+      <c r="B194" s="11" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="C193" s="32" t="inlineStr">
+      <c r="C194" s="32" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D193" s="10" t="n">
+      <c r="D194" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E193" s="10" t="inlineStr">
+      <c r="E194" s="10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F193" s="13" t="inlineStr">
+      <c r="F194" s="13" t="inlineStr">
         <is>
           <t>fastrouter</t>
         </is>
       </c>
-      <c r="G193" s="13" t="inlineStr">
+      <c r="G194" s="13" t="inlineStr">
         <is>
           <t>google/gemini-3.1-flash-image-preview</t>
         </is>
       </c>
-      <c r="H193" s="30" t="inlineStr">
+      <c r="H194" s="30" t="inlineStr">
         <is>
           <t>Long (32K-200K)</t>
         </is>
       </c>
-      <c r="I193" s="15" t="n">
+      <c r="I194" s="15" t="n">
         <v>65536</v>
       </c>
-      <c r="J193" s="10" t="inlineStr">
+      <c r="J194" s="10" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L193" s="30" t="inlineStr">
+      <c r="K194" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L194" s="30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="10" t="n">
+      <c r="M194" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="P193" s="10" t="inlineStr">
+      <c r="P194" s="10" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q193" s="13" t="inlineStr">
+      <c r="Q194" s="13" t="inlineStr">
         <is>
           <t>vision, extraction, long_doc, fast</t>
         </is>
       </c>
-      <c r="R193" s="10" t="n">
+      <c r="R194" s="10" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="18" t="n">
+    <row r="195">
+      <c r="A195" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B194" s="19" t="inlineStr">
+      <c r="B195" s="19" t="inlineStr">
         <is>
           <t>neva-22b</t>
         </is>
       </c>
-      <c r="C194" s="35" t="inlineStr">
+      <c r="C195" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D194" s="18" t="n">
+      <c r="D195" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E194" s="18" t="inlineStr">
+      <c r="E195" s="18" t="inlineStr">
         <is>
           <t>22B</t>
         </is>
       </c>
-      <c r="F194" s="20" t="inlineStr">
+      <c r="F195" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G194" s="20" t="inlineStr">
+      <c r="G195" s="20" t="inlineStr">
         <is>
           <t>nvidia/neva-22b</t>
         </is>
       </c>
-      <c r="H194" s="21" t="inlineStr">
+      <c r="H195" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I194" s="22" t="n"/>
-      <c r="J194" s="18" t="inlineStr">
+      <c r="I195" s="22" t="n"/>
+      <c r="J195" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="18" t="n">
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="P194" s="18" t="inlineStr">
+      <c r="P195" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q194" s="20" t="inlineStr">
+      <c r="Q195" s="20" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R194" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="R195" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="C195" s="35" t="inlineStr">
+      <c r="C196" s="35" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="D195" s="2" t="n">
+      <c r="D196" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
+      <c r="F196" s="5" t="inlineStr">
         <is>
           <t>gemini</t>
         </is>
       </c>
-      <c r="G195" s="5" t="inlineStr">
+      <c r="G196" s="5" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite-image</t>
         </is>
       </c>
-      <c r="H195" s="6" t="inlineStr">
+      <c r="H196" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I195" s="7" t="n">
+      <c r="I196" s="7" t="n">
         <v>1048576</v>
       </c>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="2" t="n">
+      <c r="K196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="P195" s="2" t="inlineStr">
+      <c r="P196" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q195" s="5" t="inlineStr">
+      <c r="Q196" s="5" t="inlineStr">
         <is>
           <t>vision, extraction, agent, long_doc, fast</t>
         </is>
       </c>
-      <c r="R195" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="18" t="n">
+      <c r="R196" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B196" s="19" t="inlineStr">
+      <c r="B197" s="19" t="inlineStr">
         <is>
           <t>llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="C196" s="37" t="inlineStr">
+      <c r="C197" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D196" s="18" t="n">
+      <c r="D197" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E196" s="18" t="inlineStr">
+      <c r="E197" s="18" t="inlineStr">
         <is>
           <t>11B</t>
         </is>
       </c>
-      <c r="F196" s="20" t="inlineStr">
+      <c r="F197" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G196" s="20" t="inlineStr">
+      <c r="G197" s="20" t="inlineStr">
         <is>
           <t>meta/llama-3.2-11b-vision-instruct</t>
         </is>
       </c>
-      <c r="H196" s="21" t="inlineStr">
+      <c r="H197" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I196" s="22" t="n"/>
-      <c r="J196" s="18" t="inlineStr">
+      <c r="I197" s="22" t="n"/>
+      <c r="J197" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="18" t="n">
+      <c r="K197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L197" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M197" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N197" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="P196" s="18" t="inlineStr">
+      <c r="P197" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q196" s="20" t="inlineStr">
+      <c r="Q197" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R196" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="R197" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B197" s="3" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>fuyu-8b</t>
         </is>
       </c>
-      <c r="C197" s="37" t="inlineStr">
+      <c r="C198" s="37" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="D197" s="2" t="n">
+      <c r="D198" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>8B</t>
         </is>
       </c>
-      <c r="F197" s="5" t="inlineStr">
+      <c r="F198" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G197" s="5" t="inlineStr">
+      <c r="G198" s="5" t="inlineStr">
         <is>
           <t>adept/fuyu-8b</t>
         </is>
       </c>
-      <c r="H197" s="21" t="inlineStr">
+      <c r="H198" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I197" s="7" t="n"/>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="I198" s="7" t="n"/>
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="2" t="n">
+      <c r="K198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="P197" s="2" t="inlineStr">
+      <c r="P198" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q197" s="5" t="inlineStr">
+      <c r="Q198" s="5" t="inlineStr">
         <is>
           <t>extraction, agent, fast</t>
         </is>
       </c>
-      <c r="R197" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="18" t="n">
+      <c r="R198" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B198" s="19" t="inlineStr">
+      <c r="B199" s="19" t="inlineStr">
         <is>
           <t>nemotron-3.5-super-vl</t>
         </is>
       </c>
-      <c r="C198" s="39" t="inlineStr">
+      <c r="C199" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D198" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="18" t="inlineStr">
+      <c r="D199" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F198" s="20" t="inlineStr">
+      <c r="F199" s="20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G198" s="20" t="inlineStr">
+      <c r="G199" s="20" t="inlineStr">
         <is>
           <t>nvidia/nemotron-3.5-super-vl:free</t>
         </is>
       </c>
-      <c r="H198" s="6" t="inlineStr">
+      <c r="H199" s="6" t="inlineStr">
         <is>
           <t>Ultra (&gt;200K)</t>
         </is>
       </c>
-      <c r="I198" s="22" t="n">
+      <c r="I199" s="22" t="n">
         <v>1000000</v>
       </c>
-      <c r="J198" s="18" t="inlineStr">
+      <c r="J199" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K198" s="8" t="inlineStr">
+      <c r="K199" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L198" s="8" t="inlineStr">
+      <c r="L199" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M198" s="8" t="inlineStr">
+      <c r="M199" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N198" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O198" s="18" t="n">
+      <c r="N199" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="P198" s="18" t="inlineStr">
+      <c r="P199" s="18" t="inlineStr">
         <is>
           <t>Price 0</t>
         </is>
       </c>
-      <c r="Q198" s="20" t="inlineStr">
+      <c r="Q199" s="20" t="inlineStr">
         <is>
           <t>reasoning, vision, extraction, agent, long_doc</t>
         </is>
       </c>
-      <c r="R198" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="R199" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B199" s="3" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>kosmos-2</t>
         </is>
       </c>
-      <c r="C199" s="39" t="inlineStr">
+      <c r="C200" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D199" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="D200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F199" s="5" t="inlineStr">
+      <c r="F200" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G199" s="5" t="inlineStr">
+      <c r="G200" s="5" t="inlineStr">
         <is>
           <t>microsoft/kosmos-2</t>
         </is>
       </c>
-      <c r="H199" s="21" t="inlineStr">
+      <c r="H200" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I199" s="7" t="n"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I200" s="7" t="n"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O199" s="2" t="n">
+      <c r="K200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P199" s="2" t="inlineStr">
+      <c r="P200" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q199" s="5" t="inlineStr">
+      <c r="Q200" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R199" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="18" t="n">
+      <c r="R200" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B200" s="19" t="inlineStr">
+      <c r="B201" s="19" t="inlineStr">
         <is>
           <t>phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="C200" s="39" t="inlineStr">
+      <c r="C201" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D200" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="18" t="inlineStr">
+      <c r="D201" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F200" s="20" t="inlineStr">
+      <c r="F201" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G200" s="20" t="inlineStr">
+      <c r="G201" s="20" t="inlineStr">
         <is>
           <t>microsoft/phi-3-vision-128k-instruct</t>
         </is>
       </c>
-      <c r="H200" s="21" t="inlineStr">
+      <c r="H201" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I200" s="22" t="n"/>
-      <c r="J200" s="18" t="inlineStr">
+      <c r="I201" s="22" t="n"/>
+      <c r="J201" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M200" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N200" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O200" s="18" t="n">
+      <c r="K201" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L201" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M201" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N201" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O201" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="P200" s="18" t="inlineStr">
+      <c r="P201" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q200" s="20" t="inlineStr">
+      <c r="Q201" s="20" t="inlineStr">
         <is>
           <t>vision, extraction, agent</t>
         </is>
       </c>
-      <c r="R200" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="R201" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>vila</t>
         </is>
       </c>
-      <c r="C201" s="39" t="inlineStr">
+      <c r="C202" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D201" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="D202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F201" s="5" t="inlineStr">
+      <c r="F202" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G201" s="5" t="inlineStr">
+      <c r="G202" s="5" t="inlineStr">
         <is>
           <t>nvidia/vila</t>
         </is>
       </c>
-      <c r="H201" s="21" t="inlineStr">
+      <c r="H202" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I201" s="7" t="n"/>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="I202" s="7" t="n"/>
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K201" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L201" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M201" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N201" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O201" s="2" t="n">
+      <c r="K202" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L202" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M202" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N202" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P201" s="2" t="inlineStr">
+      <c r="P202" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q201" s="5" t="inlineStr">
+      <c r="Q202" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R201" s="2" t="n">
+      <c r="R202" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R180"/>
+  <autoFilter ref="A1:R181"/>
   <mergeCells count="1">
-    <mergeCell ref="A182:R182"/>
+    <mergeCell ref="A183:R183"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O180">
+  <conditionalFormatting sqref="O2:O181">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17126,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-23T11:43:41Z (source: live)</t>
+          <t>Registry updated 2026-10-23T17:12:07Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-23T17:12:07Z (source: live)</t>
+          <t>Registry updated 2026-10-23T21:27:19Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-23T21:27:19Z (source: live)</t>
+          <t>Registry updated 2026-10-24T04:41:20Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-24T04:41:20Z (source: live)</t>
+          <t>Registry updated 2026-10-24T11:07:02Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-24T11:07:02Z (source: live)</t>
+          <t>Registry updated 2026-10-24T15:59:41Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-24T15:59:41Z (source: live)</t>
+          <t>Registry updated 2026-10-24T20:53:22Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-24T20:53:22Z (source: live)</t>
+          <t>Registry updated 2026-10-25T04:47:01Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-25T04:47:01Z (source: live)</t>
+          <t>Registry updated 2026-10-25T11:36:42Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-25T11:36:42Z (source: live)</t>
+          <t>Registry updated 2026-10-25T16:27:01Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-25T16:27:01Z (source: live)</t>
+          <t>Registry updated 2026-10-25T20:54:12Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-25T20:54:12Z (source: live)</t>
+          <t>Registry updated 2026-10-26T04:52:19Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-26T04:52:19Z (source: live)</t>
+          <t>Registry updated 2026-10-26T13:09:18Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-26T13:09:18Z (source: live)</t>
+          <t>Registry updated 2026-10-26T22:42:32Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17206,7 +17206,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-26T22:42:32Z (source: live)</t>
+          <t>Registry updated 2026-10-27T05:10:28Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17124,7 +17124,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-27T12:17:27Z (source: live)</t>
+          <t>Registry updated 2026-10-27T22:18:25Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17124,7 +17124,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-27T22:18:25Z (source: live)</t>
+          <t>Registry updated 2026-10-28T05:46:35Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to read" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Free models'!$A$1:$R$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="B167" s="19" t="inlineStr">
         <is>
-          <t>glm-5.3</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="G167" s="20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="Q167" s="20" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R167" s="18" t="n">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>ai21labs/jamba-1.5-large-instruct</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="Q168" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R168" s="2" t="n">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B169" s="19" t="inlineStr">
         <is>
-          <t>jamba-1.5-large-instruct</t>
+          <t>kimi-k2.6</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G169" s="20" t="inlineStr">
         <is>
-          <t>ai21labs/jamba-1.5-large-instruct</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="H169" s="21" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>kimi-k2.6</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -14468,12 +14468,12 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>lyria-3.5</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="B171" s="19" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="G171" s="20" t="inlineStr">
         <is>
-          <t>lyria-3.5</t>
+          <t>lyria-realtime-exp</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>lyria-realtime-exp</t>
+          <t>minimaxai/minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
       </c>
       <c r="Q172" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>extraction, agent, fast</t>
         </is>
       </c>
       <c r="R172" s="2" t="n">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="B173" s="19" t="inlineStr">
         <is>
-          <t>minimax-m3.1-flash</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -14708,12 +14708,12 @@
       </c>
       <c r="F173" s="20" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="G173" s="20" t="inlineStr">
         <is>
-          <t>minimaxai/minimax-m3.1-flash</t>
+          <t>nano-banana-pro-preview</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="O173" s="18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P173" s="18" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvclip</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>nano-banana-pro-preview</t>
+          <t>nvidia/nvclip</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="Q174" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent, fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R174" s="2" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="B175" s="19" t="inlineStr">
         <is>
-          <t>nvclip</t>
+          <t>phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="G175" s="20" t="inlineStr">
         <is>
-          <t>nvidia/nvclip</t>
+          <t>microsoft/phi-3.5-moe-instruct</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>phi-3.5-moe-instruct</t>
+          <t>prompt-to-audio</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -14948,12 +14948,12 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>fastrouter</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>microsoft/phi-3.5-moe-instruct</t>
+          <t>ace-step/prompt-to-audio</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -14967,14 +14967,14 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K176" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L176" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
+      <c r="K176" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L176" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="M176" s="9" t="inlineStr">
@@ -14988,16 +14988,16 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Price 0</t>
         </is>
       </c>
       <c r="Q176" s="5" t="inlineStr">
         <is>
-          <t>extraction, agent</t>
+          <t>general</t>
         </is>
       </c>
       <c r="R176" s="2" t="n">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="B177" s="19" t="inlineStr">
         <is>
-          <t>prompt-to-audio</t>
+          <t>recurrentgemma-2b</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -15023,17 +15023,17 @@
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>fastrouter</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G177" s="20" t="inlineStr">
         <is>
-          <t>ace-step/prompt-to-audio</t>
+          <t>google/recurrentgemma-2b</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
@@ -15052,9 +15052,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L177" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L177" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="M177" s="24" t="inlineStr">
@@ -15068,16 +15068,16 @@
         </is>
       </c>
       <c r="O177" s="18" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="P177" s="18" t="inlineStr">
         <is>
-          <t>Price 0</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="Q177" s="20" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="R177" s="18" t="n">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>recurrentgemma-2b</t>
+          <t>step-5-preview</t>
         </is>
       </c>
       <c r="C178" s="39" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>google/recurrentgemma-2b</t>
+          <t>stepfun-ai/step-5-preview</t>
         </is>
       </c>
       <c r="H178" s="21" t="inlineStr">
@@ -15127,9 +15127,9 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="K178" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="K178" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
         </is>
       </c>
       <c r="L178" s="23" t="inlineStr">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="Q178" s="5" t="inlineStr">
         <is>
-          <t>fast</t>
+          <t>extraction, agent</t>
         </is>
       </c>
       <c r="R178" s="2" t="n">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="B179" s="19" t="inlineStr">
         <is>
-          <t>step-5-preview</t>
+          <t>yi-large</t>
         </is>
       </c>
       <c r="C179" s="39" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="G179" s="20" t="inlineStr">
         <is>
-          <t>stepfun-ai/step-5-preview</t>
+          <t>01-ai/yi-large</t>
         </is>
       </c>
       <c r="H179" s="21" t="inlineStr">
@@ -15244,1651 +15244,1571 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>yi-large</t>
-        </is>
-      </c>
-      <c r="C180" s="39" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="41" t="inlineStr">
+        <is>
+          <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>Tier (1-5)</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G182" s="1" t="inlineStr">
+        <is>
+          <t>Gateway model id</t>
+        </is>
+      </c>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>Context class</t>
+        </is>
+      </c>
+      <c r="I182" s="1" t="inlineStr">
+        <is>
+          <t>Context (tokens)</t>
+        </is>
+      </c>
+      <c r="J182" s="1" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="K182" s="1" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="L182" s="1" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="M182" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="N182" s="1" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="O182" s="1" t="inlineStr">
+        <is>
+          <t>Speed (0-100)</t>
+        </is>
+      </c>
+      <c r="P182" s="1" t="inlineStr">
+        <is>
+          <t>Free type</t>
+        </is>
+      </c>
+      <c r="Q182" s="1" t="inlineStr">
+        <is>
+          <t>Best for</t>
+        </is>
+      </c>
+      <c r="R182" s="1" t="inlineStr">
+        <is>
+          <t>Gateways in group</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>nemotron-3.5-super-vl-120b-a12b</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>120B</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
+        </is>
+      </c>
+      <c r="H183" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I183" s="7" t="n"/>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M183" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N183" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q183" s="5" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D184" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E184" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F184" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G184" s="20" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I184" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J184" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L184" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M184" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N184" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O184" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P184" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q184" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R184" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I185" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L185" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M185" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N185" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q185" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E186" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F186" s="13" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G186" s="13" t="inlineStr">
+        <is>
+          <t>google/gemini-3-pro-image-preview</t>
+        </is>
+      </c>
+      <c r="H186" s="28" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I186" s="15" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J186" s="10" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L186" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N186" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O186" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="P186" s="10" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q186" s="13" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R186" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="D187" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E187" s="18" t="inlineStr">
+        <is>
+          <t>90B</t>
+        </is>
+      </c>
+      <c r="F187" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G187" s="20" t="inlineStr">
+        <is>
+          <t>meta/llama-3.2-90b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="H187" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I187" s="22" t="n"/>
+      <c r="J187" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L187" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M187" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N187" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O187" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P187" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q187" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R187" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="C188" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M188" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="N188" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q188" s="5" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="C189" s="32" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E189" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F189" s="13" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G189" s="13" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-image</t>
+        </is>
+      </c>
+      <c r="H189" s="42" t="inlineStr">
+        <is>
+          <t>Medium (8K-32K)</t>
+        </is>
+      </c>
+      <c r="I189" s="15" t="n">
+        <v>32768</v>
+      </c>
+      <c r="J189" s="10" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K189" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L189" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M189" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N189" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O189" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="P189" s="10" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q189" s="13" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, fast</t>
+        </is>
+      </c>
+      <c r="R189" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B190" s="19" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image</t>
+        </is>
+      </c>
+      <c r="C190" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D190" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E190" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F190" s="20" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G190" s="20" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I190" s="22" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J190" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L190" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M190" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N190" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O190" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="P190" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q190" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R190" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="C191" s="31" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L191" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M191" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N191" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q191" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="C192" s="32" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" s="10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F192" s="13" t="inlineStr">
+        <is>
+          <t>fastrouter</t>
+        </is>
+      </c>
+      <c r="G192" s="13" t="inlineStr">
+        <is>
+          <t>google/gemini-3.1-flash-image-preview</t>
+        </is>
+      </c>
+      <c r="H192" s="28" t="inlineStr">
+        <is>
+          <t>Long (32K-200K)</t>
+        </is>
+      </c>
+      <c r="I192" s="15" t="n">
+        <v>65536</v>
+      </c>
+      <c r="J192" s="10" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L192" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N192" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O192" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="P192" s="10" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q192" s="13" t="inlineStr">
+        <is>
+          <t>vision, extraction, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R192" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>neva-22b</t>
+        </is>
+      </c>
+      <c r="C193" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="D193" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E193" s="18" t="inlineStr">
+        <is>
+          <t>22B</t>
+        </is>
+      </c>
+      <c r="F193" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G193" s="20" t="inlineStr">
+        <is>
+          <t>nvidia/neva-22b</t>
+        </is>
+      </c>
+      <c r="H193" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I193" s="22" t="n"/>
+      <c r="J193" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L193" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N193" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O193" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="P193" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q193" s="20" t="inlineStr">
+        <is>
+          <t>extraction, agent</t>
+        </is>
+      </c>
+      <c r="R193" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="C194" s="35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite-image</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L194" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N194" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q194" s="5" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, long_doc, fast</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>llama-3.2-11b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="C195" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="D195" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" s="18" t="inlineStr">
+        <is>
+          <t>11B</t>
+        </is>
+      </c>
+      <c r="F195" s="20" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G195" s="20" t="inlineStr">
+        <is>
+          <t>meta/llama-3.2-11b-vision-instruct</t>
+        </is>
+      </c>
+      <c r="H195" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I195" s="22" t="n"/>
+      <c r="J195" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L195" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N195" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O195" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="P195" s="18" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q195" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent, fast</t>
+        </is>
+      </c>
+      <c r="R195" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>fuyu-8b</t>
+        </is>
+      </c>
+      <c r="C196" s="37" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>adept/fuyu-8b</t>
+        </is>
+      </c>
+      <c r="H196" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L196" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N196" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>Free tier</t>
+        </is>
+      </c>
+      <c r="Q196" s="5" t="inlineStr">
+        <is>
+          <t>extraction, agent, fast</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>nemotron-3.5-super-vl</t>
+        </is>
+      </c>
+      <c r="C197" s="39" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="D180" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="D197" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
+      <c r="F197" s="20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G197" s="20" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3.5-super-vl:free</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>Ultra (&gt;200K)</t>
+        </is>
+      </c>
+      <c r="I197" s="22" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J197" s="18" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K197" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L197" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M197" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N197" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O197" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="P197" s="18" t="inlineStr">
+        <is>
+          <t>Price 0</t>
+        </is>
+      </c>
+      <c r="Q197" s="20" t="inlineStr">
+        <is>
+          <t>reasoning, vision, extraction, agent, long_doc</t>
+        </is>
+      </c>
+      <c r="R197" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>kosmos-2</t>
+        </is>
+      </c>
+      <c r="C198" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>01-ai/yi-large</t>
-        </is>
-      </c>
-      <c r="H180" s="21" t="inlineStr">
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>microsoft/kosmos-2</t>
+        </is>
+      </c>
+      <c r="H198" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I180" s="7" t="n"/>
-      <c r="J180" s="2" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="K180" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L180" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M180" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N180" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O180" s="2" t="n">
+      <c r="I198" s="7" t="n"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>Vision specialist</t>
+        </is>
+      </c>
+      <c r="K198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L198" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N198" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="P180" s="2" t="inlineStr">
+      <c r="P198" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q180" s="5" t="inlineStr">
+      <c r="Q198" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R180" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="41" t="inlineStr">
-        <is>
-          <t>VISION-SPECIALIST MODELS (image models, listed separately; skip these if you only need text)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B183" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C183" s="1" t="inlineStr">
-        <is>
-          <t>Intelligence</t>
-        </is>
-      </c>
-      <c r="D183" s="1" t="inlineStr">
-        <is>
-          <t>Tier (1-5)</t>
-        </is>
-      </c>
-      <c r="E183" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F183" s="1" t="inlineStr">
-        <is>
-          <t>Gateway</t>
-        </is>
-      </c>
-      <c r="G183" s="1" t="inlineStr">
-        <is>
-          <t>Gateway model id</t>
-        </is>
-      </c>
-      <c r="H183" s="1" t="inlineStr">
-        <is>
-          <t>Context class</t>
-        </is>
-      </c>
-      <c r="I183" s="1" t="inlineStr">
-        <is>
-          <t>Context (tokens)</t>
-        </is>
-      </c>
-      <c r="J183" s="1" t="inlineStr">
-        <is>
-          <t>Modality</t>
-        </is>
-      </c>
-      <c r="K183" s="1" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="L183" s="1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="M183" s="1" t="inlineStr">
-        <is>
-          <t>Reasoning</t>
-        </is>
-      </c>
-      <c r="N183" s="1" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
-      </c>
-      <c r="O183" s="1" t="inlineStr">
-        <is>
-          <t>Speed (0-100)</t>
-        </is>
-      </c>
-      <c r="P183" s="1" t="inlineStr">
-        <is>
-          <t>Free type</t>
-        </is>
-      </c>
-      <c r="Q183" s="1" t="inlineStr">
-        <is>
-          <t>Best for</t>
-        </is>
-      </c>
-      <c r="R183" s="1" t="inlineStr">
-        <is>
-          <t>Gateways in group</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>nemotron-3.5-super-vl-120b-a12b</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>120B</t>
-        </is>
-      </c>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="R198" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B199" s="19" t="inlineStr">
+        <is>
+          <t>phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="C199" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D199" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F199" s="20" t="inlineStr">
         <is>
           <t>nvidia</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/nemotron-3.5-super-vl-120b-a12b</t>
-        </is>
-      </c>
-      <c r="H184" s="21" t="inlineStr">
+      <c r="G199" s="20" t="inlineStr">
+        <is>
+          <t>microsoft/phi-3-vision-128k-instruct</t>
+        </is>
+      </c>
+      <c r="H199" s="21" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I184" s="7" t="n"/>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="I199" s="22" t="n"/>
+      <c r="J199" s="18" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M184" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N184" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O184" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="P184" s="2" t="inlineStr">
+      <c r="K199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L199" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M199" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N199" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O199" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="P199" s="18" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q184" s="5" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R184" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B185" s="19" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D185" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E185" s="18" t="inlineStr">
+      <c r="Q199" s="20" t="inlineStr">
+        <is>
+          <t>vision, extraction, agent</t>
+        </is>
+      </c>
+      <c r="R199" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>vila</t>
+        </is>
+      </c>
+      <c r="C200" s="39" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F185" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G185" s="20" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image</t>
-        </is>
-      </c>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I185" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J185" s="18" t="inlineStr">
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>nvidia/vila</t>
+        </is>
+      </c>
+      <c r="H200" s="21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I200" s="7" t="n"/>
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>Vision specialist</t>
         </is>
       </c>
-      <c r="K185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L185" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N185" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O185" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P185" s="18" t="inlineStr">
+      <c r="K200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="L200" s="23" t="inlineStr">
+        <is>
+          <t>Yes~</t>
+        </is>
+      </c>
+      <c r="M200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N200" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
         <is>
           <t>Free tier</t>
         </is>
       </c>
-      <c r="Q185" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R185" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I186" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L186" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M186" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N186" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O186" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P186" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q186" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R186" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="C187" s="12" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E187" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F187" s="13" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G187" s="13" t="inlineStr">
-        <is>
-          <t>google/gemini-3-pro-image-preview</t>
-        </is>
-      </c>
-      <c r="H187" s="28" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I187" s="15" t="n">
-        <v>65536</v>
-      </c>
-      <c r="J187" s="10" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L187" s="28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N187" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O187" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="P187" s="10" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q187" s="13" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R187" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B188" s="19" t="inlineStr">
-        <is>
-          <t>llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D188" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E188" s="18" t="inlineStr">
-        <is>
-          <t>90B</t>
-        </is>
-      </c>
-      <c r="F188" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G188" s="20" t="inlineStr">
-        <is>
-          <t>meta/llama-3.2-90b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H188" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I188" s="22" t="n"/>
-      <c r="J188" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L188" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N188" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O188" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="P188" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q188" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R188" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="C189" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="H189" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I189" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J189" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M189" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="N189" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O189" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P189" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q189" s="5" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R189" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="C190" s="32" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D190" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E190" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F190" s="13" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G190" s="13" t="inlineStr">
-        <is>
-          <t>google/gemini-2.5-flash-image</t>
-        </is>
-      </c>
-      <c r="H190" s="42" t="inlineStr">
-        <is>
-          <t>Medium (8K-32K)</t>
-        </is>
-      </c>
-      <c r="I190" s="15" t="n">
-        <v>32768</v>
-      </c>
-      <c r="J190" s="10" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L190" s="28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M190" s="28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N190" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O190" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="P190" s="10" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q190" s="13" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, fast</t>
-        </is>
-      </c>
-      <c r="R190" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B191" s="19" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="C191" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D191" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E191" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F191" s="20" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G191" s="20" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image</t>
-        </is>
-      </c>
-      <c r="H191" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I191" s="22" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J191" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L191" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N191" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O191" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="P191" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q191" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R191" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="C192" s="31" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G192" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I192" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J192" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L192" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N192" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O192" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P192" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q192" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R192" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B193" s="11" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="C193" s="32" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D193" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E193" s="10" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F193" s="13" t="inlineStr">
-        <is>
-          <t>fastrouter</t>
-        </is>
-      </c>
-      <c r="G193" s="13" t="inlineStr">
-        <is>
-          <t>google/gemini-3.1-flash-image-preview</t>
-        </is>
-      </c>
-      <c r="H193" s="28" t="inlineStr">
-        <is>
-          <t>Long (32K-200K)</t>
-        </is>
-      </c>
-      <c r="I193" s="15" t="n">
-        <v>65536</v>
-      </c>
-      <c r="J193" s="10" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L193" s="28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N193" s="17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O193" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="P193" s="10" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q193" s="13" t="inlineStr">
-        <is>
-          <t>vision, extraction, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R193" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B194" s="19" t="inlineStr">
-        <is>
-          <t>neva-22b</t>
-        </is>
-      </c>
-      <c r="C194" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D194" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E194" s="18" t="inlineStr">
-        <is>
-          <t>22B</t>
-        </is>
-      </c>
-      <c r="F194" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G194" s="20" t="inlineStr">
-        <is>
-          <t>nvidia/neva-22b</t>
-        </is>
-      </c>
-      <c r="H194" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I194" s="22" t="n"/>
-      <c r="J194" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L194" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N194" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O194" s="18" t="n">
-        <v>33</v>
-      </c>
-      <c r="P194" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q194" s="20" t="inlineStr">
+      <c r="Q200" s="5" t="inlineStr">
         <is>
           <t>extraction, agent</t>
         </is>
       </c>
-      <c r="R194" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="C195" s="35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>gemini-3.1-flash-lite-image</t>
-        </is>
-      </c>
-      <c r="H195" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I195" s="7" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L195" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N195" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O195" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="P195" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q195" s="5" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, long_doc, fast</t>
-        </is>
-      </c>
-      <c r="R195" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B196" s="19" t="inlineStr">
-        <is>
-          <t>llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="C196" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="D196" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E196" s="18" t="inlineStr">
-        <is>
-          <t>11B</t>
-        </is>
-      </c>
-      <c r="F196" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G196" s="20" t="inlineStr">
-        <is>
-          <t>meta/llama-3.2-11b-vision-instruct</t>
-        </is>
-      </c>
-      <c r="H196" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I196" s="22" t="n"/>
-      <c r="J196" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L196" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N196" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O196" s="18" t="n">
-        <v>41</v>
-      </c>
-      <c r="P196" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q196" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent, fast</t>
-        </is>
-      </c>
-      <c r="R196" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>fuyu-8b</t>
-        </is>
-      </c>
-      <c r="C197" s="37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>adept/fuyu-8b</t>
-        </is>
-      </c>
-      <c r="H197" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I197" s="7" t="n"/>
-      <c r="J197" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L197" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N197" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O197" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="P197" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q197" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent, fast</t>
-        </is>
-      </c>
-      <c r="R197" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B198" s="19" t="inlineStr">
-        <is>
-          <t>nemotron-3.5-super-vl</t>
-        </is>
-      </c>
-      <c r="C198" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D198" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F198" s="20" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
-      <c r="G198" s="20" t="inlineStr">
-        <is>
-          <t>nvidia/nemotron-3.5-super-vl:free</t>
-        </is>
-      </c>
-      <c r="H198" s="6" t="inlineStr">
-        <is>
-          <t>Ultra (&gt;200K)</t>
-        </is>
-      </c>
-      <c r="I198" s="22" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="J198" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K198" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L198" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M198" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N198" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O198" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="P198" s="18" t="inlineStr">
-        <is>
-          <t>Price 0</t>
-        </is>
-      </c>
-      <c r="Q198" s="20" t="inlineStr">
-        <is>
-          <t>reasoning, vision, extraction, agent, long_doc</t>
-        </is>
-      </c>
-      <c r="R198" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>kosmos-2</t>
-        </is>
-      </c>
-      <c r="C199" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F199" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t>microsoft/kosmos-2</t>
-        </is>
-      </c>
-      <c r="H199" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I199" s="7" t="n"/>
-      <c r="J199" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L199" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N199" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O199" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="P199" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q199" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R199" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B200" s="19" t="inlineStr">
-        <is>
-          <t>phi-3-vision-128k-instruct</t>
-        </is>
-      </c>
-      <c r="C200" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D200" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="18" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F200" s="20" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G200" s="20" t="inlineStr">
-        <is>
-          <t>microsoft/phi-3-vision-128k-instruct</t>
-        </is>
-      </c>
-      <c r="H200" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I200" s="22" t="n"/>
-      <c r="J200" s="18" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L200" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M200" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N200" s="24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O200" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="P200" s="18" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q200" s="20" t="inlineStr">
-        <is>
-          <t>vision, extraction, agent</t>
-        </is>
-      </c>
-      <c r="R200" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>vila</t>
-        </is>
-      </c>
-      <c r="C201" s="39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F201" s="5" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="G201" s="5" t="inlineStr">
-        <is>
-          <t>nvidia/vila</t>
-        </is>
-      </c>
-      <c r="H201" s="21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="I201" s="7" t="n"/>
-      <c r="J201" s="2" t="inlineStr">
-        <is>
-          <t>Vision specialist</t>
-        </is>
-      </c>
-      <c r="K201" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="L201" s="23" t="inlineStr">
-        <is>
-          <t>Yes~</t>
-        </is>
-      </c>
-      <c r="M201" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N201" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O201" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="P201" s="2" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="Q201" s="5" t="inlineStr">
-        <is>
-          <t>extraction, agent</t>
-        </is>
-      </c>
-      <c r="R201" s="2" t="n">
+      <c r="R200" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R180"/>
+  <autoFilter ref="A1:R179"/>
   <mergeCells count="1">
-    <mergeCell ref="A182:R182"/>
+    <mergeCell ref="A181:R181"/>
   </mergeCells>
-  <conditionalFormatting sqref="O2:O180">
+  <conditionalFormatting sqref="O2:O179">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -17124,7 +17044,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-28T05:46:35Z (source: live)</t>
+          <t>Registry updated 2026-10-28T12:59:56Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17044,7 +17044,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-28T12:59:56Z (source: live)</t>
+          <t>Registry updated 2026-10-28T22:38:31Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17044,7 +17044,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-28T22:38:31Z (source: live)</t>
+          <t>Registry updated 2026-10-29T05:52:50Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17044,7 +17044,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-29T05:52:50Z (source: live)</t>
+          <t>Registry updated 2026-10-29T13:07:53Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17288,7 +17288,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-29T22:47:59Z (source: live)</t>
+          <t>Registry updated 2026-10-30T05:53:51Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17288,7 +17288,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-30T05:53:51Z (source: live)</t>
+          <t>Registry updated 2026-10-30T13:00:11Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17288,7 +17288,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-30T13:00:11Z (source: live)</t>
+          <t>Registry updated 2026-10-30T22:24:42Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17288,7 +17288,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-30T22:24:42Z (source: live)</t>
+          <t>Registry updated 2026-10-31T05:48:59Z (source: live)</t>
         </is>
       </c>
     </row>

--- a/registry/models.xlsx
+++ b/registry/models.xlsx
@@ -17288,7 +17288,7 @@
     <row r="21">
       <c r="A21" s="54" t="inlineStr">
         <is>
-          <t>Registry updated 2026-10-31T05:48:59Z (source: live)</t>
+          <t>Registry updated 2026-10-31T12:38:17Z (source: live)</t>
         </is>
       </c>
     </row>
